--- a/school_2/school_2_KP.xlsx
+++ b/school_2/school_2_KP.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\МирзаяновИИ\Documents\projects\school_2\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10425" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8055" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ТКП" sheetId="1" r:id="rId1"/>
@@ -13,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ТКП!$A$7:$U$7</definedName>
   </definedNames>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -2795,6 +2800,39 @@
     <xf numFmtId="0" fontId="14" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2825,52 +2863,19 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3259,79 +3264,79 @@
       </c>
     </row>
     <row r="2" spans="1:35" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
-      <c r="O2" s="39"/>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
-      <c r="T2" s="39"/>
-      <c r="U2" s="39"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="50"/>
+      <c r="P2" s="50"/>
+      <c r="Q2" s="50"/>
+      <c r="R2" s="50"/>
+      <c r="S2" s="50"/>
+      <c r="T2" s="50"/>
+      <c r="U2" s="50"/>
     </row>
     <row r="3" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40"/>
-      <c r="S3" s="40"/>
-      <c r="T3" s="40"/>
-      <c r="U3" s="40"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="51"/>
+      <c r="O3" s="51"/>
+      <c r="P3" s="51"/>
+      <c r="Q3" s="51"/>
+      <c r="R3" s="51"/>
+      <c r="S3" s="51"/>
+      <c r="T3" s="51"/>
+      <c r="U3" s="51"/>
     </row>
     <row r="4" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="41"/>
-      <c r="N4" s="41"/>
-      <c r="O4" s="41"/>
-      <c r="P4" s="41"/>
-      <c r="Q4" s="41"/>
-      <c r="R4" s="41"/>
-      <c r="S4" s="41"/>
-      <c r="T4" s="41"/>
-      <c r="U4" s="41"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="52"/>
+      <c r="M4" s="52"/>
+      <c r="N4" s="52"/>
+      <c r="O4" s="52"/>
+      <c r="P4" s="52"/>
+      <c r="Q4" s="52"/>
+      <c r="R4" s="52"/>
+      <c r="S4" s="52"/>
+      <c r="T4" s="52"/>
+      <c r="U4" s="52"/>
     </row>
     <row r="5" spans="1:35" ht="40.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="48" t="s">
@@ -3361,115 +3366,115 @@
       <c r="I5" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J5" s="42" t="s">
+      <c r="J5" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="43"/>
-      <c r="L5" s="43"/>
-      <c r="M5" s="43"/>
-      <c r="N5" s="43"/>
-      <c r="O5" s="44"/>
-      <c r="P5" s="45" t="s">
+      <c r="K5" s="54"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="54"/>
+      <c r="N5" s="54"/>
+      <c r="O5" s="55"/>
+      <c r="P5" s="56" t="s">
         <v>780</v>
       </c>
-      <c r="Q5" s="46"/>
-      <c r="R5" s="47"/>
-      <c r="S5" s="45">
+      <c r="Q5" s="57"/>
+      <c r="R5" s="58"/>
+      <c r="S5" s="56">
         <v>9701212867</v>
       </c>
-      <c r="T5" s="46"/>
-      <c r="U5" s="47"/>
+      <c r="T5" s="57"/>
+      <c r="U5" s="58"/>
     </row>
     <row r="6" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="49"/>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="51" t="s">
+      <c r="A6" s="59"/>
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="52"/>
+      <c r="K6" s="41"/>
       <c r="L6" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="M6" s="51" t="s">
+      <c r="M6" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="N6" s="52"/>
+      <c r="N6" s="41"/>
       <c r="O6" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="P6" s="51" t="s">
+      <c r="P6" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="Q6" s="52"/>
+      <c r="Q6" s="41"/>
       <c r="R6" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="S6" s="51" t="s">
+      <c r="S6" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="T6" s="52"/>
+      <c r="T6" s="41"/>
       <c r="U6" s="48" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:35" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="50"/>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="50"/>
-      <c r="I7" s="50"/>
+      <c r="A7" s="49"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
       <c r="J7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L7" s="50"/>
+      <c r="L7" s="49"/>
       <c r="M7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="O7" s="50"/>
+      <c r="O7" s="49"/>
       <c r="P7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="R7" s="50"/>
+      <c r="R7" s="49"/>
       <c r="S7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="T7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="U7" s="50"/>
+      <c r="U7" s="49"/>
     </row>
     <row r="8" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="55"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="47"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -3523,15 +3528,15 @@
       <c r="B9" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="56" t="s">
+      <c r="C9" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="58"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="44"/>
       <c r="M9" s="6">
         <f t="shared" si="0"/>
         <v>21918840.049999997</v>
@@ -3582,15 +3587,15 @@
       <c r="B10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="56" t="s">
+      <c r="C10" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="58"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="44"/>
       <c r="M10" s="6">
         <f t="shared" si="0"/>
         <v>21918840.049999997</v>
@@ -3641,15 +3646,15 @@
       <c r="B11" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="56" t="s">
+      <c r="C11" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="58"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="44"/>
       <c r="M11" s="6">
         <f t="shared" si="0"/>
         <v>21918840.049999997</v>
@@ -3700,15 +3705,15 @@
       <c r="B12" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="56" t="s">
+      <c r="C12" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="58"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="44"/>
       <c r="M12" s="6">
         <f>SUM(M13,M66,M148,M169)</f>
         <v>21918840.049999997</v>
@@ -3759,15 +3764,15 @@
       <c r="B13" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="56" t="s">
+      <c r="C13" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="58"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="44"/>
       <c r="M13" s="6">
         <f>SUM(M14,M37,M45)</f>
         <v>3570644.12</v>
@@ -3818,15 +3823,15 @@
       <c r="B14" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="56" t="s">
+      <c r="C14" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="58"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="44"/>
       <c r="M14" s="6">
         <f>SUM(M15,M19,M21,M29)</f>
         <v>2618573.91</v>
@@ -5251,15 +5256,15 @@
       <c r="B37" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="C37" s="56" t="s">
+      <c r="C37" s="42" t="s">
         <v>154</v>
       </c>
-      <c r="D37" s="57"/>
-      <c r="E37" s="57"/>
-      <c r="F37" s="57"/>
-      <c r="G37" s="57"/>
-      <c r="H37" s="57"/>
-      <c r="I37" s="58"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="43"/>
+      <c r="I37" s="44"/>
       <c r="M37" s="6">
         <f>SUM(M38,M41,M43)</f>
         <v>122933.90000000001</v>
@@ -5844,15 +5849,15 @@
       <c r="B45" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="C45" s="56" t="s">
+      <c r="C45" s="42" t="s">
         <v>193</v>
       </c>
-      <c r="D45" s="57"/>
-      <c r="E45" s="57"/>
-      <c r="F45" s="57"/>
-      <c r="G45" s="57"/>
-      <c r="H45" s="57"/>
-      <c r="I45" s="58"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="43"/>
+      <c r="G45" s="43"/>
+      <c r="H45" s="43"/>
+      <c r="I45" s="44"/>
       <c r="M45" s="6">
         <f>SUM(M46,M51,M55,M60,M63)</f>
         <v>829136.31</v>
@@ -7247,15 +7252,15 @@
       <c r="B66" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="C66" s="56" t="s">
+      <c r="C66" s="42" t="s">
         <v>299</v>
       </c>
-      <c r="D66" s="57"/>
-      <c r="E66" s="57"/>
-      <c r="F66" s="57"/>
-      <c r="G66" s="57"/>
-      <c r="H66" s="57"/>
-      <c r="I66" s="58"/>
+      <c r="D66" s="43"/>
+      <c r="E66" s="43"/>
+      <c r="F66" s="43"/>
+      <c r="G66" s="43"/>
+      <c r="H66" s="43"/>
+      <c r="I66" s="44"/>
       <c r="M66" s="6">
         <f>SUM(M67,M97,M128)</f>
         <v>4332566.72</v>
@@ -7306,15 +7311,15 @@
       <c r="B67" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="C67" s="56" t="s">
+      <c r="C67" s="42" t="s">
         <v>302</v>
       </c>
-      <c r="D67" s="57"/>
-      <c r="E67" s="57"/>
-      <c r="F67" s="57"/>
-      <c r="G67" s="57"/>
-      <c r="H67" s="57"/>
-      <c r="I67" s="58"/>
+      <c r="D67" s="43"/>
+      <c r="E67" s="43"/>
+      <c r="F67" s="43"/>
+      <c r="G67" s="43"/>
+      <c r="H67" s="43"/>
+      <c r="I67" s="44"/>
       <c r="M67" s="6">
         <f>SUM(M68,M71,M75,M79,M82,M85,M89,M92)</f>
         <v>2963619.5900000003</v>
@@ -9341,15 +9346,15 @@
       <c r="B97" s="10" t="s">
         <v>419</v>
       </c>
-      <c r="C97" s="56" t="s">
+      <c r="C97" s="42" t="s">
         <v>420</v>
       </c>
-      <c r="D97" s="57"/>
-      <c r="E97" s="57"/>
-      <c r="F97" s="57"/>
-      <c r="G97" s="57"/>
-      <c r="H97" s="57"/>
-      <c r="I97" s="58"/>
+      <c r="D97" s="43"/>
+      <c r="E97" s="43"/>
+      <c r="F97" s="43"/>
+      <c r="G97" s="43"/>
+      <c r="H97" s="43"/>
+      <c r="I97" s="44"/>
       <c r="M97" s="6">
         <f>SUM(M98,M107,M110,M113,M116,M119,M122,M125)</f>
         <v>1187256.6599999997</v>
@@ -11428,15 +11433,15 @@
       <c r="B128" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="C128" s="56" t="s">
+      <c r="C128" s="42" t="s">
         <v>534</v>
       </c>
-      <c r="D128" s="57"/>
-      <c r="E128" s="57"/>
-      <c r="F128" s="57"/>
-      <c r="G128" s="57"/>
-      <c r="H128" s="57"/>
-      <c r="I128" s="58"/>
+      <c r="D128" s="43"/>
+      <c r="E128" s="43"/>
+      <c r="F128" s="43"/>
+      <c r="G128" s="43"/>
+      <c r="H128" s="43"/>
+      <c r="I128" s="44"/>
       <c r="M128" s="6">
         <f>SUM(M129,M132,M135,M138,M143)</f>
         <v>181690.47</v>
@@ -12759,15 +12764,15 @@
       <c r="B148" s="10" t="s">
         <v>616</v>
       </c>
-      <c r="C148" s="56" t="s">
+      <c r="C148" s="42" t="s">
         <v>617</v>
       </c>
-      <c r="D148" s="57"/>
-      <c r="E148" s="57"/>
-      <c r="F148" s="57"/>
-      <c r="G148" s="57"/>
-      <c r="H148" s="57"/>
-      <c r="I148" s="58"/>
+      <c r="D148" s="43"/>
+      <c r="E148" s="43"/>
+      <c r="F148" s="43"/>
+      <c r="G148" s="43"/>
+      <c r="H148" s="43"/>
+      <c r="I148" s="44"/>
       <c r="M148" s="6">
         <f>SUM(M149,M153)</f>
         <v>447303.98</v>
@@ -12818,15 +12823,15 @@
       <c r="B149" s="10" t="s">
         <v>619</v>
       </c>
-      <c r="C149" s="56" t="s">
+      <c r="C149" s="42" t="s">
         <v>620</v>
       </c>
-      <c r="D149" s="57"/>
-      <c r="E149" s="57"/>
-      <c r="F149" s="57"/>
-      <c r="G149" s="57"/>
-      <c r="H149" s="57"/>
-      <c r="I149" s="58"/>
+      <c r="D149" s="43"/>
+      <c r="E149" s="43"/>
+      <c r="F149" s="43"/>
+      <c r="G149" s="43"/>
+      <c r="H149" s="43"/>
+      <c r="I149" s="44"/>
       <c r="M149" s="6">
         <f>SUM(M150)</f>
         <v>241468.92</v>
@@ -13089,15 +13094,15 @@
       <c r="B153" s="10" t="s">
         <v>635</v>
       </c>
-      <c r="C153" s="56" t="s">
+      <c r="C153" s="42" t="s">
         <v>636</v>
       </c>
-      <c r="D153" s="57"/>
-      <c r="E153" s="57"/>
-      <c r="F153" s="57"/>
-      <c r="G153" s="57"/>
-      <c r="H153" s="57"/>
-      <c r="I153" s="58"/>
+      <c r="D153" s="43"/>
+      <c r="E153" s="43"/>
+      <c r="F153" s="43"/>
+      <c r="G153" s="43"/>
+      <c r="H153" s="43"/>
+      <c r="I153" s="44"/>
       <c r="M153" s="6">
         <f>SUM(M154,M157,M160,M163,M166)</f>
         <v>205835.06</v>
@@ -14220,15 +14225,15 @@
       <c r="B169" s="10" t="s">
         <v>683</v>
       </c>
-      <c r="C169" s="56" t="s">
+      <c r="C169" s="42" t="s">
         <v>684</v>
       </c>
-      <c r="D169" s="57"/>
-      <c r="E169" s="57"/>
-      <c r="F169" s="57"/>
-      <c r="G169" s="57"/>
-      <c r="H169" s="57"/>
-      <c r="I169" s="58"/>
+      <c r="D169" s="43"/>
+      <c r="E169" s="43"/>
+      <c r="F169" s="43"/>
+      <c r="G169" s="43"/>
+      <c r="H169" s="43"/>
+      <c r="I169" s="44"/>
       <c r="M169" s="6">
         <f>SUM(M170,M173,M177)</f>
         <v>13568325.229999999</v>
@@ -14906,29 +14911,29 @@
       </c>
     </row>
     <row r="179" spans="1:35" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A179" s="53" t="s">
+      <c r="A179" s="45" t="s">
         <v>728</v>
       </c>
-      <c r="B179" s="54"/>
-      <c r="C179" s="54"/>
-      <c r="D179" s="54"/>
-      <c r="E179" s="54"/>
-      <c r="F179" s="54"/>
-      <c r="G179" s="54"/>
-      <c r="H179" s="54"/>
-      <c r="I179" s="54"/>
-      <c r="J179" s="54"/>
-      <c r="K179" s="54"/>
-      <c r="L179" s="54"/>
-      <c r="M179" s="54"/>
-      <c r="N179" s="54"/>
-      <c r="O179" s="54"/>
-      <c r="P179" s="54"/>
-      <c r="Q179" s="54"/>
-      <c r="R179" s="54"/>
-      <c r="S179" s="54"/>
-      <c r="T179" s="54"/>
-      <c r="U179" s="55"/>
+      <c r="B179" s="46"/>
+      <c r="C179" s="46"/>
+      <c r="D179" s="46"/>
+      <c r="E179" s="46"/>
+      <c r="F179" s="46"/>
+      <c r="G179" s="46"/>
+      <c r="H179" s="46"/>
+      <c r="I179" s="46"/>
+      <c r="J179" s="46"/>
+      <c r="K179" s="46"/>
+      <c r="L179" s="46"/>
+      <c r="M179" s="46"/>
+      <c r="N179" s="46"/>
+      <c r="O179" s="46"/>
+      <c r="P179" s="46"/>
+      <c r="Q179" s="46"/>
+      <c r="R179" s="46"/>
+      <c r="S179" s="46"/>
+      <c r="T179" s="46"/>
+      <c r="U179" s="47"/>
     </row>
     <row r="180" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="30"/>
@@ -14944,20 +14949,20 @@
       <c r="E180" s="31"/>
       <c r="F180" s="31"/>
       <c r="G180" s="31"/>
-      <c r="H180" s="51"/>
-      <c r="I180" s="59"/>
-      <c r="J180" s="59"/>
-      <c r="K180" s="59"/>
-      <c r="L180" s="59"/>
-      <c r="M180" s="59"/>
-      <c r="N180" s="59"/>
-      <c r="O180" s="59"/>
-      <c r="P180" s="59"/>
-      <c r="Q180" s="59"/>
-      <c r="R180" s="59"/>
-      <c r="S180" s="59"/>
-      <c r="T180" s="59"/>
-      <c r="U180" s="52"/>
+      <c r="H180" s="39"/>
+      <c r="I180" s="40"/>
+      <c r="J180" s="40"/>
+      <c r="K180" s="40"/>
+      <c r="L180" s="40"/>
+      <c r="M180" s="40"/>
+      <c r="N180" s="40"/>
+      <c r="O180" s="40"/>
+      <c r="P180" s="40"/>
+      <c r="Q180" s="40"/>
+      <c r="R180" s="40"/>
+      <c r="S180" s="40"/>
+      <c r="T180" s="40"/>
+      <c r="U180" s="41"/>
     </row>
     <row r="181" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="30"/>
@@ -14973,20 +14978,20 @@
       <c r="E181" s="31"/>
       <c r="F181" s="31"/>
       <c r="G181" s="31"/>
-      <c r="H181" s="51"/>
-      <c r="I181" s="59"/>
-      <c r="J181" s="59"/>
-      <c r="K181" s="59"/>
-      <c r="L181" s="59"/>
-      <c r="M181" s="59"/>
-      <c r="N181" s="59"/>
-      <c r="O181" s="59"/>
-      <c r="P181" s="59"/>
-      <c r="Q181" s="59"/>
-      <c r="R181" s="59"/>
-      <c r="S181" s="59"/>
-      <c r="T181" s="59"/>
-      <c r="U181" s="52"/>
+      <c r="H181" s="39"/>
+      <c r="I181" s="40"/>
+      <c r="J181" s="40"/>
+      <c r="K181" s="40"/>
+      <c r="L181" s="40"/>
+      <c r="M181" s="40"/>
+      <c r="N181" s="40"/>
+      <c r="O181" s="40"/>
+      <c r="P181" s="40"/>
+      <c r="Q181" s="40"/>
+      <c r="R181" s="40"/>
+      <c r="S181" s="40"/>
+      <c r="T181" s="40"/>
+      <c r="U181" s="41"/>
     </row>
     <row r="182" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A182" s="30"/>
@@ -15002,20 +15007,20 @@
       <c r="E182" s="31"/>
       <c r="F182" s="31"/>
       <c r="G182" s="31"/>
-      <c r="H182" s="51"/>
-      <c r="I182" s="59"/>
-      <c r="J182" s="59"/>
-      <c r="K182" s="59"/>
-      <c r="L182" s="59"/>
-      <c r="M182" s="59"/>
-      <c r="N182" s="59"/>
-      <c r="O182" s="59"/>
-      <c r="P182" s="59"/>
-      <c r="Q182" s="59"/>
-      <c r="R182" s="59"/>
-      <c r="S182" s="59"/>
-      <c r="T182" s="59"/>
-      <c r="U182" s="52"/>
+      <c r="H182" s="39"/>
+      <c r="I182" s="40"/>
+      <c r="J182" s="40"/>
+      <c r="K182" s="40"/>
+      <c r="L182" s="40"/>
+      <c r="M182" s="40"/>
+      <c r="N182" s="40"/>
+      <c r="O182" s="40"/>
+      <c r="P182" s="40"/>
+      <c r="Q182" s="40"/>
+      <c r="R182" s="40"/>
+      <c r="S182" s="40"/>
+      <c r="T182" s="40"/>
+      <c r="U182" s="41"/>
     </row>
     <row r="183" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="30"/>
@@ -15031,20 +15036,20 @@
       <c r="E183" s="31"/>
       <c r="F183" s="31"/>
       <c r="G183" s="31"/>
-      <c r="H183" s="51"/>
-      <c r="I183" s="59"/>
-      <c r="J183" s="59"/>
-      <c r="K183" s="59"/>
-      <c r="L183" s="59"/>
-      <c r="M183" s="59"/>
-      <c r="N183" s="59"/>
-      <c r="O183" s="59"/>
-      <c r="P183" s="59"/>
-      <c r="Q183" s="59"/>
-      <c r="R183" s="59"/>
-      <c r="S183" s="59"/>
-      <c r="T183" s="59"/>
-      <c r="U183" s="52"/>
+      <c r="H183" s="39"/>
+      <c r="I183" s="40"/>
+      <c r="J183" s="40"/>
+      <c r="K183" s="40"/>
+      <c r="L183" s="40"/>
+      <c r="M183" s="40"/>
+      <c r="N183" s="40"/>
+      <c r="O183" s="40"/>
+      <c r="P183" s="40"/>
+      <c r="Q183" s="40"/>
+      <c r="R183" s="40"/>
+      <c r="S183" s="40"/>
+      <c r="T183" s="40"/>
+      <c r="U183" s="41"/>
     </row>
     <row r="184" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" s="30"/>
@@ -15060,20 +15065,20 @@
       <c r="E184" s="31"/>
       <c r="F184" s="31"/>
       <c r="G184" s="31"/>
-      <c r="H184" s="51"/>
-      <c r="I184" s="59"/>
-      <c r="J184" s="59"/>
-      <c r="K184" s="59"/>
-      <c r="L184" s="59"/>
-      <c r="M184" s="59"/>
-      <c r="N184" s="59"/>
-      <c r="O184" s="59"/>
-      <c r="P184" s="59"/>
-      <c r="Q184" s="59"/>
-      <c r="R184" s="59"/>
-      <c r="S184" s="59"/>
-      <c r="T184" s="59"/>
-      <c r="U184" s="52"/>
+      <c r="H184" s="39"/>
+      <c r="I184" s="40"/>
+      <c r="J184" s="40"/>
+      <c r="K184" s="40"/>
+      <c r="L184" s="40"/>
+      <c r="M184" s="40"/>
+      <c r="N184" s="40"/>
+      <c r="O184" s="40"/>
+      <c r="P184" s="40"/>
+      <c r="Q184" s="40"/>
+      <c r="R184" s="40"/>
+      <c r="S184" s="40"/>
+      <c r="T184" s="40"/>
+      <c r="U184" s="41"/>
     </row>
     <row r="185" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A185" s="30"/>
@@ -15089,20 +15094,20 @@
       <c r="E185" s="31"/>
       <c r="F185" s="31"/>
       <c r="G185" s="31"/>
-      <c r="H185" s="51"/>
-      <c r="I185" s="59"/>
-      <c r="J185" s="59"/>
-      <c r="K185" s="59"/>
-      <c r="L185" s="59"/>
-      <c r="M185" s="59"/>
-      <c r="N185" s="59"/>
-      <c r="O185" s="59"/>
-      <c r="P185" s="59"/>
-      <c r="Q185" s="59"/>
-      <c r="R185" s="59"/>
-      <c r="S185" s="59"/>
-      <c r="T185" s="59"/>
-      <c r="U185" s="52"/>
+      <c r="H185" s="39"/>
+      <c r="I185" s="40"/>
+      <c r="J185" s="40"/>
+      <c r="K185" s="40"/>
+      <c r="L185" s="40"/>
+      <c r="M185" s="40"/>
+      <c r="N185" s="40"/>
+      <c r="O185" s="40"/>
+      <c r="P185" s="40"/>
+      <c r="Q185" s="40"/>
+      <c r="R185" s="40"/>
+      <c r="S185" s="40"/>
+      <c r="T185" s="40"/>
+      <c r="U185" s="41"/>
     </row>
     <row r="186" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A186" s="30"/>
@@ -15118,20 +15123,20 @@
       <c r="E186" s="31"/>
       <c r="F186" s="31"/>
       <c r="G186" s="31"/>
-      <c r="H186" s="51"/>
-      <c r="I186" s="59"/>
-      <c r="J186" s="59"/>
-      <c r="K186" s="59"/>
-      <c r="L186" s="59"/>
-      <c r="M186" s="59"/>
-      <c r="N186" s="59"/>
-      <c r="O186" s="59"/>
-      <c r="P186" s="59"/>
-      <c r="Q186" s="59"/>
-      <c r="R186" s="59"/>
-      <c r="S186" s="59"/>
-      <c r="T186" s="59"/>
-      <c r="U186" s="52"/>
+      <c r="H186" s="39"/>
+      <c r="I186" s="40"/>
+      <c r="J186" s="40"/>
+      <c r="K186" s="40"/>
+      <c r="L186" s="40"/>
+      <c r="M186" s="40"/>
+      <c r="N186" s="40"/>
+      <c r="O186" s="40"/>
+      <c r="P186" s="40"/>
+      <c r="Q186" s="40"/>
+      <c r="R186" s="40"/>
+      <c r="S186" s="40"/>
+      <c r="T186" s="40"/>
+      <c r="U186" s="41"/>
     </row>
     <row r="187" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" s="30"/>
@@ -15147,20 +15152,20 @@
       <c r="E187" s="31"/>
       <c r="F187" s="31"/>
       <c r="G187" s="31"/>
-      <c r="H187" s="51"/>
-      <c r="I187" s="59"/>
-      <c r="J187" s="59"/>
-      <c r="K187" s="59"/>
-      <c r="L187" s="59"/>
-      <c r="M187" s="59"/>
-      <c r="N187" s="59"/>
-      <c r="O187" s="59"/>
-      <c r="P187" s="59"/>
-      <c r="Q187" s="59"/>
-      <c r="R187" s="59"/>
-      <c r="S187" s="59"/>
-      <c r="T187" s="59"/>
-      <c r="U187" s="52"/>
+      <c r="H187" s="39"/>
+      <c r="I187" s="40"/>
+      <c r="J187" s="40"/>
+      <c r="K187" s="40"/>
+      <c r="L187" s="40"/>
+      <c r="M187" s="40"/>
+      <c r="N187" s="40"/>
+      <c r="O187" s="40"/>
+      <c r="P187" s="40"/>
+      <c r="Q187" s="40"/>
+      <c r="R187" s="40"/>
+      <c r="S187" s="40"/>
+      <c r="T187" s="40"/>
+      <c r="U187" s="41"/>
     </row>
     <row r="188" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" s="30"/>
@@ -15176,20 +15181,20 @@
       <c r="E188" s="31"/>
       <c r="F188" s="31"/>
       <c r="G188" s="31"/>
-      <c r="H188" s="51"/>
-      <c r="I188" s="59"/>
-      <c r="J188" s="59"/>
-      <c r="K188" s="59"/>
-      <c r="L188" s="59"/>
-      <c r="M188" s="59"/>
-      <c r="N188" s="59"/>
-      <c r="O188" s="59"/>
-      <c r="P188" s="59"/>
-      <c r="Q188" s="59"/>
-      <c r="R188" s="59"/>
-      <c r="S188" s="59"/>
-      <c r="T188" s="59"/>
-      <c r="U188" s="52"/>
+      <c r="H188" s="39"/>
+      <c r="I188" s="40"/>
+      <c r="J188" s="40"/>
+      <c r="K188" s="40"/>
+      <c r="L188" s="40"/>
+      <c r="M188" s="40"/>
+      <c r="N188" s="40"/>
+      <c r="O188" s="40"/>
+      <c r="P188" s="40"/>
+      <c r="Q188" s="40"/>
+      <c r="R188" s="40"/>
+      <c r="S188" s="40"/>
+      <c r="T188" s="40"/>
+      <c r="U188" s="41"/>
     </row>
     <row r="189" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A189" s="30"/>
@@ -15205,20 +15210,20 @@
       <c r="E189" s="31"/>
       <c r="F189" s="31"/>
       <c r="G189" s="31"/>
-      <c r="H189" s="51"/>
-      <c r="I189" s="59"/>
-      <c r="J189" s="59"/>
-      <c r="K189" s="59"/>
-      <c r="L189" s="59"/>
-      <c r="M189" s="59"/>
-      <c r="N189" s="59"/>
-      <c r="O189" s="59"/>
-      <c r="P189" s="59"/>
-      <c r="Q189" s="59"/>
-      <c r="R189" s="59"/>
-      <c r="S189" s="59"/>
-      <c r="T189" s="59"/>
-      <c r="U189" s="52"/>
+      <c r="H189" s="39"/>
+      <c r="I189" s="40"/>
+      <c r="J189" s="40"/>
+      <c r="K189" s="40"/>
+      <c r="L189" s="40"/>
+      <c r="M189" s="40"/>
+      <c r="N189" s="40"/>
+      <c r="O189" s="40"/>
+      <c r="P189" s="40"/>
+      <c r="Q189" s="40"/>
+      <c r="R189" s="40"/>
+      <c r="S189" s="40"/>
+      <c r="T189" s="40"/>
+      <c r="U189" s="41"/>
     </row>
     <row r="190" spans="1:35" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A190" s="30"/>
@@ -15234,20 +15239,20 @@
       <c r="E190" s="31"/>
       <c r="F190" s="31"/>
       <c r="G190" s="31"/>
-      <c r="H190" s="51"/>
-      <c r="I190" s="59"/>
-      <c r="J190" s="59"/>
-      <c r="K190" s="59"/>
-      <c r="L190" s="59"/>
-      <c r="M190" s="59"/>
-      <c r="N190" s="59"/>
-      <c r="O190" s="59"/>
-      <c r="P190" s="59"/>
-      <c r="Q190" s="59"/>
-      <c r="R190" s="59"/>
-      <c r="S190" s="59"/>
-      <c r="T190" s="59"/>
-      <c r="U190" s="52"/>
+      <c r="H190" s="39"/>
+      <c r="I190" s="40"/>
+      <c r="J190" s="40"/>
+      <c r="K190" s="40"/>
+      <c r="L190" s="40"/>
+      <c r="M190" s="40"/>
+      <c r="N190" s="40"/>
+      <c r="O190" s="40"/>
+      <c r="P190" s="40"/>
+      <c r="Q190" s="40"/>
+      <c r="R190" s="40"/>
+      <c r="S190" s="40"/>
+      <c r="T190" s="40"/>
+      <c r="U190" s="41"/>
     </row>
     <row r="191" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A191" s="30"/>
@@ -15263,20 +15268,20 @@
       <c r="E191" s="31"/>
       <c r="F191" s="31"/>
       <c r="G191" s="31"/>
-      <c r="H191" s="51"/>
-      <c r="I191" s="59"/>
-      <c r="J191" s="59"/>
-      <c r="K191" s="59"/>
-      <c r="L191" s="59"/>
-      <c r="M191" s="59"/>
-      <c r="N191" s="59"/>
-      <c r="O191" s="59"/>
-      <c r="P191" s="59"/>
-      <c r="Q191" s="59"/>
-      <c r="R191" s="59"/>
-      <c r="S191" s="59"/>
-      <c r="T191" s="59"/>
-      <c r="U191" s="52"/>
+      <c r="H191" s="39"/>
+      <c r="I191" s="40"/>
+      <c r="J191" s="40"/>
+      <c r="K191" s="40"/>
+      <c r="L191" s="40"/>
+      <c r="M191" s="40"/>
+      <c r="N191" s="40"/>
+      <c r="O191" s="40"/>
+      <c r="P191" s="40"/>
+      <c r="Q191" s="40"/>
+      <c r="R191" s="40"/>
+      <c r="S191" s="40"/>
+      <c r="T191" s="40"/>
+      <c r="U191" s="41"/>
     </row>
     <row r="192" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" s="30"/>
@@ -15292,20 +15297,20 @@
       <c r="E192" s="31"/>
       <c r="F192" s="31"/>
       <c r="G192" s="31"/>
-      <c r="H192" s="51"/>
-      <c r="I192" s="59"/>
-      <c r="J192" s="59"/>
-      <c r="K192" s="59"/>
-      <c r="L192" s="59"/>
-      <c r="M192" s="59"/>
-      <c r="N192" s="59"/>
-      <c r="O192" s="59"/>
-      <c r="P192" s="59"/>
-      <c r="Q192" s="59"/>
-      <c r="R192" s="59"/>
-      <c r="S192" s="59"/>
-      <c r="T192" s="59"/>
-      <c r="U192" s="52"/>
+      <c r="H192" s="39"/>
+      <c r="I192" s="40"/>
+      <c r="J192" s="40"/>
+      <c r="K192" s="40"/>
+      <c r="L192" s="40"/>
+      <c r="M192" s="40"/>
+      <c r="N192" s="40"/>
+      <c r="O192" s="40"/>
+      <c r="P192" s="40"/>
+      <c r="Q192" s="40"/>
+      <c r="R192" s="40"/>
+      <c r="S192" s="40"/>
+      <c r="T192" s="40"/>
+      <c r="U192" s="41"/>
     </row>
     <row r="193" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="30"/>
@@ -15321,22 +15326,22 @@
       <c r="E193" s="31"/>
       <c r="F193" s="31"/>
       <c r="G193" s="31"/>
-      <c r="H193" s="51" t="s">
+      <c r="H193" s="39" t="s">
         <v>770</v>
       </c>
-      <c r="I193" s="59"/>
-      <c r="J193" s="59"/>
-      <c r="K193" s="59"/>
-      <c r="L193" s="59"/>
-      <c r="M193" s="59"/>
-      <c r="N193" s="59"/>
-      <c r="O193" s="59"/>
-      <c r="P193" s="59"/>
-      <c r="Q193" s="59"/>
-      <c r="R193" s="59"/>
-      <c r="S193" s="59"/>
-      <c r="T193" s="59"/>
-      <c r="U193" s="52"/>
+      <c r="I193" s="40"/>
+      <c r="J193" s="40"/>
+      <c r="K193" s="40"/>
+      <c r="L193" s="40"/>
+      <c r="M193" s="40"/>
+      <c r="N193" s="40"/>
+      <c r="O193" s="40"/>
+      <c r="P193" s="40"/>
+      <c r="Q193" s="40"/>
+      <c r="R193" s="40"/>
+      <c r="S193" s="40"/>
+      <c r="T193" s="40"/>
+      <c r="U193" s="41"/>
     </row>
     <row r="194" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" s="30"/>
@@ -15352,20 +15357,20 @@
       <c r="E194" s="31"/>
       <c r="F194" s="31"/>
       <c r="G194" s="31"/>
-      <c r="H194" s="51"/>
-      <c r="I194" s="59"/>
-      <c r="J194" s="59"/>
-      <c r="K194" s="59"/>
-      <c r="L194" s="59"/>
-      <c r="M194" s="59"/>
-      <c r="N194" s="59"/>
-      <c r="O194" s="59"/>
-      <c r="P194" s="59"/>
-      <c r="Q194" s="59"/>
-      <c r="R194" s="59"/>
-      <c r="S194" s="59"/>
-      <c r="T194" s="59"/>
-      <c r="U194" s="52"/>
+      <c r="H194" s="39"/>
+      <c r="I194" s="40"/>
+      <c r="J194" s="40"/>
+      <c r="K194" s="40"/>
+      <c r="L194" s="40"/>
+      <c r="M194" s="40"/>
+      <c r="N194" s="40"/>
+      <c r="O194" s="40"/>
+      <c r="P194" s="40"/>
+      <c r="Q194" s="40"/>
+      <c r="R194" s="40"/>
+      <c r="S194" s="40"/>
+      <c r="T194" s="40"/>
+      <c r="U194" s="41"/>
     </row>
     <row r="195" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A195" s="30"/>
@@ -15379,20 +15384,20 @@
       <c r="E195" s="31"/>
       <c r="F195" s="31"/>
       <c r="G195" s="31"/>
-      <c r="H195" s="51"/>
-      <c r="I195" s="59"/>
-      <c r="J195" s="59"/>
-      <c r="K195" s="59"/>
-      <c r="L195" s="59"/>
-      <c r="M195" s="59"/>
-      <c r="N195" s="59"/>
-      <c r="O195" s="59"/>
-      <c r="P195" s="59"/>
-      <c r="Q195" s="59"/>
-      <c r="R195" s="59"/>
-      <c r="S195" s="59"/>
-      <c r="T195" s="59"/>
-      <c r="U195" s="52"/>
+      <c r="H195" s="39"/>
+      <c r="I195" s="40"/>
+      <c r="J195" s="40"/>
+      <c r="K195" s="40"/>
+      <c r="L195" s="40"/>
+      <c r="M195" s="40"/>
+      <c r="N195" s="40"/>
+      <c r="O195" s="40"/>
+      <c r="P195" s="40"/>
+      <c r="Q195" s="40"/>
+      <c r="R195" s="40"/>
+      <c r="S195" s="40"/>
+      <c r="T195" s="40"/>
+      <c r="U195" s="41"/>
     </row>
     <row r="196" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" s="30"/>
@@ -15406,20 +15411,20 @@
       <c r="E196" s="31"/>
       <c r="F196" s="31"/>
       <c r="G196" s="31"/>
-      <c r="H196" s="51"/>
-      <c r="I196" s="59"/>
-      <c r="J196" s="59"/>
-      <c r="K196" s="59"/>
-      <c r="L196" s="59"/>
-      <c r="M196" s="59"/>
-      <c r="N196" s="59"/>
-      <c r="O196" s="59"/>
-      <c r="P196" s="59"/>
-      <c r="Q196" s="59"/>
-      <c r="R196" s="59"/>
-      <c r="S196" s="59"/>
-      <c r="T196" s="59"/>
-      <c r="U196" s="52"/>
+      <c r="H196" s="39"/>
+      <c r="I196" s="40"/>
+      <c r="J196" s="40"/>
+      <c r="K196" s="40"/>
+      <c r="L196" s="40"/>
+      <c r="M196" s="40"/>
+      <c r="N196" s="40"/>
+      <c r="O196" s="40"/>
+      <c r="P196" s="40"/>
+      <c r="Q196" s="40"/>
+      <c r="R196" s="40"/>
+      <c r="S196" s="40"/>
+      <c r="T196" s="40"/>
+      <c r="U196" s="41"/>
     </row>
     <row r="197" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" s="30"/>
@@ -15433,68 +15438,25 @@
       <c r="E197" s="31"/>
       <c r="F197" s="31"/>
       <c r="G197" s="31"/>
-      <c r="H197" s="51"/>
-      <c r="I197" s="59"/>
-      <c r="J197" s="59"/>
-      <c r="K197" s="59"/>
-      <c r="L197" s="59"/>
-      <c r="M197" s="59"/>
-      <c r="N197" s="59"/>
-      <c r="O197" s="59"/>
-      <c r="P197" s="59"/>
-      <c r="Q197" s="59"/>
-      <c r="R197" s="59"/>
-      <c r="S197" s="59"/>
-      <c r="T197" s="59"/>
-      <c r="U197" s="52"/>
+      <c r="H197" s="39"/>
+      <c r="I197" s="40"/>
+      <c r="J197" s="40"/>
+      <c r="K197" s="40"/>
+      <c r="L197" s="40"/>
+      <c r="M197" s="40"/>
+      <c r="N197" s="40"/>
+      <c r="O197" s="40"/>
+      <c r="P197" s="40"/>
+      <c r="Q197" s="40"/>
+      <c r="R197" s="40"/>
+      <c r="S197" s="40"/>
+      <c r="T197" s="40"/>
+      <c r="U197" s="41"/>
     </row>
   </sheetData>
   <sheetProtection password="C644" sheet="1" formatColumns="0" autoFilter="0"/>
   <autoFilter ref="A7:U7"/>
   <mergeCells count="59">
-    <mergeCell ref="H195:U195"/>
-    <mergeCell ref="H196:U196"/>
-    <mergeCell ref="H197:U197"/>
-    <mergeCell ref="H190:U190"/>
-    <mergeCell ref="H191:U191"/>
-    <mergeCell ref="H192:U192"/>
-    <mergeCell ref="H193:U193"/>
-    <mergeCell ref="H194:U194"/>
-    <mergeCell ref="H185:U185"/>
-    <mergeCell ref="H186:U186"/>
-    <mergeCell ref="H187:U187"/>
-    <mergeCell ref="H188:U188"/>
-    <mergeCell ref="H189:U189"/>
-    <mergeCell ref="H180:U180"/>
-    <mergeCell ref="H181:U181"/>
-    <mergeCell ref="H182:U182"/>
-    <mergeCell ref="H183:U183"/>
-    <mergeCell ref="H184:U184"/>
-    <mergeCell ref="C148:I148"/>
-    <mergeCell ref="C149:I149"/>
-    <mergeCell ref="C153:I153"/>
-    <mergeCell ref="C169:I169"/>
-    <mergeCell ref="A179:U179"/>
-    <mergeCell ref="C45:I45"/>
-    <mergeCell ref="C66:I66"/>
-    <mergeCell ref="C67:I67"/>
-    <mergeCell ref="C97:I97"/>
-    <mergeCell ref="C128:I128"/>
-    <mergeCell ref="C11:I11"/>
-    <mergeCell ref="C12:I12"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="C14:I14"/>
-    <mergeCell ref="C37:I37"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="U6:U7"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="O6:O7"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="R6:R7"/>
     <mergeCell ref="A2:U2"/>
     <mergeCell ref="A3:U3"/>
     <mergeCell ref="A4:U4"/>
@@ -15511,6 +15473,49 @@
     <mergeCell ref="H5:H7"/>
     <mergeCell ref="I5:I7"/>
     <mergeCell ref="J6:K6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="R6:R7"/>
+    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="C12:I12"/>
+    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="C37:I37"/>
+    <mergeCell ref="C45:I45"/>
+    <mergeCell ref="C66:I66"/>
+    <mergeCell ref="C67:I67"/>
+    <mergeCell ref="C97:I97"/>
+    <mergeCell ref="C128:I128"/>
+    <mergeCell ref="C148:I148"/>
+    <mergeCell ref="C149:I149"/>
+    <mergeCell ref="C153:I153"/>
+    <mergeCell ref="C169:I169"/>
+    <mergeCell ref="A179:U179"/>
+    <mergeCell ref="H180:U180"/>
+    <mergeCell ref="H181:U181"/>
+    <mergeCell ref="H182:U182"/>
+    <mergeCell ref="H183:U183"/>
+    <mergeCell ref="H184:U184"/>
+    <mergeCell ref="H185:U185"/>
+    <mergeCell ref="H186:U186"/>
+    <mergeCell ref="H187:U187"/>
+    <mergeCell ref="H188:U188"/>
+    <mergeCell ref="H189:U189"/>
+    <mergeCell ref="H195:U195"/>
+    <mergeCell ref="H196:U196"/>
+    <mergeCell ref="H197:U197"/>
+    <mergeCell ref="H190:U190"/>
+    <mergeCell ref="H191:U191"/>
+    <mergeCell ref="H192:U192"/>
+    <mergeCell ref="H193:U193"/>
+    <mergeCell ref="H194:U194"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15600,79 +15605,79 @@
       </c>
     </row>
     <row r="2" spans="1:35" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
-      <c r="O2" s="39"/>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
-      <c r="T2" s="39"/>
-      <c r="U2" s="39"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="50"/>
+      <c r="P2" s="50"/>
+      <c r="Q2" s="50"/>
+      <c r="R2" s="50"/>
+      <c r="S2" s="50"/>
+      <c r="T2" s="50"/>
+      <c r="U2" s="50"/>
     </row>
     <row r="3" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40"/>
-      <c r="S3" s="40"/>
-      <c r="T3" s="40"/>
-      <c r="U3" s="40"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="51"/>
+      <c r="O3" s="51"/>
+      <c r="P3" s="51"/>
+      <c r="Q3" s="51"/>
+      <c r="R3" s="51"/>
+      <c r="S3" s="51"/>
+      <c r="T3" s="51"/>
+      <c r="U3" s="51"/>
     </row>
     <row r="4" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="41"/>
-      <c r="N4" s="41"/>
-      <c r="O4" s="41"/>
-      <c r="P4" s="41"/>
-      <c r="Q4" s="41"/>
-      <c r="R4" s="41"/>
-      <c r="S4" s="41"/>
-      <c r="T4" s="41"/>
-      <c r="U4" s="41"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="52"/>
+      <c r="M4" s="52"/>
+      <c r="N4" s="52"/>
+      <c r="O4" s="52"/>
+      <c r="P4" s="52"/>
+      <c r="Q4" s="52"/>
+      <c r="R4" s="52"/>
+      <c r="S4" s="52"/>
+      <c r="T4" s="52"/>
+      <c r="U4" s="52"/>
     </row>
     <row r="5" spans="1:35" ht="40.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="48" t="s">
@@ -15702,115 +15707,115 @@
       <c r="I5" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J5" s="42" t="s">
+      <c r="J5" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="43"/>
-      <c r="L5" s="43"/>
-      <c r="M5" s="43"/>
-      <c r="N5" s="43"/>
-      <c r="O5" s="44"/>
-      <c r="P5" s="45" t="s">
+      <c r="K5" s="54"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="54"/>
+      <c r="N5" s="54"/>
+      <c r="O5" s="55"/>
+      <c r="P5" s="56" t="s">
         <v>780</v>
       </c>
-      <c r="Q5" s="46"/>
-      <c r="R5" s="47"/>
-      <c r="S5" s="45">
+      <c r="Q5" s="57"/>
+      <c r="R5" s="58"/>
+      <c r="S5" s="56">
         <v>9701212867</v>
       </c>
-      <c r="T5" s="46"/>
-      <c r="U5" s="47"/>
+      <c r="T5" s="57"/>
+      <c r="U5" s="58"/>
     </row>
     <row r="6" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="49"/>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="51" t="s">
+      <c r="A6" s="59"/>
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="52"/>
+      <c r="K6" s="41"/>
       <c r="L6" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="M6" s="51" t="s">
+      <c r="M6" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="N6" s="52"/>
+      <c r="N6" s="41"/>
       <c r="O6" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="P6" s="51" t="s">
+      <c r="P6" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="Q6" s="52"/>
+      <c r="Q6" s="41"/>
       <c r="R6" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="S6" s="51" t="s">
+      <c r="S6" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="T6" s="52"/>
+      <c r="T6" s="41"/>
       <c r="U6" s="48" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:35" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="50"/>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="50"/>
-      <c r="I7" s="50"/>
+      <c r="A7" s="49"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
       <c r="J7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L7" s="50"/>
+      <c r="L7" s="49"/>
       <c r="M7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="O7" s="50"/>
+      <c r="O7" s="49"/>
       <c r="P7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="R7" s="50"/>
+      <c r="R7" s="49"/>
       <c r="S7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="T7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="U7" s="50"/>
+      <c r="U7" s="49"/>
     </row>
     <row r="8" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="55"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="47"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -15864,15 +15869,15 @@
       <c r="B9" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="56" t="s">
+      <c r="C9" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="58"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="44"/>
       <c r="M9" s="6">
         <f t="shared" si="0"/>
         <v>21909487.239999998</v>
@@ -15923,15 +15928,15 @@
       <c r="B10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="56" t="s">
+      <c r="C10" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="58"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="44"/>
       <c r="M10" s="6">
         <f t="shared" si="0"/>
         <v>21909487.239999998</v>
@@ -15982,15 +15987,15 @@
       <c r="B11" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="56" t="s">
+      <c r="C11" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="58"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="44"/>
       <c r="M11" s="6">
         <f t="shared" si="0"/>
         <v>21909487.239999998</v>
@@ -16041,15 +16046,15 @@
       <c r="B12" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="56" t="s">
+      <c r="C12" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="58"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="44"/>
       <c r="M12" s="6">
         <f>SUM(M13,M66,M148,M169)</f>
         <v>21909487.239999998</v>
@@ -16100,15 +16105,15 @@
       <c r="B13" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="56" t="s">
+      <c r="C13" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="58"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="44"/>
       <c r="M13" s="6">
         <f>SUM(M14,M37,M45)</f>
         <v>3561291.31</v>
@@ -16159,15 +16164,15 @@
       <c r="B14" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="56" t="s">
+      <c r="C14" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="58"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="44"/>
       <c r="M14" s="6">
         <f>SUM(M15,M19,M21,M29)</f>
         <v>2618573.91</v>
@@ -16641,7 +16646,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="21" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>87</v>
       </c>
@@ -16915,10 +16920,10 @@
       <c r="C25" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="D25" s="60" t="s">
+      <c r="D25" s="62" t="s">
         <v>781</v>
       </c>
-      <c r="E25" s="62" t="s">
+      <c r="E25" s="60" t="s">
         <v>784</v>
       </c>
       <c r="F25" s="18" t="s">
@@ -16971,8 +16976,8 @@
       <c r="C26" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="D26" s="61"/>
-      <c r="E26" s="63"/>
+      <c r="D26" s="63"/>
+      <c r="E26" s="61"/>
       <c r="F26" s="18" t="s">
         <v>79</v>
       </c>
@@ -17119,7 +17124,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>125</v>
       </c>
@@ -17399,10 +17404,10 @@
       <c r="C33" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="D33" s="60" t="s">
+      <c r="D33" s="62" t="s">
         <v>781</v>
       </c>
-      <c r="E33" s="62" t="s">
+      <c r="E33" s="60" t="s">
         <v>784</v>
       </c>
       <c r="F33" s="18" t="s">
@@ -17458,8 +17463,8 @@
       <c r="C34" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="D34" s="61"/>
-      <c r="E34" s="63"/>
+      <c r="D34" s="63"/>
+      <c r="E34" s="61"/>
       <c r="F34" s="18" t="s">
         <v>79</v>
       </c>
@@ -17616,15 +17621,15 @@
       <c r="B37" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="C37" s="56" t="s">
+      <c r="C37" s="42" t="s">
         <v>154</v>
       </c>
-      <c r="D37" s="57"/>
-      <c r="E37" s="57"/>
-      <c r="F37" s="57"/>
-      <c r="G37" s="57"/>
-      <c r="H37" s="57"/>
-      <c r="I37" s="58"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="43"/>
+      <c r="I37" s="44"/>
       <c r="M37" s="6">
         <f>SUM(M38,M41,M43)</f>
         <v>122933.90000000001</v>
@@ -17988,7 +17993,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="42" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
         <v>175</v>
       </c>
@@ -18209,15 +18214,15 @@
       <c r="B45" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="C45" s="56" t="s">
+      <c r="C45" s="42" t="s">
         <v>193</v>
       </c>
-      <c r="D45" s="57"/>
-      <c r="E45" s="57"/>
-      <c r="F45" s="57"/>
-      <c r="G45" s="57"/>
-      <c r="H45" s="57"/>
-      <c r="I45" s="58"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="43"/>
+      <c r="G45" s="43"/>
+      <c r="H45" s="43"/>
+      <c r="I45" s="44"/>
       <c r="M45" s="6">
         <f>SUM(M46,M51,M55,M60,M63)</f>
         <v>819783.5</v>
@@ -18261,7 +18266,7 @@
         <v>17909368</v>
       </c>
     </row>
-    <row r="46" spans="1:35" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
         <v>194</v>
       </c>
@@ -18371,7 +18376,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="47" spans="1:35" ht="93.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>200</v>
       </c>
@@ -18425,7 +18430,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="48" spans="1:35" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
         <v>206</v>
       </c>
@@ -18531,7 +18536,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="50" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
         <v>216</v>
       </c>
@@ -18691,7 +18696,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="52" spans="1:35" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
         <v>226</v>
       </c>
@@ -18745,7 +18750,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="53" spans="1:35" ht="93.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>232</v>
       </c>
@@ -18799,7 +18804,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="54" spans="1:35" ht="93.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
         <v>238</v>
       </c>
@@ -18961,7 +18966,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="56" spans="1:35" ht="150" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
         <v>249</v>
       </c>
@@ -19015,7 +19020,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="57" spans="1:35" ht="93.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
         <v>255</v>
       </c>
@@ -19124,7 +19129,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="59" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
         <v>263</v>
       </c>
@@ -19284,7 +19289,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="61" spans="1:35" ht="93.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
         <v>271</v>
       </c>
@@ -19338,7 +19343,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="62" spans="1:35" ht="93.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
         <v>277</v>
       </c>
@@ -19500,7 +19505,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="64" spans="1:35" ht="131.25" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
         <v>285</v>
       </c>
@@ -19554,7 +19559,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="65" spans="1:35" ht="168.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:35" ht="93.75" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
         <v>291</v>
       </c>
@@ -19615,15 +19620,15 @@
       <c r="B66" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="C66" s="56" t="s">
+      <c r="C66" s="42" t="s">
         <v>299</v>
       </c>
-      <c r="D66" s="57"/>
-      <c r="E66" s="57"/>
-      <c r="F66" s="57"/>
-      <c r="G66" s="57"/>
-      <c r="H66" s="57"/>
-      <c r="I66" s="58"/>
+      <c r="D66" s="43"/>
+      <c r="E66" s="43"/>
+      <c r="F66" s="43"/>
+      <c r="G66" s="43"/>
+      <c r="H66" s="43"/>
+      <c r="I66" s="44"/>
       <c r="M66" s="6">
         <f>SUM(M67,M97,M128)</f>
         <v>4332566.72</v>
@@ -19674,15 +19679,15 @@
       <c r="B67" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="C67" s="56" t="s">
+      <c r="C67" s="42" t="s">
         <v>302</v>
       </c>
-      <c r="D67" s="57"/>
-      <c r="E67" s="57"/>
-      <c r="F67" s="57"/>
-      <c r="G67" s="57"/>
-      <c r="H67" s="57"/>
-      <c r="I67" s="58"/>
+      <c r="D67" s="43"/>
+      <c r="E67" s="43"/>
+      <c r="F67" s="43"/>
+      <c r="G67" s="43"/>
+      <c r="H67" s="43"/>
+      <c r="I67" s="44"/>
       <c r="M67" s="6">
         <f>SUM(M68,M71,M75,M79,M82,M85,M89,M92)</f>
         <v>2963619.5900000003</v>
@@ -20152,7 +20157,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="74" spans="1:35" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
         <v>334</v>
       </c>
@@ -20321,7 +20326,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="76" spans="1:35" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A76" s="10" t="s">
         <v>340</v>
       </c>
@@ -20380,7 +20385,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="77" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A77" s="10" t="s">
         <v>343</v>
       </c>
@@ -20646,7 +20651,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="81" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A81" s="10" t="s">
         <v>360</v>
       </c>
@@ -20808,7 +20813,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="83" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A83" s="10" t="s">
         <v>365</v>
       </c>
@@ -21022,7 +21027,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="86" spans="1:35" ht="93.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A86" s="10" t="s">
         <v>376</v>
       </c>
@@ -21128,7 +21133,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="88" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
         <v>386</v>
       </c>
@@ -21290,7 +21295,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="90" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A90" s="10" t="s">
         <v>390</v>
       </c>
@@ -21502,7 +21507,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="93" spans="1:35" ht="75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A93" s="10" t="s">
         <v>401</v>
       </c>
@@ -21561,7 +21566,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="94" spans="1:35" ht="150" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:35" ht="93.75" x14ac:dyDescent="0.25">
       <c r="A94" s="10" t="s">
         <v>407</v>
       </c>
@@ -21728,15 +21733,15 @@
       <c r="B97" s="10" t="s">
         <v>419</v>
       </c>
-      <c r="C97" s="56" t="s">
+      <c r="C97" s="42" t="s">
         <v>420</v>
       </c>
-      <c r="D97" s="57"/>
-      <c r="E97" s="57"/>
-      <c r="F97" s="57"/>
-      <c r="G97" s="57"/>
-      <c r="H97" s="57"/>
-      <c r="I97" s="58"/>
+      <c r="D97" s="43"/>
+      <c r="E97" s="43"/>
+      <c r="F97" s="43"/>
+      <c r="G97" s="43"/>
+      <c r="H97" s="43"/>
+      <c r="I97" s="44"/>
       <c r="M97" s="6">
         <f>SUM(M98,M107,M110,M113,M116,M119,M122,M125)</f>
         <v>1187256.6599999997</v>
@@ -22096,7 +22101,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="103" spans="1:35" ht="93.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A103" s="10" t="s">
         <v>446</v>
       </c>
@@ -22150,7 +22155,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="104" spans="1:35" ht="93.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A104" s="10" t="s">
         <v>452</v>
       </c>
@@ -22256,7 +22261,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="106" spans="1:35" ht="93.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A106" s="10" t="s">
         <v>461</v>
       </c>
@@ -22470,7 +22475,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="109" spans="1:35" ht="168.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:35" ht="93.75" x14ac:dyDescent="0.25">
       <c r="A109" s="10" t="s">
         <v>475</v>
       </c>
@@ -22632,7 +22637,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="111" spans="1:35" ht="168.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:35" ht="93.75" x14ac:dyDescent="0.25">
       <c r="A111" s="10" t="s">
         <v>482</v>
       </c>
@@ -22898,7 +22903,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="115" spans="1:35" ht="93.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A115" s="10" t="s">
         <v>495</v>
       </c>
@@ -23060,7 +23065,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="117" spans="1:35" ht="187.5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:35" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A117" s="10" t="s">
         <v>502</v>
       </c>
@@ -23326,7 +23331,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="121" spans="1:35" ht="187.5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:35" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A121" s="10" t="s">
         <v>513</v>
       </c>
@@ -23488,7 +23493,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="123" spans="1:35" ht="168.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:35" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A123" s="10" t="s">
         <v>518</v>
       </c>
@@ -23754,7 +23759,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="127" spans="1:35" ht="187.5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:35" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A127" s="10" t="s">
         <v>529</v>
       </c>
@@ -23815,15 +23820,15 @@
       <c r="B128" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="C128" s="56" t="s">
+      <c r="C128" s="42" t="s">
         <v>534</v>
       </c>
-      <c r="D128" s="57"/>
-      <c r="E128" s="57"/>
-      <c r="F128" s="57"/>
-      <c r="G128" s="57"/>
-      <c r="H128" s="57"/>
-      <c r="I128" s="58"/>
+      <c r="D128" s="43"/>
+      <c r="E128" s="43"/>
+      <c r="F128" s="43"/>
+      <c r="G128" s="43"/>
+      <c r="H128" s="43"/>
+      <c r="I128" s="44"/>
       <c r="M128" s="6">
         <f>SUM(M129,M132,M135,M138,M143)</f>
         <v>181690.47</v>
@@ -23867,7 +23872,7 @@
         <v>17922383</v>
       </c>
     </row>
-    <row r="129" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A129" s="10" t="s">
         <v>535</v>
       </c>
@@ -24081,7 +24086,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="132" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A132" s="10" t="s">
         <v>547</v>
       </c>
@@ -25146,15 +25151,15 @@
       <c r="B148" s="10" t="s">
         <v>616</v>
       </c>
-      <c r="C148" s="56" t="s">
+      <c r="C148" s="42" t="s">
         <v>617</v>
       </c>
-      <c r="D148" s="57"/>
-      <c r="E148" s="57"/>
-      <c r="F148" s="57"/>
-      <c r="G148" s="57"/>
-      <c r="H148" s="57"/>
-      <c r="I148" s="58"/>
+      <c r="D148" s="43"/>
+      <c r="E148" s="43"/>
+      <c r="F148" s="43"/>
+      <c r="G148" s="43"/>
+      <c r="H148" s="43"/>
+      <c r="I148" s="44"/>
       <c r="M148" s="6">
         <f>SUM(M149,M153)</f>
         <v>447303.98</v>
@@ -25205,15 +25210,15 @@
       <c r="B149" s="10" t="s">
         <v>619</v>
       </c>
-      <c r="C149" s="56" t="s">
+      <c r="C149" s="42" t="s">
         <v>620</v>
       </c>
-      <c r="D149" s="57"/>
-      <c r="E149" s="57"/>
-      <c r="F149" s="57"/>
-      <c r="G149" s="57"/>
-      <c r="H149" s="57"/>
-      <c r="I149" s="58"/>
+      <c r="D149" s="43"/>
+      <c r="E149" s="43"/>
+      <c r="F149" s="43"/>
+      <c r="G149" s="43"/>
+      <c r="H149" s="43"/>
+      <c r="I149" s="44"/>
       <c r="M149" s="6">
         <f>SUM(M150)</f>
         <v>241468.92</v>
@@ -25476,15 +25481,15 @@
       <c r="B153" s="10" t="s">
         <v>635</v>
       </c>
-      <c r="C153" s="56" t="s">
+      <c r="C153" s="42" t="s">
         <v>636</v>
       </c>
-      <c r="D153" s="57"/>
-      <c r="E153" s="57"/>
-      <c r="F153" s="57"/>
-      <c r="G153" s="57"/>
-      <c r="H153" s="57"/>
-      <c r="I153" s="58"/>
+      <c r="D153" s="43"/>
+      <c r="E153" s="43"/>
+      <c r="F153" s="43"/>
+      <c r="G153" s="43"/>
+      <c r="H153" s="43"/>
+      <c r="I153" s="44"/>
       <c r="M153" s="6">
         <f>SUM(M154,M157,M160,M163,M166)</f>
         <v>205835.06</v>
@@ -25528,7 +25533,7 @@
         <v>17928898</v>
       </c>
     </row>
-    <row r="154" spans="1:35" ht="93.75" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A154" s="10" t="s">
         <v>637</v>
       </c>
@@ -25638,7 +25643,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="155" spans="1:35" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A155" s="10" t="s">
         <v>643</v>
       </c>
@@ -25904,7 +25909,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="159" spans="1:35" ht="131.25" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:35" ht="93.75" x14ac:dyDescent="0.25">
       <c r="A159" s="10" t="s">
         <v>654</v>
       </c>
@@ -26066,7 +26071,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="161" spans="1:35" ht="93.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A161" s="10" t="s">
         <v>659</v>
       </c>
@@ -26607,15 +26612,15 @@
       <c r="B169" s="10" t="s">
         <v>683</v>
       </c>
-      <c r="C169" s="56" t="s">
+      <c r="C169" s="42" t="s">
         <v>684</v>
       </c>
-      <c r="D169" s="57"/>
-      <c r="E169" s="57"/>
-      <c r="F169" s="57"/>
-      <c r="G169" s="57"/>
-      <c r="H169" s="57"/>
-      <c r="I169" s="58"/>
+      <c r="D169" s="43"/>
+      <c r="E169" s="43"/>
+      <c r="F169" s="43"/>
+      <c r="G169" s="43"/>
+      <c r="H169" s="43"/>
+      <c r="I169" s="44"/>
       <c r="M169" s="6">
         <f>SUM(M170,M173,M177)</f>
         <v>13568325.229999999</v>
@@ -27293,29 +27298,29 @@
       </c>
     </row>
     <row r="179" spans="1:35" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A179" s="53" t="s">
+      <c r="A179" s="45" t="s">
         <v>728</v>
       </c>
-      <c r="B179" s="54"/>
-      <c r="C179" s="54"/>
-      <c r="D179" s="54"/>
-      <c r="E179" s="54"/>
-      <c r="F179" s="54"/>
-      <c r="G179" s="54"/>
-      <c r="H179" s="54"/>
-      <c r="I179" s="54"/>
-      <c r="J179" s="54"/>
-      <c r="K179" s="54"/>
-      <c r="L179" s="54"/>
-      <c r="M179" s="54"/>
-      <c r="N179" s="54"/>
-      <c r="O179" s="54"/>
-      <c r="P179" s="54"/>
-      <c r="Q179" s="54"/>
-      <c r="R179" s="54"/>
-      <c r="S179" s="54"/>
-      <c r="T179" s="54"/>
-      <c r="U179" s="55"/>
+      <c r="B179" s="46"/>
+      <c r="C179" s="46"/>
+      <c r="D179" s="46"/>
+      <c r="E179" s="46"/>
+      <c r="F179" s="46"/>
+      <c r="G179" s="46"/>
+      <c r="H179" s="46"/>
+      <c r="I179" s="46"/>
+      <c r="J179" s="46"/>
+      <c r="K179" s="46"/>
+      <c r="L179" s="46"/>
+      <c r="M179" s="46"/>
+      <c r="N179" s="46"/>
+      <c r="O179" s="46"/>
+      <c r="P179" s="46"/>
+      <c r="Q179" s="46"/>
+      <c r="R179" s="46"/>
+      <c r="S179" s="46"/>
+      <c r="T179" s="46"/>
+      <c r="U179" s="47"/>
     </row>
     <row r="180" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="30"/>
@@ -27331,20 +27336,20 @@
       <c r="E180" s="31"/>
       <c r="F180" s="31"/>
       <c r="G180" s="31"/>
-      <c r="H180" s="51"/>
-      <c r="I180" s="59"/>
-      <c r="J180" s="59"/>
-      <c r="K180" s="59"/>
-      <c r="L180" s="59"/>
-      <c r="M180" s="59"/>
-      <c r="N180" s="59"/>
-      <c r="O180" s="59"/>
-      <c r="P180" s="59"/>
-      <c r="Q180" s="59"/>
-      <c r="R180" s="59"/>
-      <c r="S180" s="59"/>
-      <c r="T180" s="59"/>
-      <c r="U180" s="52"/>
+      <c r="H180" s="39"/>
+      <c r="I180" s="40"/>
+      <c r="J180" s="40"/>
+      <c r="K180" s="40"/>
+      <c r="L180" s="40"/>
+      <c r="M180" s="40"/>
+      <c r="N180" s="40"/>
+      <c r="O180" s="40"/>
+      <c r="P180" s="40"/>
+      <c r="Q180" s="40"/>
+      <c r="R180" s="40"/>
+      <c r="S180" s="40"/>
+      <c r="T180" s="40"/>
+      <c r="U180" s="41"/>
     </row>
     <row r="181" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="30"/>
@@ -27360,20 +27365,20 @@
       <c r="E181" s="31"/>
       <c r="F181" s="31"/>
       <c r="G181" s="31"/>
-      <c r="H181" s="51"/>
-      <c r="I181" s="59"/>
-      <c r="J181" s="59"/>
-      <c r="K181" s="59"/>
-      <c r="L181" s="59"/>
-      <c r="M181" s="59"/>
-      <c r="N181" s="59"/>
-      <c r="O181" s="59"/>
-      <c r="P181" s="59"/>
-      <c r="Q181" s="59"/>
-      <c r="R181" s="59"/>
-      <c r="S181" s="59"/>
-      <c r="T181" s="59"/>
-      <c r="U181" s="52"/>
+      <c r="H181" s="39"/>
+      <c r="I181" s="40"/>
+      <c r="J181" s="40"/>
+      <c r="K181" s="40"/>
+      <c r="L181" s="40"/>
+      <c r="M181" s="40"/>
+      <c r="N181" s="40"/>
+      <c r="O181" s="40"/>
+      <c r="P181" s="40"/>
+      <c r="Q181" s="40"/>
+      <c r="R181" s="40"/>
+      <c r="S181" s="40"/>
+      <c r="T181" s="40"/>
+      <c r="U181" s="41"/>
     </row>
     <row r="182" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A182" s="30"/>
@@ -27389,20 +27394,20 @@
       <c r="E182" s="31"/>
       <c r="F182" s="31"/>
       <c r="G182" s="31"/>
-      <c r="H182" s="51"/>
-      <c r="I182" s="59"/>
-      <c r="J182" s="59"/>
-      <c r="K182" s="59"/>
-      <c r="L182" s="59"/>
-      <c r="M182" s="59"/>
-      <c r="N182" s="59"/>
-      <c r="O182" s="59"/>
-      <c r="P182" s="59"/>
-      <c r="Q182" s="59"/>
-      <c r="R182" s="59"/>
-      <c r="S182" s="59"/>
-      <c r="T182" s="59"/>
-      <c r="U182" s="52"/>
+      <c r="H182" s="39"/>
+      <c r="I182" s="40"/>
+      <c r="J182" s="40"/>
+      <c r="K182" s="40"/>
+      <c r="L182" s="40"/>
+      <c r="M182" s="40"/>
+      <c r="N182" s="40"/>
+      <c r="O182" s="40"/>
+      <c r="P182" s="40"/>
+      <c r="Q182" s="40"/>
+      <c r="R182" s="40"/>
+      <c r="S182" s="40"/>
+      <c r="T182" s="40"/>
+      <c r="U182" s="41"/>
     </row>
     <row r="183" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="30"/>
@@ -27418,20 +27423,20 @@
       <c r="E183" s="31"/>
       <c r="F183" s="31"/>
       <c r="G183" s="31"/>
-      <c r="H183" s="51"/>
-      <c r="I183" s="59"/>
-      <c r="J183" s="59"/>
-      <c r="K183" s="59"/>
-      <c r="L183" s="59"/>
-      <c r="M183" s="59"/>
-      <c r="N183" s="59"/>
-      <c r="O183" s="59"/>
-      <c r="P183" s="59"/>
-      <c r="Q183" s="59"/>
-      <c r="R183" s="59"/>
-      <c r="S183" s="59"/>
-      <c r="T183" s="59"/>
-      <c r="U183" s="52"/>
+      <c r="H183" s="39"/>
+      <c r="I183" s="40"/>
+      <c r="J183" s="40"/>
+      <c r="K183" s="40"/>
+      <c r="L183" s="40"/>
+      <c r="M183" s="40"/>
+      <c r="N183" s="40"/>
+      <c r="O183" s="40"/>
+      <c r="P183" s="40"/>
+      <c r="Q183" s="40"/>
+      <c r="R183" s="40"/>
+      <c r="S183" s="40"/>
+      <c r="T183" s="40"/>
+      <c r="U183" s="41"/>
     </row>
     <row r="184" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" s="30"/>
@@ -27447,20 +27452,20 @@
       <c r="E184" s="31"/>
       <c r="F184" s="31"/>
       <c r="G184" s="31"/>
-      <c r="H184" s="51"/>
-      <c r="I184" s="59"/>
-      <c r="J184" s="59"/>
-      <c r="K184" s="59"/>
-      <c r="L184" s="59"/>
-      <c r="M184" s="59"/>
-      <c r="N184" s="59"/>
-      <c r="O184" s="59"/>
-      <c r="P184" s="59"/>
-      <c r="Q184" s="59"/>
-      <c r="R184" s="59"/>
-      <c r="S184" s="59"/>
-      <c r="T184" s="59"/>
-      <c r="U184" s="52"/>
+      <c r="H184" s="39"/>
+      <c r="I184" s="40"/>
+      <c r="J184" s="40"/>
+      <c r="K184" s="40"/>
+      <c r="L184" s="40"/>
+      <c r="M184" s="40"/>
+      <c r="N184" s="40"/>
+      <c r="O184" s="40"/>
+      <c r="P184" s="40"/>
+      <c r="Q184" s="40"/>
+      <c r="R184" s="40"/>
+      <c r="S184" s="40"/>
+      <c r="T184" s="40"/>
+      <c r="U184" s="41"/>
     </row>
     <row r="185" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A185" s="30"/>
@@ -27476,20 +27481,20 @@
       <c r="E185" s="31"/>
       <c r="F185" s="31"/>
       <c r="G185" s="31"/>
-      <c r="H185" s="51"/>
-      <c r="I185" s="59"/>
-      <c r="J185" s="59"/>
-      <c r="K185" s="59"/>
-      <c r="L185" s="59"/>
-      <c r="M185" s="59"/>
-      <c r="N185" s="59"/>
-      <c r="O185" s="59"/>
-      <c r="P185" s="59"/>
-      <c r="Q185" s="59"/>
-      <c r="R185" s="59"/>
-      <c r="S185" s="59"/>
-      <c r="T185" s="59"/>
-      <c r="U185" s="52"/>
+      <c r="H185" s="39"/>
+      <c r="I185" s="40"/>
+      <c r="J185" s="40"/>
+      <c r="K185" s="40"/>
+      <c r="L185" s="40"/>
+      <c r="M185" s="40"/>
+      <c r="N185" s="40"/>
+      <c r="O185" s="40"/>
+      <c r="P185" s="40"/>
+      <c r="Q185" s="40"/>
+      <c r="R185" s="40"/>
+      <c r="S185" s="40"/>
+      <c r="T185" s="40"/>
+      <c r="U185" s="41"/>
     </row>
     <row r="186" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A186" s="30"/>
@@ -27505,20 +27510,20 @@
       <c r="E186" s="31"/>
       <c r="F186" s="31"/>
       <c r="G186" s="31"/>
-      <c r="H186" s="51"/>
-      <c r="I186" s="59"/>
-      <c r="J186" s="59"/>
-      <c r="K186" s="59"/>
-      <c r="L186" s="59"/>
-      <c r="M186" s="59"/>
-      <c r="N186" s="59"/>
-      <c r="O186" s="59"/>
-      <c r="P186" s="59"/>
-      <c r="Q186" s="59"/>
-      <c r="R186" s="59"/>
-      <c r="S186" s="59"/>
-      <c r="T186" s="59"/>
-      <c r="U186" s="52"/>
+      <c r="H186" s="39"/>
+      <c r="I186" s="40"/>
+      <c r="J186" s="40"/>
+      <c r="K186" s="40"/>
+      <c r="L186" s="40"/>
+      <c r="M186" s="40"/>
+      <c r="N186" s="40"/>
+      <c r="O186" s="40"/>
+      <c r="P186" s="40"/>
+      <c r="Q186" s="40"/>
+      <c r="R186" s="40"/>
+      <c r="S186" s="40"/>
+      <c r="T186" s="40"/>
+      <c r="U186" s="41"/>
     </row>
     <row r="187" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" s="30"/>
@@ -27534,20 +27539,20 @@
       <c r="E187" s="31"/>
       <c r="F187" s="31"/>
       <c r="G187" s="31"/>
-      <c r="H187" s="51"/>
-      <c r="I187" s="59"/>
-      <c r="J187" s="59"/>
-      <c r="K187" s="59"/>
-      <c r="L187" s="59"/>
-      <c r="M187" s="59"/>
-      <c r="N187" s="59"/>
-      <c r="O187" s="59"/>
-      <c r="P187" s="59"/>
-      <c r="Q187" s="59"/>
-      <c r="R187" s="59"/>
-      <c r="S187" s="59"/>
-      <c r="T187" s="59"/>
-      <c r="U187" s="52"/>
+      <c r="H187" s="39"/>
+      <c r="I187" s="40"/>
+      <c r="J187" s="40"/>
+      <c r="K187" s="40"/>
+      <c r="L187" s="40"/>
+      <c r="M187" s="40"/>
+      <c r="N187" s="40"/>
+      <c r="O187" s="40"/>
+      <c r="P187" s="40"/>
+      <c r="Q187" s="40"/>
+      <c r="R187" s="40"/>
+      <c r="S187" s="40"/>
+      <c r="T187" s="40"/>
+      <c r="U187" s="41"/>
     </row>
     <row r="188" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" s="30"/>
@@ -27563,20 +27568,20 @@
       <c r="E188" s="31"/>
       <c r="F188" s="31"/>
       <c r="G188" s="31"/>
-      <c r="H188" s="51"/>
-      <c r="I188" s="59"/>
-      <c r="J188" s="59"/>
-      <c r="K188" s="59"/>
-      <c r="L188" s="59"/>
-      <c r="M188" s="59"/>
-      <c r="N188" s="59"/>
-      <c r="O188" s="59"/>
-      <c r="P188" s="59"/>
-      <c r="Q188" s="59"/>
-      <c r="R188" s="59"/>
-      <c r="S188" s="59"/>
-      <c r="T188" s="59"/>
-      <c r="U188" s="52"/>
+      <c r="H188" s="39"/>
+      <c r="I188" s="40"/>
+      <c r="J188" s="40"/>
+      <c r="K188" s="40"/>
+      <c r="L188" s="40"/>
+      <c r="M188" s="40"/>
+      <c r="N188" s="40"/>
+      <c r="O188" s="40"/>
+      <c r="P188" s="40"/>
+      <c r="Q188" s="40"/>
+      <c r="R188" s="40"/>
+      <c r="S188" s="40"/>
+      <c r="T188" s="40"/>
+      <c r="U188" s="41"/>
     </row>
     <row r="189" spans="1:35" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A189" s="30"/>
@@ -27592,20 +27597,20 @@
       <c r="E189" s="31"/>
       <c r="F189" s="31"/>
       <c r="G189" s="31"/>
-      <c r="H189" s="51"/>
-      <c r="I189" s="59"/>
-      <c r="J189" s="59"/>
-      <c r="K189" s="59"/>
-      <c r="L189" s="59"/>
-      <c r="M189" s="59"/>
-      <c r="N189" s="59"/>
-      <c r="O189" s="59"/>
-      <c r="P189" s="59"/>
-      <c r="Q189" s="59"/>
-      <c r="R189" s="59"/>
-      <c r="S189" s="59"/>
-      <c r="T189" s="59"/>
-      <c r="U189" s="52"/>
+      <c r="H189" s="39"/>
+      <c r="I189" s="40"/>
+      <c r="J189" s="40"/>
+      <c r="K189" s="40"/>
+      <c r="L189" s="40"/>
+      <c r="M189" s="40"/>
+      <c r="N189" s="40"/>
+      <c r="O189" s="40"/>
+      <c r="P189" s="40"/>
+      <c r="Q189" s="40"/>
+      <c r="R189" s="40"/>
+      <c r="S189" s="40"/>
+      <c r="T189" s="40"/>
+      <c r="U189" s="41"/>
     </row>
     <row r="190" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A190" s="30"/>
@@ -27621,20 +27626,20 @@
       <c r="E190" s="31"/>
       <c r="F190" s="31"/>
       <c r="G190" s="31"/>
-      <c r="H190" s="51"/>
-      <c r="I190" s="59"/>
-      <c r="J190" s="59"/>
-      <c r="K190" s="59"/>
-      <c r="L190" s="59"/>
-      <c r="M190" s="59"/>
-      <c r="N190" s="59"/>
-      <c r="O190" s="59"/>
-      <c r="P190" s="59"/>
-      <c r="Q190" s="59"/>
-      <c r="R190" s="59"/>
-      <c r="S190" s="59"/>
-      <c r="T190" s="59"/>
-      <c r="U190" s="52"/>
+      <c r="H190" s="39"/>
+      <c r="I190" s="40"/>
+      <c r="J190" s="40"/>
+      <c r="K190" s="40"/>
+      <c r="L190" s="40"/>
+      <c r="M190" s="40"/>
+      <c r="N190" s="40"/>
+      <c r="O190" s="40"/>
+      <c r="P190" s="40"/>
+      <c r="Q190" s="40"/>
+      <c r="R190" s="40"/>
+      <c r="S190" s="40"/>
+      <c r="T190" s="40"/>
+      <c r="U190" s="41"/>
     </row>
     <row r="191" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A191" s="30"/>
@@ -27650,20 +27655,20 @@
       <c r="E191" s="31"/>
       <c r="F191" s="31"/>
       <c r="G191" s="31"/>
-      <c r="H191" s="51"/>
-      <c r="I191" s="59"/>
-      <c r="J191" s="59"/>
-      <c r="K191" s="59"/>
-      <c r="L191" s="59"/>
-      <c r="M191" s="59"/>
-      <c r="N191" s="59"/>
-      <c r="O191" s="59"/>
-      <c r="P191" s="59"/>
-      <c r="Q191" s="59"/>
-      <c r="R191" s="59"/>
-      <c r="S191" s="59"/>
-      <c r="T191" s="59"/>
-      <c r="U191" s="52"/>
+      <c r="H191" s="39"/>
+      <c r="I191" s="40"/>
+      <c r="J191" s="40"/>
+      <c r="K191" s="40"/>
+      <c r="L191" s="40"/>
+      <c r="M191" s="40"/>
+      <c r="N191" s="40"/>
+      <c r="O191" s="40"/>
+      <c r="P191" s="40"/>
+      <c r="Q191" s="40"/>
+      <c r="R191" s="40"/>
+      <c r="S191" s="40"/>
+      <c r="T191" s="40"/>
+      <c r="U191" s="41"/>
     </row>
     <row r="192" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" s="30"/>
@@ -27679,20 +27684,20 @@
       <c r="E192" s="31"/>
       <c r="F192" s="31"/>
       <c r="G192" s="31"/>
-      <c r="H192" s="51"/>
-      <c r="I192" s="59"/>
-      <c r="J192" s="59"/>
-      <c r="K192" s="59"/>
-      <c r="L192" s="59"/>
-      <c r="M192" s="59"/>
-      <c r="N192" s="59"/>
-      <c r="O192" s="59"/>
-      <c r="P192" s="59"/>
-      <c r="Q192" s="59"/>
-      <c r="R192" s="59"/>
-      <c r="S192" s="59"/>
-      <c r="T192" s="59"/>
-      <c r="U192" s="52"/>
+      <c r="H192" s="39"/>
+      <c r="I192" s="40"/>
+      <c r="J192" s="40"/>
+      <c r="K192" s="40"/>
+      <c r="L192" s="40"/>
+      <c r="M192" s="40"/>
+      <c r="N192" s="40"/>
+      <c r="O192" s="40"/>
+      <c r="P192" s="40"/>
+      <c r="Q192" s="40"/>
+      <c r="R192" s="40"/>
+      <c r="S192" s="40"/>
+      <c r="T192" s="40"/>
+      <c r="U192" s="41"/>
     </row>
     <row r="193" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="30"/>
@@ -27708,22 +27713,22 @@
       <c r="E193" s="31"/>
       <c r="F193" s="31"/>
       <c r="G193" s="31"/>
-      <c r="H193" s="51" t="s">
+      <c r="H193" s="39" t="s">
         <v>770</v>
       </c>
-      <c r="I193" s="59"/>
-      <c r="J193" s="59"/>
-      <c r="K193" s="59"/>
-      <c r="L193" s="59"/>
-      <c r="M193" s="59"/>
-      <c r="N193" s="59"/>
-      <c r="O193" s="59"/>
-      <c r="P193" s="59"/>
-      <c r="Q193" s="59"/>
-      <c r="R193" s="59"/>
-      <c r="S193" s="59"/>
-      <c r="T193" s="59"/>
-      <c r="U193" s="52"/>
+      <c r="I193" s="40"/>
+      <c r="J193" s="40"/>
+      <c r="K193" s="40"/>
+      <c r="L193" s="40"/>
+      <c r="M193" s="40"/>
+      <c r="N193" s="40"/>
+      <c r="O193" s="40"/>
+      <c r="P193" s="40"/>
+      <c r="Q193" s="40"/>
+      <c r="R193" s="40"/>
+      <c r="S193" s="40"/>
+      <c r="T193" s="40"/>
+      <c r="U193" s="41"/>
     </row>
     <row r="194" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" s="30"/>
@@ -27739,20 +27744,20 @@
       <c r="E194" s="31"/>
       <c r="F194" s="31"/>
       <c r="G194" s="31"/>
-      <c r="H194" s="51"/>
-      <c r="I194" s="59"/>
-      <c r="J194" s="59"/>
-      <c r="K194" s="59"/>
-      <c r="L194" s="59"/>
-      <c r="M194" s="59"/>
-      <c r="N194" s="59"/>
-      <c r="O194" s="59"/>
-      <c r="P194" s="59"/>
-      <c r="Q194" s="59"/>
-      <c r="R194" s="59"/>
-      <c r="S194" s="59"/>
-      <c r="T194" s="59"/>
-      <c r="U194" s="52"/>
+      <c r="H194" s="39"/>
+      <c r="I194" s="40"/>
+      <c r="J194" s="40"/>
+      <c r="K194" s="40"/>
+      <c r="L194" s="40"/>
+      <c r="M194" s="40"/>
+      <c r="N194" s="40"/>
+      <c r="O194" s="40"/>
+      <c r="P194" s="40"/>
+      <c r="Q194" s="40"/>
+      <c r="R194" s="40"/>
+      <c r="S194" s="40"/>
+      <c r="T194" s="40"/>
+      <c r="U194" s="41"/>
     </row>
     <row r="195" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" s="30"/>
@@ -27766,20 +27771,20 @@
       <c r="E195" s="31"/>
       <c r="F195" s="31"/>
       <c r="G195" s="31"/>
-      <c r="H195" s="51"/>
-      <c r="I195" s="59"/>
-      <c r="J195" s="59"/>
-      <c r="K195" s="59"/>
-      <c r="L195" s="59"/>
-      <c r="M195" s="59"/>
-      <c r="N195" s="59"/>
-      <c r="O195" s="59"/>
-      <c r="P195" s="59"/>
-      <c r="Q195" s="59"/>
-      <c r="R195" s="59"/>
-      <c r="S195" s="59"/>
-      <c r="T195" s="59"/>
-      <c r="U195" s="52"/>
+      <c r="H195" s="39"/>
+      <c r="I195" s="40"/>
+      <c r="J195" s="40"/>
+      <c r="K195" s="40"/>
+      <c r="L195" s="40"/>
+      <c r="M195" s="40"/>
+      <c r="N195" s="40"/>
+      <c r="O195" s="40"/>
+      <c r="P195" s="40"/>
+      <c r="Q195" s="40"/>
+      <c r="R195" s="40"/>
+      <c r="S195" s="40"/>
+      <c r="T195" s="40"/>
+      <c r="U195" s="41"/>
     </row>
     <row r="196" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" s="30"/>
@@ -27793,20 +27798,20 @@
       <c r="E196" s="31"/>
       <c r="F196" s="31"/>
       <c r="G196" s="31"/>
-      <c r="H196" s="51"/>
-      <c r="I196" s="59"/>
-      <c r="J196" s="59"/>
-      <c r="K196" s="59"/>
-      <c r="L196" s="59"/>
-      <c r="M196" s="59"/>
-      <c r="N196" s="59"/>
-      <c r="O196" s="59"/>
-      <c r="P196" s="59"/>
-      <c r="Q196" s="59"/>
-      <c r="R196" s="59"/>
-      <c r="S196" s="59"/>
-      <c r="T196" s="59"/>
-      <c r="U196" s="52"/>
+      <c r="H196" s="39"/>
+      <c r="I196" s="40"/>
+      <c r="J196" s="40"/>
+      <c r="K196" s="40"/>
+      <c r="L196" s="40"/>
+      <c r="M196" s="40"/>
+      <c r="N196" s="40"/>
+      <c r="O196" s="40"/>
+      <c r="P196" s="40"/>
+      <c r="Q196" s="40"/>
+      <c r="R196" s="40"/>
+      <c r="S196" s="40"/>
+      <c r="T196" s="40"/>
+      <c r="U196" s="41"/>
     </row>
     <row r="197" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" s="30"/>
@@ -27820,23 +27825,70 @@
       <c r="E197" s="31"/>
       <c r="F197" s="31"/>
       <c r="G197" s="31"/>
-      <c r="H197" s="51"/>
-      <c r="I197" s="59"/>
-      <c r="J197" s="59"/>
-      <c r="K197" s="59"/>
-      <c r="L197" s="59"/>
-      <c r="M197" s="59"/>
-      <c r="N197" s="59"/>
-      <c r="O197" s="59"/>
-      <c r="P197" s="59"/>
-      <c r="Q197" s="59"/>
-      <c r="R197" s="59"/>
-      <c r="S197" s="59"/>
-      <c r="T197" s="59"/>
-      <c r="U197" s="52"/>
+      <c r="H197" s="39"/>
+      <c r="I197" s="40"/>
+      <c r="J197" s="40"/>
+      <c r="K197" s="40"/>
+      <c r="L197" s="40"/>
+      <c r="M197" s="40"/>
+      <c r="N197" s="40"/>
+      <c r="O197" s="40"/>
+      <c r="P197" s="40"/>
+      <c r="Q197" s="40"/>
+      <c r="R197" s="40"/>
+      <c r="S197" s="40"/>
+      <c r="T197" s="40"/>
+      <c r="U197" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="63">
+    <mergeCell ref="H195:U195"/>
+    <mergeCell ref="H196:U196"/>
+    <mergeCell ref="H197:U197"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="H189:U189"/>
+    <mergeCell ref="H190:U190"/>
+    <mergeCell ref="H191:U191"/>
+    <mergeCell ref="H192:U192"/>
+    <mergeCell ref="H193:U193"/>
+    <mergeCell ref="H194:U194"/>
+    <mergeCell ref="H183:U183"/>
+    <mergeCell ref="H184:U184"/>
+    <mergeCell ref="H185:U185"/>
+    <mergeCell ref="H186:U186"/>
+    <mergeCell ref="H187:U187"/>
+    <mergeCell ref="C128:I128"/>
+    <mergeCell ref="C148:I148"/>
+    <mergeCell ref="H188:U188"/>
+    <mergeCell ref="C153:I153"/>
+    <mergeCell ref="C169:I169"/>
+    <mergeCell ref="A179:U179"/>
+    <mergeCell ref="H180:U180"/>
+    <mergeCell ref="H181:U181"/>
+    <mergeCell ref="H182:U182"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="C149:I149"/>
+    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="C12:I12"/>
+    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="C37:I37"/>
+    <mergeCell ref="C45:I45"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="C66:I66"/>
+    <mergeCell ref="C67:I67"/>
+    <mergeCell ref="C97:I97"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="H5:H7"/>
+    <mergeCell ref="I5:I7"/>
+    <mergeCell ref="J5:O5"/>
+    <mergeCell ref="P5:R5"/>
+    <mergeCell ref="R6:R7"/>
     <mergeCell ref="A2:U2"/>
     <mergeCell ref="A3:U3"/>
     <mergeCell ref="A4:U4"/>
@@ -27853,53 +27905,6 @@
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="O6:O7"/>
     <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="H5:H7"/>
-    <mergeCell ref="I5:I7"/>
-    <mergeCell ref="J5:O5"/>
-    <mergeCell ref="P5:R5"/>
-    <mergeCell ref="R6:R7"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="U6:U7"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="C149:I149"/>
-    <mergeCell ref="C11:I11"/>
-    <mergeCell ref="C12:I12"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="C14:I14"/>
-    <mergeCell ref="C37:I37"/>
-    <mergeCell ref="C45:I45"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="C66:I66"/>
-    <mergeCell ref="C67:I67"/>
-    <mergeCell ref="C97:I97"/>
-    <mergeCell ref="C128:I128"/>
-    <mergeCell ref="C148:I148"/>
-    <mergeCell ref="H188:U188"/>
-    <mergeCell ref="C153:I153"/>
-    <mergeCell ref="C169:I169"/>
-    <mergeCell ref="A179:U179"/>
-    <mergeCell ref="H180:U180"/>
-    <mergeCell ref="H181:U181"/>
-    <mergeCell ref="H182:U182"/>
-    <mergeCell ref="H195:U195"/>
-    <mergeCell ref="H196:U196"/>
-    <mergeCell ref="H197:U197"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="H189:U189"/>
-    <mergeCell ref="H190:U190"/>
-    <mergeCell ref="H191:U191"/>
-    <mergeCell ref="H192:U192"/>
-    <mergeCell ref="H193:U193"/>
-    <mergeCell ref="H194:U194"/>
-    <mergeCell ref="H183:U183"/>
-    <mergeCell ref="H184:U184"/>
-    <mergeCell ref="H185:U185"/>
-    <mergeCell ref="H186:U186"/>
-    <mergeCell ref="H187:U187"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/school_2/school_2_KP.xlsx
+++ b/school_2/school_2_KP.xlsx
@@ -2800,39 +2800,6 @@
     <xf numFmtId="0" fontId="14" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2863,19 +2830,52 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3264,79 +3264,79 @@
       </c>
     </row>
     <row r="2" spans="1:35" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="50"/>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="50"/>
-      <c r="S2" s="50"/>
-      <c r="T2" s="50"/>
-      <c r="U2" s="50"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
+      <c r="O2" s="39"/>
+      <c r="P2" s="39"/>
+      <c r="Q2" s="39"/>
+      <c r="R2" s="39"/>
+      <c r="S2" s="39"/>
+      <c r="T2" s="39"/>
+      <c r="U2" s="39"/>
     </row>
     <row r="3" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="51"/>
-      <c r="N3" s="51"/>
-      <c r="O3" s="51"/>
-      <c r="P3" s="51"/>
-      <c r="Q3" s="51"/>
-      <c r="R3" s="51"/>
-      <c r="S3" s="51"/>
-      <c r="T3" s="51"/>
-      <c r="U3" s="51"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40"/>
+      <c r="S3" s="40"/>
+      <c r="T3" s="40"/>
+      <c r="U3" s="40"/>
     </row>
     <row r="4" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="52"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="52"/>
-      <c r="N4" s="52"/>
-      <c r="O4" s="52"/>
-      <c r="P4" s="52"/>
-      <c r="Q4" s="52"/>
-      <c r="R4" s="52"/>
-      <c r="S4" s="52"/>
-      <c r="T4" s="52"/>
-      <c r="U4" s="52"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="41"/>
+      <c r="P4" s="41"/>
+      <c r="Q4" s="41"/>
+      <c r="R4" s="41"/>
+      <c r="S4" s="41"/>
+      <c r="T4" s="41"/>
+      <c r="U4" s="41"/>
     </row>
     <row r="5" spans="1:35" ht="40.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="48" t="s">
@@ -3366,115 +3366,115 @@
       <c r="I5" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J5" s="53" t="s">
+      <c r="J5" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="54"/>
-      <c r="N5" s="54"/>
-      <c r="O5" s="55"/>
-      <c r="P5" s="56" t="s">
+      <c r="K5" s="43"/>
+      <c r="L5" s="43"/>
+      <c r="M5" s="43"/>
+      <c r="N5" s="43"/>
+      <c r="O5" s="44"/>
+      <c r="P5" s="45" t="s">
         <v>780</v>
       </c>
-      <c r="Q5" s="57"/>
-      <c r="R5" s="58"/>
-      <c r="S5" s="56">
+      <c r="Q5" s="46"/>
+      <c r="R5" s="47"/>
+      <c r="S5" s="45">
         <v>9701212867</v>
       </c>
-      <c r="T5" s="57"/>
-      <c r="U5" s="58"/>
+      <c r="T5" s="46"/>
+      <c r="U5" s="47"/>
     </row>
     <row r="6" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="59"/>
-      <c r="B6" s="59"/>
-      <c r="C6" s="59"/>
-      <c r="D6" s="59"/>
-      <c r="E6" s="59"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="59"/>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59"/>
-      <c r="J6" s="39" t="s">
+      <c r="A6" s="49"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="41"/>
+      <c r="K6" s="52"/>
       <c r="L6" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="M6" s="39" t="s">
+      <c r="M6" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="N6" s="41"/>
+      <c r="N6" s="52"/>
       <c r="O6" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="P6" s="39" t="s">
+      <c r="P6" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="Q6" s="41"/>
+      <c r="Q6" s="52"/>
       <c r="R6" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="S6" s="39" t="s">
+      <c r="S6" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="T6" s="41"/>
+      <c r="T6" s="52"/>
       <c r="U6" s="48" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:35" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="49"/>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
+      <c r="A7" s="50"/>
+      <c r="B7" s="50"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="50"/>
+      <c r="H7" s="50"/>
+      <c r="I7" s="50"/>
       <c r="J7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L7" s="49"/>
+      <c r="L7" s="50"/>
       <c r="M7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="O7" s="49"/>
+      <c r="O7" s="50"/>
       <c r="P7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="R7" s="49"/>
+      <c r="R7" s="50"/>
       <c r="S7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="T7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="U7" s="49"/>
+      <c r="U7" s="50"/>
     </row>
     <row r="8" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="45" t="s">
+      <c r="A8" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="46"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="46"/>
-      <c r="F8" s="46"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="47"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="55"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -3528,15 +3528,15 @@
       <c r="B9" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="42" t="s">
+      <c r="C9" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="44"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="58"/>
       <c r="M9" s="6">
         <f t="shared" si="0"/>
         <v>21918840.049999997</v>
@@ -3587,15 +3587,15 @@
       <c r="B10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="44"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="58"/>
       <c r="M10" s="6">
         <f t="shared" si="0"/>
         <v>21918840.049999997</v>
@@ -3646,15 +3646,15 @@
       <c r="B11" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="42" t="s">
+      <c r="C11" s="56" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="43"/>
-      <c r="I11" s="44"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="58"/>
       <c r="M11" s="6">
         <f t="shared" si="0"/>
         <v>21918840.049999997</v>
@@ -3705,15 +3705,15 @@
       <c r="B12" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="42" t="s">
+      <c r="C12" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="44"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="58"/>
       <c r="M12" s="6">
         <f>SUM(M13,M66,M148,M169)</f>
         <v>21918840.049999997</v>
@@ -3764,15 +3764,15 @@
       <c r="B13" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="42" t="s">
+      <c r="C13" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="44"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="58"/>
       <c r="M13" s="6">
         <f>SUM(M14,M37,M45)</f>
         <v>3570644.12</v>
@@ -3823,15 +3823,15 @@
       <c r="B14" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="42" t="s">
+      <c r="C14" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="44"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="58"/>
       <c r="M14" s="6">
         <f>SUM(M15,M19,M21,M29)</f>
         <v>2618573.91</v>
@@ -5256,15 +5256,15 @@
       <c r="B37" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="C37" s="42" t="s">
+      <c r="C37" s="56" t="s">
         <v>154</v>
       </c>
-      <c r="D37" s="43"/>
-      <c r="E37" s="43"/>
-      <c r="F37" s="43"/>
-      <c r="G37" s="43"/>
-      <c r="H37" s="43"/>
-      <c r="I37" s="44"/>
+      <c r="D37" s="57"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="57"/>
+      <c r="H37" s="57"/>
+      <c r="I37" s="58"/>
       <c r="M37" s="6">
         <f>SUM(M38,M41,M43)</f>
         <v>122933.90000000001</v>
@@ -5849,15 +5849,15 @@
       <c r="B45" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="C45" s="42" t="s">
+      <c r="C45" s="56" t="s">
         <v>193</v>
       </c>
-      <c r="D45" s="43"/>
-      <c r="E45" s="43"/>
-      <c r="F45" s="43"/>
-      <c r="G45" s="43"/>
-      <c r="H45" s="43"/>
-      <c r="I45" s="44"/>
+      <c r="D45" s="57"/>
+      <c r="E45" s="57"/>
+      <c r="F45" s="57"/>
+      <c r="G45" s="57"/>
+      <c r="H45" s="57"/>
+      <c r="I45" s="58"/>
       <c r="M45" s="6">
         <f>SUM(M46,M51,M55,M60,M63)</f>
         <v>829136.31</v>
@@ -7252,15 +7252,15 @@
       <c r="B66" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="C66" s="42" t="s">
+      <c r="C66" s="56" t="s">
         <v>299</v>
       </c>
-      <c r="D66" s="43"/>
-      <c r="E66" s="43"/>
-      <c r="F66" s="43"/>
-      <c r="G66" s="43"/>
-      <c r="H66" s="43"/>
-      <c r="I66" s="44"/>
+      <c r="D66" s="57"/>
+      <c r="E66" s="57"/>
+      <c r="F66" s="57"/>
+      <c r="G66" s="57"/>
+      <c r="H66" s="57"/>
+      <c r="I66" s="58"/>
       <c r="M66" s="6">
         <f>SUM(M67,M97,M128)</f>
         <v>4332566.72</v>
@@ -7311,15 +7311,15 @@
       <c r="B67" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="C67" s="42" t="s">
+      <c r="C67" s="56" t="s">
         <v>302</v>
       </c>
-      <c r="D67" s="43"/>
-      <c r="E67" s="43"/>
-      <c r="F67" s="43"/>
-      <c r="G67" s="43"/>
-      <c r="H67" s="43"/>
-      <c r="I67" s="44"/>
+      <c r="D67" s="57"/>
+      <c r="E67" s="57"/>
+      <c r="F67" s="57"/>
+      <c r="G67" s="57"/>
+      <c r="H67" s="57"/>
+      <c r="I67" s="58"/>
       <c r="M67" s="6">
         <f>SUM(M68,M71,M75,M79,M82,M85,M89,M92)</f>
         <v>2963619.5900000003</v>
@@ -9346,15 +9346,15 @@
       <c r="B97" s="10" t="s">
         <v>419</v>
       </c>
-      <c r="C97" s="42" t="s">
+      <c r="C97" s="56" t="s">
         <v>420</v>
       </c>
-      <c r="D97" s="43"/>
-      <c r="E97" s="43"/>
-      <c r="F97" s="43"/>
-      <c r="G97" s="43"/>
-      <c r="H97" s="43"/>
-      <c r="I97" s="44"/>
+      <c r="D97" s="57"/>
+      <c r="E97" s="57"/>
+      <c r="F97" s="57"/>
+      <c r="G97" s="57"/>
+      <c r="H97" s="57"/>
+      <c r="I97" s="58"/>
       <c r="M97" s="6">
         <f>SUM(M98,M107,M110,M113,M116,M119,M122,M125)</f>
         <v>1187256.6599999997</v>
@@ -11433,15 +11433,15 @@
       <c r="B128" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="C128" s="42" t="s">
+      <c r="C128" s="56" t="s">
         <v>534</v>
       </c>
-      <c r="D128" s="43"/>
-      <c r="E128" s="43"/>
-      <c r="F128" s="43"/>
-      <c r="G128" s="43"/>
-      <c r="H128" s="43"/>
-      <c r="I128" s="44"/>
+      <c r="D128" s="57"/>
+      <c r="E128" s="57"/>
+      <c r="F128" s="57"/>
+      <c r="G128" s="57"/>
+      <c r="H128" s="57"/>
+      <c r="I128" s="58"/>
       <c r="M128" s="6">
         <f>SUM(M129,M132,M135,M138,M143)</f>
         <v>181690.47</v>
@@ -12764,15 +12764,15 @@
       <c r="B148" s="10" t="s">
         <v>616</v>
       </c>
-      <c r="C148" s="42" t="s">
+      <c r="C148" s="56" t="s">
         <v>617</v>
       </c>
-      <c r="D148" s="43"/>
-      <c r="E148" s="43"/>
-      <c r="F148" s="43"/>
-      <c r="G148" s="43"/>
-      <c r="H148" s="43"/>
-      <c r="I148" s="44"/>
+      <c r="D148" s="57"/>
+      <c r="E148" s="57"/>
+      <c r="F148" s="57"/>
+      <c r="G148" s="57"/>
+      <c r="H148" s="57"/>
+      <c r="I148" s="58"/>
       <c r="M148" s="6">
         <f>SUM(M149,M153)</f>
         <v>447303.98</v>
@@ -12823,15 +12823,15 @@
       <c r="B149" s="10" t="s">
         <v>619</v>
       </c>
-      <c r="C149" s="42" t="s">
+      <c r="C149" s="56" t="s">
         <v>620</v>
       </c>
-      <c r="D149" s="43"/>
-      <c r="E149" s="43"/>
-      <c r="F149" s="43"/>
-      <c r="G149" s="43"/>
-      <c r="H149" s="43"/>
-      <c r="I149" s="44"/>
+      <c r="D149" s="57"/>
+      <c r="E149" s="57"/>
+      <c r="F149" s="57"/>
+      <c r="G149" s="57"/>
+      <c r="H149" s="57"/>
+      <c r="I149" s="58"/>
       <c r="M149" s="6">
         <f>SUM(M150)</f>
         <v>241468.92</v>
@@ -13094,15 +13094,15 @@
       <c r="B153" s="10" t="s">
         <v>635</v>
       </c>
-      <c r="C153" s="42" t="s">
+      <c r="C153" s="56" t="s">
         <v>636</v>
       </c>
-      <c r="D153" s="43"/>
-      <c r="E153" s="43"/>
-      <c r="F153" s="43"/>
-      <c r="G153" s="43"/>
-      <c r="H153" s="43"/>
-      <c r="I153" s="44"/>
+      <c r="D153" s="57"/>
+      <c r="E153" s="57"/>
+      <c r="F153" s="57"/>
+      <c r="G153" s="57"/>
+      <c r="H153" s="57"/>
+      <c r="I153" s="58"/>
       <c r="M153" s="6">
         <f>SUM(M154,M157,M160,M163,M166)</f>
         <v>205835.06</v>
@@ -14225,15 +14225,15 @@
       <c r="B169" s="10" t="s">
         <v>683</v>
       </c>
-      <c r="C169" s="42" t="s">
+      <c r="C169" s="56" t="s">
         <v>684</v>
       </c>
-      <c r="D169" s="43"/>
-      <c r="E169" s="43"/>
-      <c r="F169" s="43"/>
-      <c r="G169" s="43"/>
-      <c r="H169" s="43"/>
-      <c r="I169" s="44"/>
+      <c r="D169" s="57"/>
+      <c r="E169" s="57"/>
+      <c r="F169" s="57"/>
+      <c r="G169" s="57"/>
+      <c r="H169" s="57"/>
+      <c r="I169" s="58"/>
       <c r="M169" s="6">
         <f>SUM(M170,M173,M177)</f>
         <v>13568325.229999999</v>
@@ -14911,29 +14911,29 @@
       </c>
     </row>
     <row r="179" spans="1:35" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A179" s="45" t="s">
+      <c r="A179" s="53" t="s">
         <v>728</v>
       </c>
-      <c r="B179" s="46"/>
-      <c r="C179" s="46"/>
-      <c r="D179" s="46"/>
-      <c r="E179" s="46"/>
-      <c r="F179" s="46"/>
-      <c r="G179" s="46"/>
-      <c r="H179" s="46"/>
-      <c r="I179" s="46"/>
-      <c r="J179" s="46"/>
-      <c r="K179" s="46"/>
-      <c r="L179" s="46"/>
-      <c r="M179" s="46"/>
-      <c r="N179" s="46"/>
-      <c r="O179" s="46"/>
-      <c r="P179" s="46"/>
-      <c r="Q179" s="46"/>
-      <c r="R179" s="46"/>
-      <c r="S179" s="46"/>
-      <c r="T179" s="46"/>
-      <c r="U179" s="47"/>
+      <c r="B179" s="54"/>
+      <c r="C179" s="54"/>
+      <c r="D179" s="54"/>
+      <c r="E179" s="54"/>
+      <c r="F179" s="54"/>
+      <c r="G179" s="54"/>
+      <c r="H179" s="54"/>
+      <c r="I179" s="54"/>
+      <c r="J179" s="54"/>
+      <c r="K179" s="54"/>
+      <c r="L179" s="54"/>
+      <c r="M179" s="54"/>
+      <c r="N179" s="54"/>
+      <c r="O179" s="54"/>
+      <c r="P179" s="54"/>
+      <c r="Q179" s="54"/>
+      <c r="R179" s="54"/>
+      <c r="S179" s="54"/>
+      <c r="T179" s="54"/>
+      <c r="U179" s="55"/>
     </row>
     <row r="180" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="30"/>
@@ -14949,20 +14949,20 @@
       <c r="E180" s="31"/>
       <c r="F180" s="31"/>
       <c r="G180" s="31"/>
-      <c r="H180" s="39"/>
-      <c r="I180" s="40"/>
-      <c r="J180" s="40"/>
-      <c r="K180" s="40"/>
-      <c r="L180" s="40"/>
-      <c r="M180" s="40"/>
-      <c r="N180" s="40"/>
-      <c r="O180" s="40"/>
-      <c r="P180" s="40"/>
-      <c r="Q180" s="40"/>
-      <c r="R180" s="40"/>
-      <c r="S180" s="40"/>
-      <c r="T180" s="40"/>
-      <c r="U180" s="41"/>
+      <c r="H180" s="51"/>
+      <c r="I180" s="59"/>
+      <c r="J180" s="59"/>
+      <c r="K180" s="59"/>
+      <c r="L180" s="59"/>
+      <c r="M180" s="59"/>
+      <c r="N180" s="59"/>
+      <c r="O180" s="59"/>
+      <c r="P180" s="59"/>
+      <c r="Q180" s="59"/>
+      <c r="R180" s="59"/>
+      <c r="S180" s="59"/>
+      <c r="T180" s="59"/>
+      <c r="U180" s="52"/>
     </row>
     <row r="181" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="30"/>
@@ -14978,20 +14978,20 @@
       <c r="E181" s="31"/>
       <c r="F181" s="31"/>
       <c r="G181" s="31"/>
-      <c r="H181" s="39"/>
-      <c r="I181" s="40"/>
-      <c r="J181" s="40"/>
-      <c r="K181" s="40"/>
-      <c r="L181" s="40"/>
-      <c r="M181" s="40"/>
-      <c r="N181" s="40"/>
-      <c r="O181" s="40"/>
-      <c r="P181" s="40"/>
-      <c r="Q181" s="40"/>
-      <c r="R181" s="40"/>
-      <c r="S181" s="40"/>
-      <c r="T181" s="40"/>
-      <c r="U181" s="41"/>
+      <c r="H181" s="51"/>
+      <c r="I181" s="59"/>
+      <c r="J181" s="59"/>
+      <c r="K181" s="59"/>
+      <c r="L181" s="59"/>
+      <c r="M181" s="59"/>
+      <c r="N181" s="59"/>
+      <c r="O181" s="59"/>
+      <c r="P181" s="59"/>
+      <c r="Q181" s="59"/>
+      <c r="R181" s="59"/>
+      <c r="S181" s="59"/>
+      <c r="T181" s="59"/>
+      <c r="U181" s="52"/>
     </row>
     <row r="182" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A182" s="30"/>
@@ -15007,20 +15007,20 @@
       <c r="E182" s="31"/>
       <c r="F182" s="31"/>
       <c r="G182" s="31"/>
-      <c r="H182" s="39"/>
-      <c r="I182" s="40"/>
-      <c r="J182" s="40"/>
-      <c r="K182" s="40"/>
-      <c r="L182" s="40"/>
-      <c r="M182" s="40"/>
-      <c r="N182" s="40"/>
-      <c r="O182" s="40"/>
-      <c r="P182" s="40"/>
-      <c r="Q182" s="40"/>
-      <c r="R182" s="40"/>
-      <c r="S182" s="40"/>
-      <c r="T182" s="40"/>
-      <c r="U182" s="41"/>
+      <c r="H182" s="51"/>
+      <c r="I182" s="59"/>
+      <c r="J182" s="59"/>
+      <c r="K182" s="59"/>
+      <c r="L182" s="59"/>
+      <c r="M182" s="59"/>
+      <c r="N182" s="59"/>
+      <c r="O182" s="59"/>
+      <c r="P182" s="59"/>
+      <c r="Q182" s="59"/>
+      <c r="R182" s="59"/>
+      <c r="S182" s="59"/>
+      <c r="T182" s="59"/>
+      <c r="U182" s="52"/>
     </row>
     <row r="183" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="30"/>
@@ -15036,20 +15036,20 @@
       <c r="E183" s="31"/>
       <c r="F183" s="31"/>
       <c r="G183" s="31"/>
-      <c r="H183" s="39"/>
-      <c r="I183" s="40"/>
-      <c r="J183" s="40"/>
-      <c r="K183" s="40"/>
-      <c r="L183" s="40"/>
-      <c r="M183" s="40"/>
-      <c r="N183" s="40"/>
-      <c r="O183" s="40"/>
-      <c r="P183" s="40"/>
-      <c r="Q183" s="40"/>
-      <c r="R183" s="40"/>
-      <c r="S183" s="40"/>
-      <c r="T183" s="40"/>
-      <c r="U183" s="41"/>
+      <c r="H183" s="51"/>
+      <c r="I183" s="59"/>
+      <c r="J183" s="59"/>
+      <c r="K183" s="59"/>
+      <c r="L183" s="59"/>
+      <c r="M183" s="59"/>
+      <c r="N183" s="59"/>
+      <c r="O183" s="59"/>
+      <c r="P183" s="59"/>
+      <c r="Q183" s="59"/>
+      <c r="R183" s="59"/>
+      <c r="S183" s="59"/>
+      <c r="T183" s="59"/>
+      <c r="U183" s="52"/>
     </row>
     <row r="184" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" s="30"/>
@@ -15065,20 +15065,20 @@
       <c r="E184" s="31"/>
       <c r="F184" s="31"/>
       <c r="G184" s="31"/>
-      <c r="H184" s="39"/>
-      <c r="I184" s="40"/>
-      <c r="J184" s="40"/>
-      <c r="K184" s="40"/>
-      <c r="L184" s="40"/>
-      <c r="M184" s="40"/>
-      <c r="N184" s="40"/>
-      <c r="O184" s="40"/>
-      <c r="P184" s="40"/>
-      <c r="Q184" s="40"/>
-      <c r="R184" s="40"/>
-      <c r="S184" s="40"/>
-      <c r="T184" s="40"/>
-      <c r="U184" s="41"/>
+      <c r="H184" s="51"/>
+      <c r="I184" s="59"/>
+      <c r="J184" s="59"/>
+      <c r="K184" s="59"/>
+      <c r="L184" s="59"/>
+      <c r="M184" s="59"/>
+      <c r="N184" s="59"/>
+      <c r="O184" s="59"/>
+      <c r="P184" s="59"/>
+      <c r="Q184" s="59"/>
+      <c r="R184" s="59"/>
+      <c r="S184" s="59"/>
+      <c r="T184" s="59"/>
+      <c r="U184" s="52"/>
     </row>
     <row r="185" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A185" s="30"/>
@@ -15094,20 +15094,20 @@
       <c r="E185" s="31"/>
       <c r="F185" s="31"/>
       <c r="G185" s="31"/>
-      <c r="H185" s="39"/>
-      <c r="I185" s="40"/>
-      <c r="J185" s="40"/>
-      <c r="K185" s="40"/>
-      <c r="L185" s="40"/>
-      <c r="M185" s="40"/>
-      <c r="N185" s="40"/>
-      <c r="O185" s="40"/>
-      <c r="P185" s="40"/>
-      <c r="Q185" s="40"/>
-      <c r="R185" s="40"/>
-      <c r="S185" s="40"/>
-      <c r="T185" s="40"/>
-      <c r="U185" s="41"/>
+      <c r="H185" s="51"/>
+      <c r="I185" s="59"/>
+      <c r="J185" s="59"/>
+      <c r="K185" s="59"/>
+      <c r="L185" s="59"/>
+      <c r="M185" s="59"/>
+      <c r="N185" s="59"/>
+      <c r="O185" s="59"/>
+      <c r="P185" s="59"/>
+      <c r="Q185" s="59"/>
+      <c r="R185" s="59"/>
+      <c r="S185" s="59"/>
+      <c r="T185" s="59"/>
+      <c r="U185" s="52"/>
     </row>
     <row r="186" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A186" s="30"/>
@@ -15123,20 +15123,20 @@
       <c r="E186" s="31"/>
       <c r="F186" s="31"/>
       <c r="G186" s="31"/>
-      <c r="H186" s="39"/>
-      <c r="I186" s="40"/>
-      <c r="J186" s="40"/>
-      <c r="K186" s="40"/>
-      <c r="L186" s="40"/>
-      <c r="M186" s="40"/>
-      <c r="N186" s="40"/>
-      <c r="O186" s="40"/>
-      <c r="P186" s="40"/>
-      <c r="Q186" s="40"/>
-      <c r="R186" s="40"/>
-      <c r="S186" s="40"/>
-      <c r="T186" s="40"/>
-      <c r="U186" s="41"/>
+      <c r="H186" s="51"/>
+      <c r="I186" s="59"/>
+      <c r="J186" s="59"/>
+      <c r="K186" s="59"/>
+      <c r="L186" s="59"/>
+      <c r="M186" s="59"/>
+      <c r="N186" s="59"/>
+      <c r="O186" s="59"/>
+      <c r="P186" s="59"/>
+      <c r="Q186" s="59"/>
+      <c r="R186" s="59"/>
+      <c r="S186" s="59"/>
+      <c r="T186" s="59"/>
+      <c r="U186" s="52"/>
     </row>
     <row r="187" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" s="30"/>
@@ -15152,20 +15152,20 @@
       <c r="E187" s="31"/>
       <c r="F187" s="31"/>
       <c r="G187" s="31"/>
-      <c r="H187" s="39"/>
-      <c r="I187" s="40"/>
-      <c r="J187" s="40"/>
-      <c r="K187" s="40"/>
-      <c r="L187" s="40"/>
-      <c r="M187" s="40"/>
-      <c r="N187" s="40"/>
-      <c r="O187" s="40"/>
-      <c r="P187" s="40"/>
-      <c r="Q187" s="40"/>
-      <c r="R187" s="40"/>
-      <c r="S187" s="40"/>
-      <c r="T187" s="40"/>
-      <c r="U187" s="41"/>
+      <c r="H187" s="51"/>
+      <c r="I187" s="59"/>
+      <c r="J187" s="59"/>
+      <c r="K187" s="59"/>
+      <c r="L187" s="59"/>
+      <c r="M187" s="59"/>
+      <c r="N187" s="59"/>
+      <c r="O187" s="59"/>
+      <c r="P187" s="59"/>
+      <c r="Q187" s="59"/>
+      <c r="R187" s="59"/>
+      <c r="S187" s="59"/>
+      <c r="T187" s="59"/>
+      <c r="U187" s="52"/>
     </row>
     <row r="188" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" s="30"/>
@@ -15181,20 +15181,20 @@
       <c r="E188" s="31"/>
       <c r="F188" s="31"/>
       <c r="G188" s="31"/>
-      <c r="H188" s="39"/>
-      <c r="I188" s="40"/>
-      <c r="J188" s="40"/>
-      <c r="K188" s="40"/>
-      <c r="L188" s="40"/>
-      <c r="M188" s="40"/>
-      <c r="N188" s="40"/>
-      <c r="O188" s="40"/>
-      <c r="P188" s="40"/>
-      <c r="Q188" s="40"/>
-      <c r="R188" s="40"/>
-      <c r="S188" s="40"/>
-      <c r="T188" s="40"/>
-      <c r="U188" s="41"/>
+      <c r="H188" s="51"/>
+      <c r="I188" s="59"/>
+      <c r="J188" s="59"/>
+      <c r="K188" s="59"/>
+      <c r="L188" s="59"/>
+      <c r="M188" s="59"/>
+      <c r="N188" s="59"/>
+      <c r="O188" s="59"/>
+      <c r="P188" s="59"/>
+      <c r="Q188" s="59"/>
+      <c r="R188" s="59"/>
+      <c r="S188" s="59"/>
+      <c r="T188" s="59"/>
+      <c r="U188" s="52"/>
     </row>
     <row r="189" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A189" s="30"/>
@@ -15210,20 +15210,20 @@
       <c r="E189" s="31"/>
       <c r="F189" s="31"/>
       <c r="G189" s="31"/>
-      <c r="H189" s="39"/>
-      <c r="I189" s="40"/>
-      <c r="J189" s="40"/>
-      <c r="K189" s="40"/>
-      <c r="L189" s="40"/>
-      <c r="M189" s="40"/>
-      <c r="N189" s="40"/>
-      <c r="O189" s="40"/>
-      <c r="P189" s="40"/>
-      <c r="Q189" s="40"/>
-      <c r="R189" s="40"/>
-      <c r="S189" s="40"/>
-      <c r="T189" s="40"/>
-      <c r="U189" s="41"/>
+      <c r="H189" s="51"/>
+      <c r="I189" s="59"/>
+      <c r="J189" s="59"/>
+      <c r="K189" s="59"/>
+      <c r="L189" s="59"/>
+      <c r="M189" s="59"/>
+      <c r="N189" s="59"/>
+      <c r="O189" s="59"/>
+      <c r="P189" s="59"/>
+      <c r="Q189" s="59"/>
+      <c r="R189" s="59"/>
+      <c r="S189" s="59"/>
+      <c r="T189" s="59"/>
+      <c r="U189" s="52"/>
     </row>
     <row r="190" spans="1:35" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A190" s="30"/>
@@ -15239,20 +15239,20 @@
       <c r="E190" s="31"/>
       <c r="F190" s="31"/>
       <c r="G190" s="31"/>
-      <c r="H190" s="39"/>
-      <c r="I190" s="40"/>
-      <c r="J190" s="40"/>
-      <c r="K190" s="40"/>
-      <c r="L190" s="40"/>
-      <c r="M190" s="40"/>
-      <c r="N190" s="40"/>
-      <c r="O190" s="40"/>
-      <c r="P190" s="40"/>
-      <c r="Q190" s="40"/>
-      <c r="R190" s="40"/>
-      <c r="S190" s="40"/>
-      <c r="T190" s="40"/>
-      <c r="U190" s="41"/>
+      <c r="H190" s="51"/>
+      <c r="I190" s="59"/>
+      <c r="J190" s="59"/>
+      <c r="K190" s="59"/>
+      <c r="L190" s="59"/>
+      <c r="M190" s="59"/>
+      <c r="N190" s="59"/>
+      <c r="O190" s="59"/>
+      <c r="P190" s="59"/>
+      <c r="Q190" s="59"/>
+      <c r="R190" s="59"/>
+      <c r="S190" s="59"/>
+      <c r="T190" s="59"/>
+      <c r="U190" s="52"/>
     </row>
     <row r="191" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A191" s="30"/>
@@ -15268,20 +15268,20 @@
       <c r="E191" s="31"/>
       <c r="F191" s="31"/>
       <c r="G191" s="31"/>
-      <c r="H191" s="39"/>
-      <c r="I191" s="40"/>
-      <c r="J191" s="40"/>
-      <c r="K191" s="40"/>
-      <c r="L191" s="40"/>
-      <c r="M191" s="40"/>
-      <c r="N191" s="40"/>
-      <c r="O191" s="40"/>
-      <c r="P191" s="40"/>
-      <c r="Q191" s="40"/>
-      <c r="R191" s="40"/>
-      <c r="S191" s="40"/>
-      <c r="T191" s="40"/>
-      <c r="U191" s="41"/>
+      <c r="H191" s="51"/>
+      <c r="I191" s="59"/>
+      <c r="J191" s="59"/>
+      <c r="K191" s="59"/>
+      <c r="L191" s="59"/>
+      <c r="M191" s="59"/>
+      <c r="N191" s="59"/>
+      <c r="O191" s="59"/>
+      <c r="P191" s="59"/>
+      <c r="Q191" s="59"/>
+      <c r="R191" s="59"/>
+      <c r="S191" s="59"/>
+      <c r="T191" s="59"/>
+      <c r="U191" s="52"/>
     </row>
     <row r="192" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" s="30"/>
@@ -15297,20 +15297,20 @@
       <c r="E192" s="31"/>
       <c r="F192" s="31"/>
       <c r="G192" s="31"/>
-      <c r="H192" s="39"/>
-      <c r="I192" s="40"/>
-      <c r="J192" s="40"/>
-      <c r="K192" s="40"/>
-      <c r="L192" s="40"/>
-      <c r="M192" s="40"/>
-      <c r="N192" s="40"/>
-      <c r="O192" s="40"/>
-      <c r="P192" s="40"/>
-      <c r="Q192" s="40"/>
-      <c r="R192" s="40"/>
-      <c r="S192" s="40"/>
-      <c r="T192" s="40"/>
-      <c r="U192" s="41"/>
+      <c r="H192" s="51"/>
+      <c r="I192" s="59"/>
+      <c r="J192" s="59"/>
+      <c r="K192" s="59"/>
+      <c r="L192" s="59"/>
+      <c r="M192" s="59"/>
+      <c r="N192" s="59"/>
+      <c r="O192" s="59"/>
+      <c r="P192" s="59"/>
+      <c r="Q192" s="59"/>
+      <c r="R192" s="59"/>
+      <c r="S192" s="59"/>
+      <c r="T192" s="59"/>
+      <c r="U192" s="52"/>
     </row>
     <row r="193" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="30"/>
@@ -15326,22 +15326,22 @@
       <c r="E193" s="31"/>
       <c r="F193" s="31"/>
       <c r="G193" s="31"/>
-      <c r="H193" s="39" t="s">
+      <c r="H193" s="51" t="s">
         <v>770</v>
       </c>
-      <c r="I193" s="40"/>
-      <c r="J193" s="40"/>
-      <c r="K193" s="40"/>
-      <c r="L193" s="40"/>
-      <c r="M193" s="40"/>
-      <c r="N193" s="40"/>
-      <c r="O193" s="40"/>
-      <c r="P193" s="40"/>
-      <c r="Q193" s="40"/>
-      <c r="R193" s="40"/>
-      <c r="S193" s="40"/>
-      <c r="T193" s="40"/>
-      <c r="U193" s="41"/>
+      <c r="I193" s="59"/>
+      <c r="J193" s="59"/>
+      <c r="K193" s="59"/>
+      <c r="L193" s="59"/>
+      <c r="M193" s="59"/>
+      <c r="N193" s="59"/>
+      <c r="O193" s="59"/>
+      <c r="P193" s="59"/>
+      <c r="Q193" s="59"/>
+      <c r="R193" s="59"/>
+      <c r="S193" s="59"/>
+      <c r="T193" s="59"/>
+      <c r="U193" s="52"/>
     </row>
     <row r="194" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" s="30"/>
@@ -15357,20 +15357,20 @@
       <c r="E194" s="31"/>
       <c r="F194" s="31"/>
       <c r="G194" s="31"/>
-      <c r="H194" s="39"/>
-      <c r="I194" s="40"/>
-      <c r="J194" s="40"/>
-      <c r="K194" s="40"/>
-      <c r="L194" s="40"/>
-      <c r="M194" s="40"/>
-      <c r="N194" s="40"/>
-      <c r="O194" s="40"/>
-      <c r="P194" s="40"/>
-      <c r="Q194" s="40"/>
-      <c r="R194" s="40"/>
-      <c r="S194" s="40"/>
-      <c r="T194" s="40"/>
-      <c r="U194" s="41"/>
+      <c r="H194" s="51"/>
+      <c r="I194" s="59"/>
+      <c r="J194" s="59"/>
+      <c r="K194" s="59"/>
+      <c r="L194" s="59"/>
+      <c r="M194" s="59"/>
+      <c r="N194" s="59"/>
+      <c r="O194" s="59"/>
+      <c r="P194" s="59"/>
+      <c r="Q194" s="59"/>
+      <c r="R194" s="59"/>
+      <c r="S194" s="59"/>
+      <c r="T194" s="59"/>
+      <c r="U194" s="52"/>
     </row>
     <row r="195" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A195" s="30"/>
@@ -15384,20 +15384,20 @@
       <c r="E195" s="31"/>
       <c r="F195" s="31"/>
       <c r="G195" s="31"/>
-      <c r="H195" s="39"/>
-      <c r="I195" s="40"/>
-      <c r="J195" s="40"/>
-      <c r="K195" s="40"/>
-      <c r="L195" s="40"/>
-      <c r="M195" s="40"/>
-      <c r="N195" s="40"/>
-      <c r="O195" s="40"/>
-      <c r="P195" s="40"/>
-      <c r="Q195" s="40"/>
-      <c r="R195" s="40"/>
-      <c r="S195" s="40"/>
-      <c r="T195" s="40"/>
-      <c r="U195" s="41"/>
+      <c r="H195" s="51"/>
+      <c r="I195" s="59"/>
+      <c r="J195" s="59"/>
+      <c r="K195" s="59"/>
+      <c r="L195" s="59"/>
+      <c r="M195" s="59"/>
+      <c r="N195" s="59"/>
+      <c r="O195" s="59"/>
+      <c r="P195" s="59"/>
+      <c r="Q195" s="59"/>
+      <c r="R195" s="59"/>
+      <c r="S195" s="59"/>
+      <c r="T195" s="59"/>
+      <c r="U195" s="52"/>
     </row>
     <row r="196" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" s="30"/>
@@ -15411,20 +15411,20 @@
       <c r="E196" s="31"/>
       <c r="F196" s="31"/>
       <c r="G196" s="31"/>
-      <c r="H196" s="39"/>
-      <c r="I196" s="40"/>
-      <c r="J196" s="40"/>
-      <c r="K196" s="40"/>
-      <c r="L196" s="40"/>
-      <c r="M196" s="40"/>
-      <c r="N196" s="40"/>
-      <c r="O196" s="40"/>
-      <c r="P196" s="40"/>
-      <c r="Q196" s="40"/>
-      <c r="R196" s="40"/>
-      <c r="S196" s="40"/>
-      <c r="T196" s="40"/>
-      <c r="U196" s="41"/>
+      <c r="H196" s="51"/>
+      <c r="I196" s="59"/>
+      <c r="J196" s="59"/>
+      <c r="K196" s="59"/>
+      <c r="L196" s="59"/>
+      <c r="M196" s="59"/>
+      <c r="N196" s="59"/>
+      <c r="O196" s="59"/>
+      <c r="P196" s="59"/>
+      <c r="Q196" s="59"/>
+      <c r="R196" s="59"/>
+      <c r="S196" s="59"/>
+      <c r="T196" s="59"/>
+      <c r="U196" s="52"/>
     </row>
     <row r="197" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" s="30"/>
@@ -15438,25 +15438,68 @@
       <c r="E197" s="31"/>
       <c r="F197" s="31"/>
       <c r="G197" s="31"/>
-      <c r="H197" s="39"/>
-      <c r="I197" s="40"/>
-      <c r="J197" s="40"/>
-      <c r="K197" s="40"/>
-      <c r="L197" s="40"/>
-      <c r="M197" s="40"/>
-      <c r="N197" s="40"/>
-      <c r="O197" s="40"/>
-      <c r="P197" s="40"/>
-      <c r="Q197" s="40"/>
-      <c r="R197" s="40"/>
-      <c r="S197" s="40"/>
-      <c r="T197" s="40"/>
-      <c r="U197" s="41"/>
+      <c r="H197" s="51"/>
+      <c r="I197" s="59"/>
+      <c r="J197" s="59"/>
+      <c r="K197" s="59"/>
+      <c r="L197" s="59"/>
+      <c r="M197" s="59"/>
+      <c r="N197" s="59"/>
+      <c r="O197" s="59"/>
+      <c r="P197" s="59"/>
+      <c r="Q197" s="59"/>
+      <c r="R197" s="59"/>
+      <c r="S197" s="59"/>
+      <c r="T197" s="59"/>
+      <c r="U197" s="52"/>
     </row>
   </sheetData>
   <sheetProtection password="C644" sheet="1" formatColumns="0" autoFilter="0"/>
   <autoFilter ref="A7:U7"/>
   <mergeCells count="59">
+    <mergeCell ref="H195:U195"/>
+    <mergeCell ref="H196:U196"/>
+    <mergeCell ref="H197:U197"/>
+    <mergeCell ref="H190:U190"/>
+    <mergeCell ref="H191:U191"/>
+    <mergeCell ref="H192:U192"/>
+    <mergeCell ref="H193:U193"/>
+    <mergeCell ref="H194:U194"/>
+    <mergeCell ref="H185:U185"/>
+    <mergeCell ref="H186:U186"/>
+    <mergeCell ref="H187:U187"/>
+    <mergeCell ref="H188:U188"/>
+    <mergeCell ref="H189:U189"/>
+    <mergeCell ref="H180:U180"/>
+    <mergeCell ref="H181:U181"/>
+    <mergeCell ref="H182:U182"/>
+    <mergeCell ref="H183:U183"/>
+    <mergeCell ref="H184:U184"/>
+    <mergeCell ref="C148:I148"/>
+    <mergeCell ref="C149:I149"/>
+    <mergeCell ref="C153:I153"/>
+    <mergeCell ref="C169:I169"/>
+    <mergeCell ref="A179:U179"/>
+    <mergeCell ref="C45:I45"/>
+    <mergeCell ref="C66:I66"/>
+    <mergeCell ref="C67:I67"/>
+    <mergeCell ref="C97:I97"/>
+    <mergeCell ref="C128:I128"/>
+    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="C12:I12"/>
+    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="C37:I37"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="R6:R7"/>
     <mergeCell ref="A2:U2"/>
     <mergeCell ref="A3:U3"/>
     <mergeCell ref="A4:U4"/>
@@ -15473,49 +15516,6 @@
     <mergeCell ref="H5:H7"/>
     <mergeCell ref="I5:I7"/>
     <mergeCell ref="J6:K6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="U6:U7"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="O6:O7"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="R6:R7"/>
-    <mergeCell ref="C11:I11"/>
-    <mergeCell ref="C12:I12"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="C14:I14"/>
-    <mergeCell ref="C37:I37"/>
-    <mergeCell ref="C45:I45"/>
-    <mergeCell ref="C66:I66"/>
-    <mergeCell ref="C67:I67"/>
-    <mergeCell ref="C97:I97"/>
-    <mergeCell ref="C128:I128"/>
-    <mergeCell ref="C148:I148"/>
-    <mergeCell ref="C149:I149"/>
-    <mergeCell ref="C153:I153"/>
-    <mergeCell ref="C169:I169"/>
-    <mergeCell ref="A179:U179"/>
-    <mergeCell ref="H180:U180"/>
-    <mergeCell ref="H181:U181"/>
-    <mergeCell ref="H182:U182"/>
-    <mergeCell ref="H183:U183"/>
-    <mergeCell ref="H184:U184"/>
-    <mergeCell ref="H185:U185"/>
-    <mergeCell ref="H186:U186"/>
-    <mergeCell ref="H187:U187"/>
-    <mergeCell ref="H188:U188"/>
-    <mergeCell ref="H189:U189"/>
-    <mergeCell ref="H195:U195"/>
-    <mergeCell ref="H196:U196"/>
-    <mergeCell ref="H197:U197"/>
-    <mergeCell ref="H190:U190"/>
-    <mergeCell ref="H191:U191"/>
-    <mergeCell ref="H192:U192"/>
-    <mergeCell ref="H193:U193"/>
-    <mergeCell ref="H194:U194"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15532,7 +15532,7 @@
     <col min="4" max="4" width="17" customWidth="1"/>
     <col min="5" max="5" width="39.5703125" customWidth="1"/>
     <col min="6" max="7" width="16.42578125" customWidth="1"/>
-    <col min="8" max="8" width="5.85546875" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" customWidth="1"/>
     <col min="9" max="9" width="16.85546875" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
@@ -15605,79 +15605,79 @@
       </c>
     </row>
     <row r="2" spans="1:35" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="50"/>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="50"/>
-      <c r="R2" s="50"/>
-      <c r="S2" s="50"/>
-      <c r="T2" s="50"/>
-      <c r="U2" s="50"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
+      <c r="O2" s="39"/>
+      <c r="P2" s="39"/>
+      <c r="Q2" s="39"/>
+      <c r="R2" s="39"/>
+      <c r="S2" s="39"/>
+      <c r="T2" s="39"/>
+      <c r="U2" s="39"/>
     </row>
     <row r="3" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="51"/>
-      <c r="N3" s="51"/>
-      <c r="O3" s="51"/>
-      <c r="P3" s="51"/>
-      <c r="Q3" s="51"/>
-      <c r="R3" s="51"/>
-      <c r="S3" s="51"/>
-      <c r="T3" s="51"/>
-      <c r="U3" s="51"/>
+      <c r="B3" s="40"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40"/>
+      <c r="S3" s="40"/>
+      <c r="T3" s="40"/>
+      <c r="U3" s="40"/>
     </row>
     <row r="4" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="52"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="52"/>
-      <c r="N4" s="52"/>
-      <c r="O4" s="52"/>
-      <c r="P4" s="52"/>
-      <c r="Q4" s="52"/>
-      <c r="R4" s="52"/>
-      <c r="S4" s="52"/>
-      <c r="T4" s="52"/>
-      <c r="U4" s="52"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="41"/>
+      <c r="P4" s="41"/>
+      <c r="Q4" s="41"/>
+      <c r="R4" s="41"/>
+      <c r="S4" s="41"/>
+      <c r="T4" s="41"/>
+      <c r="U4" s="41"/>
     </row>
     <row r="5" spans="1:35" ht="40.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="48" t="s">
@@ -15707,115 +15707,115 @@
       <c r="I5" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J5" s="53" t="s">
+      <c r="J5" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="54"/>
-      <c r="L5" s="54"/>
-      <c r="M5" s="54"/>
-      <c r="N5" s="54"/>
-      <c r="O5" s="55"/>
-      <c r="P5" s="56" t="s">
+      <c r="K5" s="43"/>
+      <c r="L5" s="43"/>
+      <c r="M5" s="43"/>
+      <c r="N5" s="43"/>
+      <c r="O5" s="44"/>
+      <c r="P5" s="45" t="s">
         <v>780</v>
       </c>
-      <c r="Q5" s="57"/>
-      <c r="R5" s="58"/>
-      <c r="S5" s="56">
+      <c r="Q5" s="46"/>
+      <c r="R5" s="47"/>
+      <c r="S5" s="45">
         <v>9701212867</v>
       </c>
-      <c r="T5" s="57"/>
-      <c r="U5" s="58"/>
+      <c r="T5" s="46"/>
+      <c r="U5" s="47"/>
     </row>
     <row r="6" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="59"/>
-      <c r="B6" s="59"/>
-      <c r="C6" s="59"/>
-      <c r="D6" s="59"/>
-      <c r="E6" s="59"/>
-      <c r="F6" s="59"/>
-      <c r="G6" s="59"/>
-      <c r="H6" s="59"/>
-      <c r="I6" s="59"/>
-      <c r="J6" s="39" t="s">
+      <c r="A6" s="49"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="41"/>
+      <c r="K6" s="52"/>
       <c r="L6" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="M6" s="39" t="s">
+      <c r="M6" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="N6" s="41"/>
+      <c r="N6" s="52"/>
       <c r="O6" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="P6" s="39" t="s">
+      <c r="P6" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="Q6" s="41"/>
+      <c r="Q6" s="52"/>
       <c r="R6" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="S6" s="39" t="s">
+      <c r="S6" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="T6" s="41"/>
+      <c r="T6" s="52"/>
       <c r="U6" s="48" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:35" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="49"/>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
+      <c r="A7" s="50"/>
+      <c r="B7" s="50"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="50"/>
+      <c r="H7" s="50"/>
+      <c r="I7" s="50"/>
       <c r="J7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L7" s="49"/>
+      <c r="L7" s="50"/>
       <c r="M7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="O7" s="49"/>
+      <c r="O7" s="50"/>
       <c r="P7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="R7" s="49"/>
+      <c r="R7" s="50"/>
       <c r="S7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="T7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="U7" s="49"/>
+      <c r="U7" s="50"/>
     </row>
     <row r="8" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="45" t="s">
+      <c r="A8" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="46"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="46"/>
-      <c r="F8" s="46"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="47"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="55"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -15869,15 +15869,15 @@
       <c r="B9" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="42" t="s">
+      <c r="C9" s="56" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="44"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="58"/>
       <c r="M9" s="6">
         <f t="shared" si="0"/>
         <v>21909487.239999998</v>
@@ -15928,15 +15928,15 @@
       <c r="B10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="44"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="58"/>
       <c r="M10" s="6">
         <f t="shared" si="0"/>
         <v>21909487.239999998</v>
@@ -15987,15 +15987,15 @@
       <c r="B11" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="42" t="s">
+      <c r="C11" s="56" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="43"/>
-      <c r="I11" s="44"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="58"/>
       <c r="M11" s="6">
         <f t="shared" si="0"/>
         <v>21909487.239999998</v>
@@ -16046,15 +16046,15 @@
       <c r="B12" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="42" t="s">
+      <c r="C12" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="44"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="58"/>
       <c r="M12" s="6">
         <f>SUM(M13,M66,M148,M169)</f>
         <v>21909487.239999998</v>
@@ -16105,15 +16105,15 @@
       <c r="B13" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="42" t="s">
+      <c r="C13" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="44"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="58"/>
       <c r="M13" s="6">
         <f>SUM(M14,M37,M45)</f>
         <v>3561291.31</v>
@@ -16164,15 +16164,15 @@
       <c r="B14" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="42" t="s">
+      <c r="C14" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="44"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="58"/>
       <c r="M14" s="6">
         <f>SUM(M15,M19,M21,M29)</f>
         <v>2618573.91</v>
@@ -16920,10 +16920,10 @@
       <c r="C25" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="D25" s="62" t="s">
+      <c r="D25" s="60" t="s">
         <v>781</v>
       </c>
-      <c r="E25" s="60" t="s">
+      <c r="E25" s="62" t="s">
         <v>784</v>
       </c>
       <c r="F25" s="18" t="s">
@@ -16976,8 +16976,8 @@
       <c r="C26" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="D26" s="63"/>
-      <c r="E26" s="61"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="63"/>
       <c r="F26" s="18" t="s">
         <v>79</v>
       </c>
@@ -17404,10 +17404,10 @@
       <c r="C33" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="D33" s="62" t="s">
+      <c r="D33" s="60" t="s">
         <v>781</v>
       </c>
-      <c r="E33" s="60" t="s">
+      <c r="E33" s="62" t="s">
         <v>784</v>
       </c>
       <c r="F33" s="18" t="s">
@@ -17463,8 +17463,8 @@
       <c r="C34" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="D34" s="63"/>
-      <c r="E34" s="61"/>
+      <c r="D34" s="61"/>
+      <c r="E34" s="63"/>
       <c r="F34" s="18" t="s">
         <v>79</v>
       </c>
@@ -17621,15 +17621,15 @@
       <c r="B37" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="C37" s="42" t="s">
+      <c r="C37" s="56" t="s">
         <v>154</v>
       </c>
-      <c r="D37" s="43"/>
-      <c r="E37" s="43"/>
-      <c r="F37" s="43"/>
-      <c r="G37" s="43"/>
-      <c r="H37" s="43"/>
-      <c r="I37" s="44"/>
+      <c r="D37" s="57"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="57"/>
+      <c r="H37" s="57"/>
+      <c r="I37" s="58"/>
       <c r="M37" s="6">
         <f>SUM(M38,M41,M43)</f>
         <v>122933.90000000001</v>
@@ -18214,15 +18214,15 @@
       <c r="B45" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="C45" s="42" t="s">
+      <c r="C45" s="56" t="s">
         <v>193</v>
       </c>
-      <c r="D45" s="43"/>
-      <c r="E45" s="43"/>
-      <c r="F45" s="43"/>
-      <c r="G45" s="43"/>
-      <c r="H45" s="43"/>
-      <c r="I45" s="44"/>
+      <c r="D45" s="57"/>
+      <c r="E45" s="57"/>
+      <c r="F45" s="57"/>
+      <c r="G45" s="57"/>
+      <c r="H45" s="57"/>
+      <c r="I45" s="58"/>
       <c r="M45" s="6">
         <f>SUM(M46,M51,M55,M60,M63)</f>
         <v>819783.5</v>
@@ -19620,15 +19620,15 @@
       <c r="B66" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="C66" s="42" t="s">
+      <c r="C66" s="56" t="s">
         <v>299</v>
       </c>
-      <c r="D66" s="43"/>
-      <c r="E66" s="43"/>
-      <c r="F66" s="43"/>
-      <c r="G66" s="43"/>
-      <c r="H66" s="43"/>
-      <c r="I66" s="44"/>
+      <c r="D66" s="57"/>
+      <c r="E66" s="57"/>
+      <c r="F66" s="57"/>
+      <c r="G66" s="57"/>
+      <c r="H66" s="57"/>
+      <c r="I66" s="58"/>
       <c r="M66" s="6">
         <f>SUM(M67,M97,M128)</f>
         <v>4332566.72</v>
@@ -19679,15 +19679,15 @@
       <c r="B67" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="C67" s="42" t="s">
+      <c r="C67" s="56" t="s">
         <v>302</v>
       </c>
-      <c r="D67" s="43"/>
-      <c r="E67" s="43"/>
-      <c r="F67" s="43"/>
-      <c r="G67" s="43"/>
-      <c r="H67" s="43"/>
-      <c r="I67" s="44"/>
+      <c r="D67" s="57"/>
+      <c r="E67" s="57"/>
+      <c r="F67" s="57"/>
+      <c r="G67" s="57"/>
+      <c r="H67" s="57"/>
+      <c r="I67" s="58"/>
       <c r="M67" s="6">
         <f>SUM(M68,M71,M75,M79,M82,M85,M89,M92)</f>
         <v>2963619.5900000003</v>
@@ -20114,7 +20114,10 @@
         <v>330</v>
       </c>
       <c r="D73" s="12"/>
-      <c r="E73" s="12"/>
+      <c r="E73" s="12">
+        <f>I74/G74/I73</f>
+        <v>28.571428571428573</v>
+      </c>
       <c r="F73" s="18" t="s">
         <v>67</v>
       </c>
@@ -20394,7 +20397,10 @@
         <v>217</v>
       </c>
       <c r="D77" s="12"/>
-      <c r="E77" s="12"/>
+      <c r="E77" s="12">
+        <f>I76/I75</f>
+        <v>32.510320205288409</v>
+      </c>
       <c r="F77" s="18" t="s">
         <v>61</v>
       </c>
@@ -21733,15 +21739,15 @@
       <c r="B97" s="10" t="s">
         <v>419</v>
       </c>
-      <c r="C97" s="42" t="s">
+      <c r="C97" s="56" t="s">
         <v>420</v>
       </c>
-      <c r="D97" s="43"/>
-      <c r="E97" s="43"/>
-      <c r="F97" s="43"/>
-      <c r="G97" s="43"/>
-      <c r="H97" s="43"/>
-      <c r="I97" s="44"/>
+      <c r="D97" s="57"/>
+      <c r="E97" s="57"/>
+      <c r="F97" s="57"/>
+      <c r="G97" s="57"/>
+      <c r="H97" s="57"/>
+      <c r="I97" s="58"/>
       <c r="M97" s="6">
         <f>SUM(M98,M107,M110,M113,M116,M119,M122,M125)</f>
         <v>1187256.6599999997</v>
@@ -23820,15 +23826,15 @@
       <c r="B128" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="C128" s="42" t="s">
+      <c r="C128" s="56" t="s">
         <v>534</v>
       </c>
-      <c r="D128" s="43"/>
-      <c r="E128" s="43"/>
-      <c r="F128" s="43"/>
-      <c r="G128" s="43"/>
-      <c r="H128" s="43"/>
-      <c r="I128" s="44"/>
+      <c r="D128" s="57"/>
+      <c r="E128" s="57"/>
+      <c r="F128" s="57"/>
+      <c r="G128" s="57"/>
+      <c r="H128" s="57"/>
+      <c r="I128" s="58"/>
       <c r="M128" s="6">
         <f>SUM(M129,M132,M135,M138,M143)</f>
         <v>181690.47</v>
@@ -25151,15 +25157,15 @@
       <c r="B148" s="10" t="s">
         <v>616</v>
       </c>
-      <c r="C148" s="42" t="s">
+      <c r="C148" s="56" t="s">
         <v>617</v>
       </c>
-      <c r="D148" s="43"/>
-      <c r="E148" s="43"/>
-      <c r="F148" s="43"/>
-      <c r="G148" s="43"/>
-      <c r="H148" s="43"/>
-      <c r="I148" s="44"/>
+      <c r="D148" s="57"/>
+      <c r="E148" s="57"/>
+      <c r="F148" s="57"/>
+      <c r="G148" s="57"/>
+      <c r="H148" s="57"/>
+      <c r="I148" s="58"/>
       <c r="M148" s="6">
         <f>SUM(M149,M153)</f>
         <v>447303.98</v>
@@ -25210,15 +25216,15 @@
       <c r="B149" s="10" t="s">
         <v>619</v>
       </c>
-      <c r="C149" s="42" t="s">
+      <c r="C149" s="56" t="s">
         <v>620</v>
       </c>
-      <c r="D149" s="43"/>
-      <c r="E149" s="43"/>
-      <c r="F149" s="43"/>
-      <c r="G149" s="43"/>
-      <c r="H149" s="43"/>
-      <c r="I149" s="44"/>
+      <c r="D149" s="57"/>
+      <c r="E149" s="57"/>
+      <c r="F149" s="57"/>
+      <c r="G149" s="57"/>
+      <c r="H149" s="57"/>
+      <c r="I149" s="58"/>
       <c r="M149" s="6">
         <f>SUM(M150)</f>
         <v>241468.92</v>
@@ -25481,15 +25487,15 @@
       <c r="B153" s="10" t="s">
         <v>635</v>
       </c>
-      <c r="C153" s="42" t="s">
+      <c r="C153" s="56" t="s">
         <v>636</v>
       </c>
-      <c r="D153" s="43"/>
-      <c r="E153" s="43"/>
-      <c r="F153" s="43"/>
-      <c r="G153" s="43"/>
-      <c r="H153" s="43"/>
-      <c r="I153" s="44"/>
+      <c r="D153" s="57"/>
+      <c r="E153" s="57"/>
+      <c r="F153" s="57"/>
+      <c r="G153" s="57"/>
+      <c r="H153" s="57"/>
+      <c r="I153" s="58"/>
       <c r="M153" s="6">
         <f>SUM(M154,M157,M160,M163,M166)</f>
         <v>205835.06</v>
@@ -26612,15 +26618,15 @@
       <c r="B169" s="10" t="s">
         <v>683</v>
       </c>
-      <c r="C169" s="42" t="s">
+      <c r="C169" s="56" t="s">
         <v>684</v>
       </c>
-      <c r="D169" s="43"/>
-      <c r="E169" s="43"/>
-      <c r="F169" s="43"/>
-      <c r="G169" s="43"/>
-      <c r="H169" s="43"/>
-      <c r="I169" s="44"/>
+      <c r="D169" s="57"/>
+      <c r="E169" s="57"/>
+      <c r="F169" s="57"/>
+      <c r="G169" s="57"/>
+      <c r="H169" s="57"/>
+      <c r="I169" s="58"/>
       <c r="M169" s="6">
         <f>SUM(M170,M173,M177)</f>
         <v>13568325.229999999</v>
@@ -27298,29 +27304,29 @@
       </c>
     </row>
     <row r="179" spans="1:35" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A179" s="45" t="s">
+      <c r="A179" s="53" t="s">
         <v>728</v>
       </c>
-      <c r="B179" s="46"/>
-      <c r="C179" s="46"/>
-      <c r="D179" s="46"/>
-      <c r="E179" s="46"/>
-      <c r="F179" s="46"/>
-      <c r="G179" s="46"/>
-      <c r="H179" s="46"/>
-      <c r="I179" s="46"/>
-      <c r="J179" s="46"/>
-      <c r="K179" s="46"/>
-      <c r="L179" s="46"/>
-      <c r="M179" s="46"/>
-      <c r="N179" s="46"/>
-      <c r="O179" s="46"/>
-      <c r="P179" s="46"/>
-      <c r="Q179" s="46"/>
-      <c r="R179" s="46"/>
-      <c r="S179" s="46"/>
-      <c r="T179" s="46"/>
-      <c r="U179" s="47"/>
+      <c r="B179" s="54"/>
+      <c r="C179" s="54"/>
+      <c r="D179" s="54"/>
+      <c r="E179" s="54"/>
+      <c r="F179" s="54"/>
+      <c r="G179" s="54"/>
+      <c r="H179" s="54"/>
+      <c r="I179" s="54"/>
+      <c r="J179" s="54"/>
+      <c r="K179" s="54"/>
+      <c r="L179" s="54"/>
+      <c r="M179" s="54"/>
+      <c r="N179" s="54"/>
+      <c r="O179" s="54"/>
+      <c r="P179" s="54"/>
+      <c r="Q179" s="54"/>
+      <c r="R179" s="54"/>
+      <c r="S179" s="54"/>
+      <c r="T179" s="54"/>
+      <c r="U179" s="55"/>
     </row>
     <row r="180" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="30"/>
@@ -27336,20 +27342,20 @@
       <c r="E180" s="31"/>
       <c r="F180" s="31"/>
       <c r="G180" s="31"/>
-      <c r="H180" s="39"/>
-      <c r="I180" s="40"/>
-      <c r="J180" s="40"/>
-      <c r="K180" s="40"/>
-      <c r="L180" s="40"/>
-      <c r="M180" s="40"/>
-      <c r="N180" s="40"/>
-      <c r="O180" s="40"/>
-      <c r="P180" s="40"/>
-      <c r="Q180" s="40"/>
-      <c r="R180" s="40"/>
-      <c r="S180" s="40"/>
-      <c r="T180" s="40"/>
-      <c r="U180" s="41"/>
+      <c r="H180" s="51"/>
+      <c r="I180" s="59"/>
+      <c r="J180" s="59"/>
+      <c r="K180" s="59"/>
+      <c r="L180" s="59"/>
+      <c r="M180" s="59"/>
+      <c r="N180" s="59"/>
+      <c r="O180" s="59"/>
+      <c r="P180" s="59"/>
+      <c r="Q180" s="59"/>
+      <c r="R180" s="59"/>
+      <c r="S180" s="59"/>
+      <c r="T180" s="59"/>
+      <c r="U180" s="52"/>
     </row>
     <row r="181" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="30"/>
@@ -27365,20 +27371,20 @@
       <c r="E181" s="31"/>
       <c r="F181" s="31"/>
       <c r="G181" s="31"/>
-      <c r="H181" s="39"/>
-      <c r="I181" s="40"/>
-      <c r="J181" s="40"/>
-      <c r="K181" s="40"/>
-      <c r="L181" s="40"/>
-      <c r="M181" s="40"/>
-      <c r="N181" s="40"/>
-      <c r="O181" s="40"/>
-      <c r="P181" s="40"/>
-      <c r="Q181" s="40"/>
-      <c r="R181" s="40"/>
-      <c r="S181" s="40"/>
-      <c r="T181" s="40"/>
-      <c r="U181" s="41"/>
+      <c r="H181" s="51"/>
+      <c r="I181" s="59"/>
+      <c r="J181" s="59"/>
+      <c r="K181" s="59"/>
+      <c r="L181" s="59"/>
+      <c r="M181" s="59"/>
+      <c r="N181" s="59"/>
+      <c r="O181" s="59"/>
+      <c r="P181" s="59"/>
+      <c r="Q181" s="59"/>
+      <c r="R181" s="59"/>
+      <c r="S181" s="59"/>
+      <c r="T181" s="59"/>
+      <c r="U181" s="52"/>
     </row>
     <row r="182" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A182" s="30"/>
@@ -27394,20 +27400,20 @@
       <c r="E182" s="31"/>
       <c r="F182" s="31"/>
       <c r="G182" s="31"/>
-      <c r="H182" s="39"/>
-      <c r="I182" s="40"/>
-      <c r="J182" s="40"/>
-      <c r="K182" s="40"/>
-      <c r="L182" s="40"/>
-      <c r="M182" s="40"/>
-      <c r="N182" s="40"/>
-      <c r="O182" s="40"/>
-      <c r="P182" s="40"/>
-      <c r="Q182" s="40"/>
-      <c r="R182" s="40"/>
-      <c r="S182" s="40"/>
-      <c r="T182" s="40"/>
-      <c r="U182" s="41"/>
+      <c r="H182" s="51"/>
+      <c r="I182" s="59"/>
+      <c r="J182" s="59"/>
+      <c r="K182" s="59"/>
+      <c r="L182" s="59"/>
+      <c r="M182" s="59"/>
+      <c r="N182" s="59"/>
+      <c r="O182" s="59"/>
+      <c r="P182" s="59"/>
+      <c r="Q182" s="59"/>
+      <c r="R182" s="59"/>
+      <c r="S182" s="59"/>
+      <c r="T182" s="59"/>
+      <c r="U182" s="52"/>
     </row>
     <row r="183" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="30"/>
@@ -27423,20 +27429,20 @@
       <c r="E183" s="31"/>
       <c r="F183" s="31"/>
       <c r="G183" s="31"/>
-      <c r="H183" s="39"/>
-      <c r="I183" s="40"/>
-      <c r="J183" s="40"/>
-      <c r="K183" s="40"/>
-      <c r="L183" s="40"/>
-      <c r="M183" s="40"/>
-      <c r="N183" s="40"/>
-      <c r="O183" s="40"/>
-      <c r="P183" s="40"/>
-      <c r="Q183" s="40"/>
-      <c r="R183" s="40"/>
-      <c r="S183" s="40"/>
-      <c r="T183" s="40"/>
-      <c r="U183" s="41"/>
+      <c r="H183" s="51"/>
+      <c r="I183" s="59"/>
+      <c r="J183" s="59"/>
+      <c r="K183" s="59"/>
+      <c r="L183" s="59"/>
+      <c r="M183" s="59"/>
+      <c r="N183" s="59"/>
+      <c r="O183" s="59"/>
+      <c r="P183" s="59"/>
+      <c r="Q183" s="59"/>
+      <c r="R183" s="59"/>
+      <c r="S183" s="59"/>
+      <c r="T183" s="59"/>
+      <c r="U183" s="52"/>
     </row>
     <row r="184" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" s="30"/>
@@ -27452,20 +27458,20 @@
       <c r="E184" s="31"/>
       <c r="F184" s="31"/>
       <c r="G184" s="31"/>
-      <c r="H184" s="39"/>
-      <c r="I184" s="40"/>
-      <c r="J184" s="40"/>
-      <c r="K184" s="40"/>
-      <c r="L184" s="40"/>
-      <c r="M184" s="40"/>
-      <c r="N184" s="40"/>
-      <c r="O184" s="40"/>
-      <c r="P184" s="40"/>
-      <c r="Q184" s="40"/>
-      <c r="R184" s="40"/>
-      <c r="S184" s="40"/>
-      <c r="T184" s="40"/>
-      <c r="U184" s="41"/>
+      <c r="H184" s="51"/>
+      <c r="I184" s="59"/>
+      <c r="J184" s="59"/>
+      <c r="K184" s="59"/>
+      <c r="L184" s="59"/>
+      <c r="M184" s="59"/>
+      <c r="N184" s="59"/>
+      <c r="O184" s="59"/>
+      <c r="P184" s="59"/>
+      <c r="Q184" s="59"/>
+      <c r="R184" s="59"/>
+      <c r="S184" s="59"/>
+      <c r="T184" s="59"/>
+      <c r="U184" s="52"/>
     </row>
     <row r="185" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A185" s="30"/>
@@ -27481,20 +27487,20 @@
       <c r="E185" s="31"/>
       <c r="F185" s="31"/>
       <c r="G185" s="31"/>
-      <c r="H185" s="39"/>
-      <c r="I185" s="40"/>
-      <c r="J185" s="40"/>
-      <c r="K185" s="40"/>
-      <c r="L185" s="40"/>
-      <c r="M185" s="40"/>
-      <c r="N185" s="40"/>
-      <c r="O185" s="40"/>
-      <c r="P185" s="40"/>
-      <c r="Q185" s="40"/>
-      <c r="R185" s="40"/>
-      <c r="S185" s="40"/>
-      <c r="T185" s="40"/>
-      <c r="U185" s="41"/>
+      <c r="H185" s="51"/>
+      <c r="I185" s="59"/>
+      <c r="J185" s="59"/>
+      <c r="K185" s="59"/>
+      <c r="L185" s="59"/>
+      <c r="M185" s="59"/>
+      <c r="N185" s="59"/>
+      <c r="O185" s="59"/>
+      <c r="P185" s="59"/>
+      <c r="Q185" s="59"/>
+      <c r="R185" s="59"/>
+      <c r="S185" s="59"/>
+      <c r="T185" s="59"/>
+      <c r="U185" s="52"/>
     </row>
     <row r="186" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A186" s="30"/>
@@ -27510,20 +27516,20 @@
       <c r="E186" s="31"/>
       <c r="F186" s="31"/>
       <c r="G186" s="31"/>
-      <c r="H186" s="39"/>
-      <c r="I186" s="40"/>
-      <c r="J186" s="40"/>
-      <c r="K186" s="40"/>
-      <c r="L186" s="40"/>
-      <c r="M186" s="40"/>
-      <c r="N186" s="40"/>
-      <c r="O186" s="40"/>
-      <c r="P186" s="40"/>
-      <c r="Q186" s="40"/>
-      <c r="R186" s="40"/>
-      <c r="S186" s="40"/>
-      <c r="T186" s="40"/>
-      <c r="U186" s="41"/>
+      <c r="H186" s="51"/>
+      <c r="I186" s="59"/>
+      <c r="J186" s="59"/>
+      <c r="K186" s="59"/>
+      <c r="L186" s="59"/>
+      <c r="M186" s="59"/>
+      <c r="N186" s="59"/>
+      <c r="O186" s="59"/>
+      <c r="P186" s="59"/>
+      <c r="Q186" s="59"/>
+      <c r="R186" s="59"/>
+      <c r="S186" s="59"/>
+      <c r="T186" s="59"/>
+      <c r="U186" s="52"/>
     </row>
     <row r="187" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" s="30"/>
@@ -27539,20 +27545,20 @@
       <c r="E187" s="31"/>
       <c r="F187" s="31"/>
       <c r="G187" s="31"/>
-      <c r="H187" s="39"/>
-      <c r="I187" s="40"/>
-      <c r="J187" s="40"/>
-      <c r="K187" s="40"/>
-      <c r="L187" s="40"/>
-      <c r="M187" s="40"/>
-      <c r="N187" s="40"/>
-      <c r="O187" s="40"/>
-      <c r="P187" s="40"/>
-      <c r="Q187" s="40"/>
-      <c r="R187" s="40"/>
-      <c r="S187" s="40"/>
-      <c r="T187" s="40"/>
-      <c r="U187" s="41"/>
+      <c r="H187" s="51"/>
+      <c r="I187" s="59"/>
+      <c r="J187" s="59"/>
+      <c r="K187" s="59"/>
+      <c r="L187" s="59"/>
+      <c r="M187" s="59"/>
+      <c r="N187" s="59"/>
+      <c r="O187" s="59"/>
+      <c r="P187" s="59"/>
+      <c r="Q187" s="59"/>
+      <c r="R187" s="59"/>
+      <c r="S187" s="59"/>
+      <c r="T187" s="59"/>
+      <c r="U187" s="52"/>
     </row>
     <row r="188" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" s="30"/>
@@ -27568,20 +27574,20 @@
       <c r="E188" s="31"/>
       <c r="F188" s="31"/>
       <c r="G188" s="31"/>
-      <c r="H188" s="39"/>
-      <c r="I188" s="40"/>
-      <c r="J188" s="40"/>
-      <c r="K188" s="40"/>
-      <c r="L188" s="40"/>
-      <c r="M188" s="40"/>
-      <c r="N188" s="40"/>
-      <c r="O188" s="40"/>
-      <c r="P188" s="40"/>
-      <c r="Q188" s="40"/>
-      <c r="R188" s="40"/>
-      <c r="S188" s="40"/>
-      <c r="T188" s="40"/>
-      <c r="U188" s="41"/>
+      <c r="H188" s="51"/>
+      <c r="I188" s="59"/>
+      <c r="J188" s="59"/>
+      <c r="K188" s="59"/>
+      <c r="L188" s="59"/>
+      <c r="M188" s="59"/>
+      <c r="N188" s="59"/>
+      <c r="O188" s="59"/>
+      <c r="P188" s="59"/>
+      <c r="Q188" s="59"/>
+      <c r="R188" s="59"/>
+      <c r="S188" s="59"/>
+      <c r="T188" s="59"/>
+      <c r="U188" s="52"/>
     </row>
     <row r="189" spans="1:35" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A189" s="30"/>
@@ -27597,20 +27603,20 @@
       <c r="E189" s="31"/>
       <c r="F189" s="31"/>
       <c r="G189" s="31"/>
-      <c r="H189" s="39"/>
-      <c r="I189" s="40"/>
-      <c r="J189" s="40"/>
-      <c r="K189" s="40"/>
-      <c r="L189" s="40"/>
-      <c r="M189" s="40"/>
-      <c r="N189" s="40"/>
-      <c r="O189" s="40"/>
-      <c r="P189" s="40"/>
-      <c r="Q189" s="40"/>
-      <c r="R189" s="40"/>
-      <c r="S189" s="40"/>
-      <c r="T189" s="40"/>
-      <c r="U189" s="41"/>
+      <c r="H189" s="51"/>
+      <c r="I189" s="59"/>
+      <c r="J189" s="59"/>
+      <c r="K189" s="59"/>
+      <c r="L189" s="59"/>
+      <c r="M189" s="59"/>
+      <c r="N189" s="59"/>
+      <c r="O189" s="59"/>
+      <c r="P189" s="59"/>
+      <c r="Q189" s="59"/>
+      <c r="R189" s="59"/>
+      <c r="S189" s="59"/>
+      <c r="T189" s="59"/>
+      <c r="U189" s="52"/>
     </row>
     <row r="190" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A190" s="30"/>
@@ -27626,20 +27632,20 @@
       <c r="E190" s="31"/>
       <c r="F190" s="31"/>
       <c r="G190" s="31"/>
-      <c r="H190" s="39"/>
-      <c r="I190" s="40"/>
-      <c r="J190" s="40"/>
-      <c r="K190" s="40"/>
-      <c r="L190" s="40"/>
-      <c r="M190" s="40"/>
-      <c r="N190" s="40"/>
-      <c r="O190" s="40"/>
-      <c r="P190" s="40"/>
-      <c r="Q190" s="40"/>
-      <c r="R190" s="40"/>
-      <c r="S190" s="40"/>
-      <c r="T190" s="40"/>
-      <c r="U190" s="41"/>
+      <c r="H190" s="51"/>
+      <c r="I190" s="59"/>
+      <c r="J190" s="59"/>
+      <c r="K190" s="59"/>
+      <c r="L190" s="59"/>
+      <c r="M190" s="59"/>
+      <c r="N190" s="59"/>
+      <c r="O190" s="59"/>
+      <c r="P190" s="59"/>
+      <c r="Q190" s="59"/>
+      <c r="R190" s="59"/>
+      <c r="S190" s="59"/>
+      <c r="T190" s="59"/>
+      <c r="U190" s="52"/>
     </row>
     <row r="191" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A191" s="30"/>
@@ -27655,20 +27661,20 @@
       <c r="E191" s="31"/>
       <c r="F191" s="31"/>
       <c r="G191" s="31"/>
-      <c r="H191" s="39"/>
-      <c r="I191" s="40"/>
-      <c r="J191" s="40"/>
-      <c r="K191" s="40"/>
-      <c r="L191" s="40"/>
-      <c r="M191" s="40"/>
-      <c r="N191" s="40"/>
-      <c r="O191" s="40"/>
-      <c r="P191" s="40"/>
-      <c r="Q191" s="40"/>
-      <c r="R191" s="40"/>
-      <c r="S191" s="40"/>
-      <c r="T191" s="40"/>
-      <c r="U191" s="41"/>
+      <c r="H191" s="51"/>
+      <c r="I191" s="59"/>
+      <c r="J191" s="59"/>
+      <c r="K191" s="59"/>
+      <c r="L191" s="59"/>
+      <c r="M191" s="59"/>
+      <c r="N191" s="59"/>
+      <c r="O191" s="59"/>
+      <c r="P191" s="59"/>
+      <c r="Q191" s="59"/>
+      <c r="R191" s="59"/>
+      <c r="S191" s="59"/>
+      <c r="T191" s="59"/>
+      <c r="U191" s="52"/>
     </row>
     <row r="192" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" s="30"/>
@@ -27684,20 +27690,20 @@
       <c r="E192" s="31"/>
       <c r="F192" s="31"/>
       <c r="G192" s="31"/>
-      <c r="H192" s="39"/>
-      <c r="I192" s="40"/>
-      <c r="J192" s="40"/>
-      <c r="K192" s="40"/>
-      <c r="L192" s="40"/>
-      <c r="M192" s="40"/>
-      <c r="N192" s="40"/>
-      <c r="O192" s="40"/>
-      <c r="P192" s="40"/>
-      <c r="Q192" s="40"/>
-      <c r="R192" s="40"/>
-      <c r="S192" s="40"/>
-      <c r="T192" s="40"/>
-      <c r="U192" s="41"/>
+      <c r="H192" s="51"/>
+      <c r="I192" s="59"/>
+      <c r="J192" s="59"/>
+      <c r="K192" s="59"/>
+      <c r="L192" s="59"/>
+      <c r="M192" s="59"/>
+      <c r="N192" s="59"/>
+      <c r="O192" s="59"/>
+      <c r="P192" s="59"/>
+      <c r="Q192" s="59"/>
+      <c r="R192" s="59"/>
+      <c r="S192" s="59"/>
+      <c r="T192" s="59"/>
+      <c r="U192" s="52"/>
     </row>
     <row r="193" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="30"/>
@@ -27713,22 +27719,22 @@
       <c r="E193" s="31"/>
       <c r="F193" s="31"/>
       <c r="G193" s="31"/>
-      <c r="H193" s="39" t="s">
+      <c r="H193" s="51" t="s">
         <v>770</v>
       </c>
-      <c r="I193" s="40"/>
-      <c r="J193" s="40"/>
-      <c r="K193" s="40"/>
-      <c r="L193" s="40"/>
-      <c r="M193" s="40"/>
-      <c r="N193" s="40"/>
-      <c r="O193" s="40"/>
-      <c r="P193" s="40"/>
-      <c r="Q193" s="40"/>
-      <c r="R193" s="40"/>
-      <c r="S193" s="40"/>
-      <c r="T193" s="40"/>
-      <c r="U193" s="41"/>
+      <c r="I193" s="59"/>
+      <c r="J193" s="59"/>
+      <c r="K193" s="59"/>
+      <c r="L193" s="59"/>
+      <c r="M193" s="59"/>
+      <c r="N193" s="59"/>
+      <c r="O193" s="59"/>
+      <c r="P193" s="59"/>
+      <c r="Q193" s="59"/>
+      <c r="R193" s="59"/>
+      <c r="S193" s="59"/>
+      <c r="T193" s="59"/>
+      <c r="U193" s="52"/>
     </row>
     <row r="194" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" s="30"/>
@@ -27744,20 +27750,20 @@
       <c r="E194" s="31"/>
       <c r="F194" s="31"/>
       <c r="G194" s="31"/>
-      <c r="H194" s="39"/>
-      <c r="I194" s="40"/>
-      <c r="J194" s="40"/>
-      <c r="K194" s="40"/>
-      <c r="L194" s="40"/>
-      <c r="M194" s="40"/>
-      <c r="N194" s="40"/>
-      <c r="O194" s="40"/>
-      <c r="P194" s="40"/>
-      <c r="Q194" s="40"/>
-      <c r="R194" s="40"/>
-      <c r="S194" s="40"/>
-      <c r="T194" s="40"/>
-      <c r="U194" s="41"/>
+      <c r="H194" s="51"/>
+      <c r="I194" s="59"/>
+      <c r="J194" s="59"/>
+      <c r="K194" s="59"/>
+      <c r="L194" s="59"/>
+      <c r="M194" s="59"/>
+      <c r="N194" s="59"/>
+      <c r="O194" s="59"/>
+      <c r="P194" s="59"/>
+      <c r="Q194" s="59"/>
+      <c r="R194" s="59"/>
+      <c r="S194" s="59"/>
+      <c r="T194" s="59"/>
+      <c r="U194" s="52"/>
     </row>
     <row r="195" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" s="30"/>
@@ -27771,20 +27777,20 @@
       <c r="E195" s="31"/>
       <c r="F195" s="31"/>
       <c r="G195" s="31"/>
-      <c r="H195" s="39"/>
-      <c r="I195" s="40"/>
-      <c r="J195" s="40"/>
-      <c r="K195" s="40"/>
-      <c r="L195" s="40"/>
-      <c r="M195" s="40"/>
-      <c r="N195" s="40"/>
-      <c r="O195" s="40"/>
-      <c r="P195" s="40"/>
-      <c r="Q195" s="40"/>
-      <c r="R195" s="40"/>
-      <c r="S195" s="40"/>
-      <c r="T195" s="40"/>
-      <c r="U195" s="41"/>
+      <c r="H195" s="51"/>
+      <c r="I195" s="59"/>
+      <c r="J195" s="59"/>
+      <c r="K195" s="59"/>
+      <c r="L195" s="59"/>
+      <c r="M195" s="59"/>
+      <c r="N195" s="59"/>
+      <c r="O195" s="59"/>
+      <c r="P195" s="59"/>
+      <c r="Q195" s="59"/>
+      <c r="R195" s="59"/>
+      <c r="S195" s="59"/>
+      <c r="T195" s="59"/>
+      <c r="U195" s="52"/>
     </row>
     <row r="196" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" s="30"/>
@@ -27798,20 +27804,20 @@
       <c r="E196" s="31"/>
       <c r="F196" s="31"/>
       <c r="G196" s="31"/>
-      <c r="H196" s="39"/>
-      <c r="I196" s="40"/>
-      <c r="J196" s="40"/>
-      <c r="K196" s="40"/>
-      <c r="L196" s="40"/>
-      <c r="M196" s="40"/>
-      <c r="N196" s="40"/>
-      <c r="O196" s="40"/>
-      <c r="P196" s="40"/>
-      <c r="Q196" s="40"/>
-      <c r="R196" s="40"/>
-      <c r="S196" s="40"/>
-      <c r="T196" s="40"/>
-      <c r="U196" s="41"/>
+      <c r="H196" s="51"/>
+      <c r="I196" s="59"/>
+      <c r="J196" s="59"/>
+      <c r="K196" s="59"/>
+      <c r="L196" s="59"/>
+      <c r="M196" s="59"/>
+      <c r="N196" s="59"/>
+      <c r="O196" s="59"/>
+      <c r="P196" s="59"/>
+      <c r="Q196" s="59"/>
+      <c r="R196" s="59"/>
+      <c r="S196" s="59"/>
+      <c r="T196" s="59"/>
+      <c r="U196" s="52"/>
     </row>
     <row r="197" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" s="30"/>
@@ -27825,23 +27831,70 @@
       <c r="E197" s="31"/>
       <c r="F197" s="31"/>
       <c r="G197" s="31"/>
-      <c r="H197" s="39"/>
-      <c r="I197" s="40"/>
-      <c r="J197" s="40"/>
-      <c r="K197" s="40"/>
-      <c r="L197" s="40"/>
-      <c r="M197" s="40"/>
-      <c r="N197" s="40"/>
-      <c r="O197" s="40"/>
-      <c r="P197" s="40"/>
-      <c r="Q197" s="40"/>
-      <c r="R197" s="40"/>
-      <c r="S197" s="40"/>
-      <c r="T197" s="40"/>
-      <c r="U197" s="41"/>
+      <c r="H197" s="51"/>
+      <c r="I197" s="59"/>
+      <c r="J197" s="59"/>
+      <c r="K197" s="59"/>
+      <c r="L197" s="59"/>
+      <c r="M197" s="59"/>
+      <c r="N197" s="59"/>
+      <c r="O197" s="59"/>
+      <c r="P197" s="59"/>
+      <c r="Q197" s="59"/>
+      <c r="R197" s="59"/>
+      <c r="S197" s="59"/>
+      <c r="T197" s="59"/>
+      <c r="U197" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="63">
+    <mergeCell ref="A2:U2"/>
+    <mergeCell ref="A3:U3"/>
+    <mergeCell ref="A4:U4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="G5:G7"/>
+    <mergeCell ref="S5:U5"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="H5:H7"/>
+    <mergeCell ref="I5:I7"/>
+    <mergeCell ref="J5:O5"/>
+    <mergeCell ref="P5:R5"/>
+    <mergeCell ref="R6:R7"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="C149:I149"/>
+    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="C12:I12"/>
+    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="C37:I37"/>
+    <mergeCell ref="C45:I45"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="C66:I66"/>
+    <mergeCell ref="C67:I67"/>
+    <mergeCell ref="C97:I97"/>
+    <mergeCell ref="C128:I128"/>
+    <mergeCell ref="C148:I148"/>
+    <mergeCell ref="H188:U188"/>
+    <mergeCell ref="C153:I153"/>
+    <mergeCell ref="C169:I169"/>
+    <mergeCell ref="A179:U179"/>
+    <mergeCell ref="H180:U180"/>
+    <mergeCell ref="H181:U181"/>
+    <mergeCell ref="H182:U182"/>
     <mergeCell ref="H195:U195"/>
     <mergeCell ref="H196:U196"/>
     <mergeCell ref="H197:U197"/>
@@ -27858,53 +27911,6 @@
     <mergeCell ref="H185:U185"/>
     <mergeCell ref="H186:U186"/>
     <mergeCell ref="H187:U187"/>
-    <mergeCell ref="C128:I128"/>
-    <mergeCell ref="C148:I148"/>
-    <mergeCell ref="H188:U188"/>
-    <mergeCell ref="C153:I153"/>
-    <mergeCell ref="C169:I169"/>
-    <mergeCell ref="A179:U179"/>
-    <mergeCell ref="H180:U180"/>
-    <mergeCell ref="H181:U181"/>
-    <mergeCell ref="H182:U182"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="U6:U7"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="C149:I149"/>
-    <mergeCell ref="C11:I11"/>
-    <mergeCell ref="C12:I12"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="C14:I14"/>
-    <mergeCell ref="C37:I37"/>
-    <mergeCell ref="C45:I45"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="C66:I66"/>
-    <mergeCell ref="C67:I67"/>
-    <mergeCell ref="C97:I97"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="H5:H7"/>
-    <mergeCell ref="I5:I7"/>
-    <mergeCell ref="J5:O5"/>
-    <mergeCell ref="P5:R5"/>
-    <mergeCell ref="R6:R7"/>
-    <mergeCell ref="A2:U2"/>
-    <mergeCell ref="A3:U3"/>
-    <mergeCell ref="A4:U4"/>
-    <mergeCell ref="A5:A7"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="C5:C7"/>
-    <mergeCell ref="D5:D7"/>
-    <mergeCell ref="E5:E7"/>
-    <mergeCell ref="F5:F7"/>
-    <mergeCell ref="G5:G7"/>
-    <mergeCell ref="S5:U5"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="O6:O7"/>
-    <mergeCell ref="P6:Q6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/school_2/school_2_KP.xlsx
+++ b/school_2/school_2_KP.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8055" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8055"/>
   </bookViews>
   <sheets>
     <sheet name="ТКП" sheetId="1" r:id="rId1"/>
@@ -2800,6 +2800,39 @@
     <xf numFmtId="0" fontId="14" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2830,52 +2863,19 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3264,79 +3264,79 @@
       </c>
     </row>
     <row r="2" spans="1:35" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
-      <c r="O2" s="39"/>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
-      <c r="T2" s="39"/>
-      <c r="U2" s="39"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="50"/>
+      <c r="P2" s="50"/>
+      <c r="Q2" s="50"/>
+      <c r="R2" s="50"/>
+      <c r="S2" s="50"/>
+      <c r="T2" s="50"/>
+      <c r="U2" s="50"/>
     </row>
     <row r="3" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40"/>
-      <c r="S3" s="40"/>
-      <c r="T3" s="40"/>
-      <c r="U3" s="40"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="51"/>
+      <c r="O3" s="51"/>
+      <c r="P3" s="51"/>
+      <c r="Q3" s="51"/>
+      <c r="R3" s="51"/>
+      <c r="S3" s="51"/>
+      <c r="T3" s="51"/>
+      <c r="U3" s="51"/>
     </row>
     <row r="4" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="41"/>
-      <c r="N4" s="41"/>
-      <c r="O4" s="41"/>
-      <c r="P4" s="41"/>
-      <c r="Q4" s="41"/>
-      <c r="R4" s="41"/>
-      <c r="S4" s="41"/>
-      <c r="T4" s="41"/>
-      <c r="U4" s="41"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="52"/>
+      <c r="M4" s="52"/>
+      <c r="N4" s="52"/>
+      <c r="O4" s="52"/>
+      <c r="P4" s="52"/>
+      <c r="Q4" s="52"/>
+      <c r="R4" s="52"/>
+      <c r="S4" s="52"/>
+      <c r="T4" s="52"/>
+      <c r="U4" s="52"/>
     </row>
     <row r="5" spans="1:35" ht="40.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="48" t="s">
@@ -3366,115 +3366,115 @@
       <c r="I5" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J5" s="42" t="s">
+      <c r="J5" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="43"/>
-      <c r="L5" s="43"/>
-      <c r="M5" s="43"/>
-      <c r="N5" s="43"/>
-      <c r="O5" s="44"/>
-      <c r="P5" s="45" t="s">
+      <c r="K5" s="54"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="54"/>
+      <c r="N5" s="54"/>
+      <c r="O5" s="55"/>
+      <c r="P5" s="56" t="s">
         <v>780</v>
       </c>
-      <c r="Q5" s="46"/>
-      <c r="R5" s="47"/>
-      <c r="S5" s="45">
+      <c r="Q5" s="57"/>
+      <c r="R5" s="58"/>
+      <c r="S5" s="56">
         <v>9701212867</v>
       </c>
-      <c r="T5" s="46"/>
-      <c r="U5" s="47"/>
+      <c r="T5" s="57"/>
+      <c r="U5" s="58"/>
     </row>
     <row r="6" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="49"/>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="51" t="s">
+      <c r="A6" s="59"/>
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="52"/>
+      <c r="K6" s="41"/>
       <c r="L6" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="M6" s="51" t="s">
+      <c r="M6" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="N6" s="52"/>
+      <c r="N6" s="41"/>
       <c r="O6" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="P6" s="51" t="s">
+      <c r="P6" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="Q6" s="52"/>
+      <c r="Q6" s="41"/>
       <c r="R6" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="S6" s="51" t="s">
+      <c r="S6" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="T6" s="52"/>
+      <c r="T6" s="41"/>
       <c r="U6" s="48" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:35" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="50"/>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="50"/>
-      <c r="I7" s="50"/>
+      <c r="A7" s="49"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
       <c r="J7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L7" s="50"/>
+      <c r="L7" s="49"/>
       <c r="M7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="O7" s="50"/>
+      <c r="O7" s="49"/>
       <c r="P7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="R7" s="50"/>
+      <c r="R7" s="49"/>
       <c r="S7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="T7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="U7" s="50"/>
+      <c r="U7" s="49"/>
     </row>
     <row r="8" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="55"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="47"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -3528,15 +3528,15 @@
       <c r="B9" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="56" t="s">
+      <c r="C9" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="58"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="44"/>
       <c r="M9" s="6">
         <f t="shared" si="0"/>
         <v>21918840.049999997</v>
@@ -3587,15 +3587,15 @@
       <c r="B10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="56" t="s">
+      <c r="C10" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="58"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="44"/>
       <c r="M10" s="6">
         <f t="shared" si="0"/>
         <v>21918840.049999997</v>
@@ -3646,15 +3646,15 @@
       <c r="B11" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="56" t="s">
+      <c r="C11" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="58"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="44"/>
       <c r="M11" s="6">
         <f t="shared" si="0"/>
         <v>21918840.049999997</v>
@@ -3705,15 +3705,15 @@
       <c r="B12" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="56" t="s">
+      <c r="C12" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="58"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="44"/>
       <c r="M12" s="6">
         <f>SUM(M13,M66,M148,M169)</f>
         <v>21918840.049999997</v>
@@ -3764,15 +3764,15 @@
       <c r="B13" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="56" t="s">
+      <c r="C13" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="58"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="44"/>
       <c r="M13" s="6">
         <f>SUM(M14,M37,M45)</f>
         <v>3570644.12</v>
@@ -3823,15 +3823,15 @@
       <c r="B14" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="56" t="s">
+      <c r="C14" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="58"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="44"/>
       <c r="M14" s="6">
         <f>SUM(M15,M19,M21,M29)</f>
         <v>2618573.91</v>
@@ -5256,15 +5256,15 @@
       <c r="B37" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="C37" s="56" t="s">
+      <c r="C37" s="42" t="s">
         <v>154</v>
       </c>
-      <c r="D37" s="57"/>
-      <c r="E37" s="57"/>
-      <c r="F37" s="57"/>
-      <c r="G37" s="57"/>
-      <c r="H37" s="57"/>
-      <c r="I37" s="58"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="43"/>
+      <c r="I37" s="44"/>
       <c r="M37" s="6">
         <f>SUM(M38,M41,M43)</f>
         <v>122933.90000000001</v>
@@ -5628,7 +5628,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="42" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
         <v>175</v>
       </c>
@@ -5849,15 +5849,15 @@
       <c r="B45" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="C45" s="56" t="s">
+      <c r="C45" s="42" t="s">
         <v>193</v>
       </c>
-      <c r="D45" s="57"/>
-      <c r="E45" s="57"/>
-      <c r="F45" s="57"/>
-      <c r="G45" s="57"/>
-      <c r="H45" s="57"/>
-      <c r="I45" s="58"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="43"/>
+      <c r="G45" s="43"/>
+      <c r="H45" s="43"/>
+      <c r="I45" s="44"/>
       <c r="M45" s="6">
         <f>SUM(M46,M51,M55,M60,M63)</f>
         <v>829136.31</v>
@@ -6065,7 +6065,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="48" spans="1:35" ht="56.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:35" ht="75" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
         <v>206</v>
       </c>
@@ -7252,15 +7252,15 @@
       <c r="B66" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="C66" s="56" t="s">
+      <c r="C66" s="42" t="s">
         <v>299</v>
       </c>
-      <c r="D66" s="57"/>
-      <c r="E66" s="57"/>
-      <c r="F66" s="57"/>
-      <c r="G66" s="57"/>
-      <c r="H66" s="57"/>
-      <c r="I66" s="58"/>
+      <c r="D66" s="43"/>
+      <c r="E66" s="43"/>
+      <c r="F66" s="43"/>
+      <c r="G66" s="43"/>
+      <c r="H66" s="43"/>
+      <c r="I66" s="44"/>
       <c r="M66" s="6">
         <f>SUM(M67,M97,M128)</f>
         <v>4332566.72</v>
@@ -7311,15 +7311,15 @@
       <c r="B67" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="C67" s="56" t="s">
+      <c r="C67" s="42" t="s">
         <v>302</v>
       </c>
-      <c r="D67" s="57"/>
-      <c r="E67" s="57"/>
-      <c r="F67" s="57"/>
-      <c r="G67" s="57"/>
-      <c r="H67" s="57"/>
-      <c r="I67" s="58"/>
+      <c r="D67" s="43"/>
+      <c r="E67" s="43"/>
+      <c r="F67" s="43"/>
+      <c r="G67" s="43"/>
+      <c r="H67" s="43"/>
+      <c r="I67" s="44"/>
       <c r="M67" s="6">
         <f>SUM(M68,M71,M75,M79,M82,M85,M89,M92)</f>
         <v>2963619.5900000003</v>
@@ -9346,15 +9346,15 @@
       <c r="B97" s="10" t="s">
         <v>419</v>
       </c>
-      <c r="C97" s="56" t="s">
+      <c r="C97" s="42" t="s">
         <v>420</v>
       </c>
-      <c r="D97" s="57"/>
-      <c r="E97" s="57"/>
-      <c r="F97" s="57"/>
-      <c r="G97" s="57"/>
-      <c r="H97" s="57"/>
-      <c r="I97" s="58"/>
+      <c r="D97" s="43"/>
+      <c r="E97" s="43"/>
+      <c r="F97" s="43"/>
+      <c r="G97" s="43"/>
+      <c r="H97" s="43"/>
+      <c r="I97" s="44"/>
       <c r="M97" s="6">
         <f>SUM(M98,M107,M110,M113,M116,M119,M122,M125)</f>
         <v>1187256.6599999997</v>
@@ -11433,15 +11433,15 @@
       <c r="B128" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="C128" s="56" t="s">
+      <c r="C128" s="42" t="s">
         <v>534</v>
       </c>
-      <c r="D128" s="57"/>
-      <c r="E128" s="57"/>
-      <c r="F128" s="57"/>
-      <c r="G128" s="57"/>
-      <c r="H128" s="57"/>
-      <c r="I128" s="58"/>
+      <c r="D128" s="43"/>
+      <c r="E128" s="43"/>
+      <c r="F128" s="43"/>
+      <c r="G128" s="43"/>
+      <c r="H128" s="43"/>
+      <c r="I128" s="44"/>
       <c r="M128" s="6">
         <f>SUM(M129,M132,M135,M138,M143)</f>
         <v>181690.47</v>
@@ -12125,7 +12125,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="138" spans="1:35" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:35" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A138" s="10" t="s">
         <v>568</v>
       </c>
@@ -12764,15 +12764,15 @@
       <c r="B148" s="10" t="s">
         <v>616</v>
       </c>
-      <c r="C148" s="56" t="s">
+      <c r="C148" s="42" t="s">
         <v>617</v>
       </c>
-      <c r="D148" s="57"/>
-      <c r="E148" s="57"/>
-      <c r="F148" s="57"/>
-      <c r="G148" s="57"/>
-      <c r="H148" s="57"/>
-      <c r="I148" s="58"/>
+      <c r="D148" s="43"/>
+      <c r="E148" s="43"/>
+      <c r="F148" s="43"/>
+      <c r="G148" s="43"/>
+      <c r="H148" s="43"/>
+      <c r="I148" s="44"/>
       <c r="M148" s="6">
         <f>SUM(M149,M153)</f>
         <v>447303.98</v>
@@ -12823,15 +12823,15 @@
       <c r="B149" s="10" t="s">
         <v>619</v>
       </c>
-      <c r="C149" s="56" t="s">
+      <c r="C149" s="42" t="s">
         <v>620</v>
       </c>
-      <c r="D149" s="57"/>
-      <c r="E149" s="57"/>
-      <c r="F149" s="57"/>
-      <c r="G149" s="57"/>
-      <c r="H149" s="57"/>
-      <c r="I149" s="58"/>
+      <c r="D149" s="43"/>
+      <c r="E149" s="43"/>
+      <c r="F149" s="43"/>
+      <c r="G149" s="43"/>
+      <c r="H149" s="43"/>
+      <c r="I149" s="44"/>
       <c r="M149" s="6">
         <f>SUM(M150)</f>
         <v>241468.92</v>
@@ -13094,15 +13094,15 @@
       <c r="B153" s="10" t="s">
         <v>635</v>
       </c>
-      <c r="C153" s="56" t="s">
+      <c r="C153" s="42" t="s">
         <v>636</v>
       </c>
-      <c r="D153" s="57"/>
-      <c r="E153" s="57"/>
-      <c r="F153" s="57"/>
-      <c r="G153" s="57"/>
-      <c r="H153" s="57"/>
-      <c r="I153" s="58"/>
+      <c r="D153" s="43"/>
+      <c r="E153" s="43"/>
+      <c r="F153" s="43"/>
+      <c r="G153" s="43"/>
+      <c r="H153" s="43"/>
+      <c r="I153" s="44"/>
       <c r="M153" s="6">
         <f>SUM(M154,M157,M160,M163,M166)</f>
         <v>205835.06</v>
@@ -14225,15 +14225,15 @@
       <c r="B169" s="10" t="s">
         <v>683</v>
       </c>
-      <c r="C169" s="56" t="s">
+      <c r="C169" s="42" t="s">
         <v>684</v>
       </c>
-      <c r="D169" s="57"/>
-      <c r="E169" s="57"/>
-      <c r="F169" s="57"/>
-      <c r="G169" s="57"/>
-      <c r="H169" s="57"/>
-      <c r="I169" s="58"/>
+      <c r="D169" s="43"/>
+      <c r="E169" s="43"/>
+      <c r="F169" s="43"/>
+      <c r="G169" s="43"/>
+      <c r="H169" s="43"/>
+      <c r="I169" s="44"/>
       <c r="M169" s="6">
         <f>SUM(M170,M173,M177)</f>
         <v>13568325.229999999</v>
@@ -14911,29 +14911,29 @@
       </c>
     </row>
     <row r="179" spans="1:35" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A179" s="53" t="s">
+      <c r="A179" s="45" t="s">
         <v>728</v>
       </c>
-      <c r="B179" s="54"/>
-      <c r="C179" s="54"/>
-      <c r="D179" s="54"/>
-      <c r="E179" s="54"/>
-      <c r="F179" s="54"/>
-      <c r="G179" s="54"/>
-      <c r="H179" s="54"/>
-      <c r="I179" s="54"/>
-      <c r="J179" s="54"/>
-      <c r="K179" s="54"/>
-      <c r="L179" s="54"/>
-      <c r="M179" s="54"/>
-      <c r="N179" s="54"/>
-      <c r="O179" s="54"/>
-      <c r="P179" s="54"/>
-      <c r="Q179" s="54"/>
-      <c r="R179" s="54"/>
-      <c r="S179" s="54"/>
-      <c r="T179" s="54"/>
-      <c r="U179" s="55"/>
+      <c r="B179" s="46"/>
+      <c r="C179" s="46"/>
+      <c r="D179" s="46"/>
+      <c r="E179" s="46"/>
+      <c r="F179" s="46"/>
+      <c r="G179" s="46"/>
+      <c r="H179" s="46"/>
+      <c r="I179" s="46"/>
+      <c r="J179" s="46"/>
+      <c r="K179" s="46"/>
+      <c r="L179" s="46"/>
+      <c r="M179" s="46"/>
+      <c r="N179" s="46"/>
+      <c r="O179" s="46"/>
+      <c r="P179" s="46"/>
+      <c r="Q179" s="46"/>
+      <c r="R179" s="46"/>
+      <c r="S179" s="46"/>
+      <c r="T179" s="46"/>
+      <c r="U179" s="47"/>
     </row>
     <row r="180" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="30"/>
@@ -14949,20 +14949,20 @@
       <c r="E180" s="31"/>
       <c r="F180" s="31"/>
       <c r="G180" s="31"/>
-      <c r="H180" s="51"/>
-      <c r="I180" s="59"/>
-      <c r="J180" s="59"/>
-      <c r="K180" s="59"/>
-      <c r="L180" s="59"/>
-      <c r="M180" s="59"/>
-      <c r="N180" s="59"/>
-      <c r="O180" s="59"/>
-      <c r="P180" s="59"/>
-      <c r="Q180" s="59"/>
-      <c r="R180" s="59"/>
-      <c r="S180" s="59"/>
-      <c r="T180" s="59"/>
-      <c r="U180" s="52"/>
+      <c r="H180" s="39"/>
+      <c r="I180" s="40"/>
+      <c r="J180" s="40"/>
+      <c r="K180" s="40"/>
+      <c r="L180" s="40"/>
+      <c r="M180" s="40"/>
+      <c r="N180" s="40"/>
+      <c r="O180" s="40"/>
+      <c r="P180" s="40"/>
+      <c r="Q180" s="40"/>
+      <c r="R180" s="40"/>
+      <c r="S180" s="40"/>
+      <c r="T180" s="40"/>
+      <c r="U180" s="41"/>
     </row>
     <row r="181" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="30"/>
@@ -14978,20 +14978,20 @@
       <c r="E181" s="31"/>
       <c r="F181" s="31"/>
       <c r="G181" s="31"/>
-      <c r="H181" s="51"/>
-      <c r="I181" s="59"/>
-      <c r="J181" s="59"/>
-      <c r="K181" s="59"/>
-      <c r="L181" s="59"/>
-      <c r="M181" s="59"/>
-      <c r="N181" s="59"/>
-      <c r="O181" s="59"/>
-      <c r="P181" s="59"/>
-      <c r="Q181" s="59"/>
-      <c r="R181" s="59"/>
-      <c r="S181" s="59"/>
-      <c r="T181" s="59"/>
-      <c r="U181" s="52"/>
+      <c r="H181" s="39"/>
+      <c r="I181" s="40"/>
+      <c r="J181" s="40"/>
+      <c r="K181" s="40"/>
+      <c r="L181" s="40"/>
+      <c r="M181" s="40"/>
+      <c r="N181" s="40"/>
+      <c r="O181" s="40"/>
+      <c r="P181" s="40"/>
+      <c r="Q181" s="40"/>
+      <c r="R181" s="40"/>
+      <c r="S181" s="40"/>
+      <c r="T181" s="40"/>
+      <c r="U181" s="41"/>
     </row>
     <row r="182" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A182" s="30"/>
@@ -15007,20 +15007,20 @@
       <c r="E182" s="31"/>
       <c r="F182" s="31"/>
       <c r="G182" s="31"/>
-      <c r="H182" s="51"/>
-      <c r="I182" s="59"/>
-      <c r="J182" s="59"/>
-      <c r="K182" s="59"/>
-      <c r="L182" s="59"/>
-      <c r="M182" s="59"/>
-      <c r="N182" s="59"/>
-      <c r="O182" s="59"/>
-      <c r="P182" s="59"/>
-      <c r="Q182" s="59"/>
-      <c r="R182" s="59"/>
-      <c r="S182" s="59"/>
-      <c r="T182" s="59"/>
-      <c r="U182" s="52"/>
+      <c r="H182" s="39"/>
+      <c r="I182" s="40"/>
+      <c r="J182" s="40"/>
+      <c r="K182" s="40"/>
+      <c r="L182" s="40"/>
+      <c r="M182" s="40"/>
+      <c r="N182" s="40"/>
+      <c r="O182" s="40"/>
+      <c r="P182" s="40"/>
+      <c r="Q182" s="40"/>
+      <c r="R182" s="40"/>
+      <c r="S182" s="40"/>
+      <c r="T182" s="40"/>
+      <c r="U182" s="41"/>
     </row>
     <row r="183" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="30"/>
@@ -15036,20 +15036,20 @@
       <c r="E183" s="31"/>
       <c r="F183" s="31"/>
       <c r="G183" s="31"/>
-      <c r="H183" s="51"/>
-      <c r="I183" s="59"/>
-      <c r="J183" s="59"/>
-      <c r="K183" s="59"/>
-      <c r="L183" s="59"/>
-      <c r="M183" s="59"/>
-      <c r="N183" s="59"/>
-      <c r="O183" s="59"/>
-      <c r="P183" s="59"/>
-      <c r="Q183" s="59"/>
-      <c r="R183" s="59"/>
-      <c r="S183" s="59"/>
-      <c r="T183" s="59"/>
-      <c r="U183" s="52"/>
+      <c r="H183" s="39"/>
+      <c r="I183" s="40"/>
+      <c r="J183" s="40"/>
+      <c r="K183" s="40"/>
+      <c r="L183" s="40"/>
+      <c r="M183" s="40"/>
+      <c r="N183" s="40"/>
+      <c r="O183" s="40"/>
+      <c r="P183" s="40"/>
+      <c r="Q183" s="40"/>
+      <c r="R183" s="40"/>
+      <c r="S183" s="40"/>
+      <c r="T183" s="40"/>
+      <c r="U183" s="41"/>
     </row>
     <row r="184" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" s="30"/>
@@ -15065,20 +15065,20 @@
       <c r="E184" s="31"/>
       <c r="F184" s="31"/>
       <c r="G184" s="31"/>
-      <c r="H184" s="51"/>
-      <c r="I184" s="59"/>
-      <c r="J184" s="59"/>
-      <c r="K184" s="59"/>
-      <c r="L184" s="59"/>
-      <c r="M184" s="59"/>
-      <c r="N184" s="59"/>
-      <c r="O184" s="59"/>
-      <c r="P184" s="59"/>
-      <c r="Q184" s="59"/>
-      <c r="R184" s="59"/>
-      <c r="S184" s="59"/>
-      <c r="T184" s="59"/>
-      <c r="U184" s="52"/>
+      <c r="H184" s="39"/>
+      <c r="I184" s="40"/>
+      <c r="J184" s="40"/>
+      <c r="K184" s="40"/>
+      <c r="L184" s="40"/>
+      <c r="M184" s="40"/>
+      <c r="N184" s="40"/>
+      <c r="O184" s="40"/>
+      <c r="P184" s="40"/>
+      <c r="Q184" s="40"/>
+      <c r="R184" s="40"/>
+      <c r="S184" s="40"/>
+      <c r="T184" s="40"/>
+      <c r="U184" s="41"/>
     </row>
     <row r="185" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A185" s="30"/>
@@ -15094,20 +15094,20 @@
       <c r="E185" s="31"/>
       <c r="F185" s="31"/>
       <c r="G185" s="31"/>
-      <c r="H185" s="51"/>
-      <c r="I185" s="59"/>
-      <c r="J185" s="59"/>
-      <c r="K185" s="59"/>
-      <c r="L185" s="59"/>
-      <c r="M185" s="59"/>
-      <c r="N185" s="59"/>
-      <c r="O185" s="59"/>
-      <c r="P185" s="59"/>
-      <c r="Q185" s="59"/>
-      <c r="R185" s="59"/>
-      <c r="S185" s="59"/>
-      <c r="T185" s="59"/>
-      <c r="U185" s="52"/>
+      <c r="H185" s="39"/>
+      <c r="I185" s="40"/>
+      <c r="J185" s="40"/>
+      <c r="K185" s="40"/>
+      <c r="L185" s="40"/>
+      <c r="M185" s="40"/>
+      <c r="N185" s="40"/>
+      <c r="O185" s="40"/>
+      <c r="P185" s="40"/>
+      <c r="Q185" s="40"/>
+      <c r="R185" s="40"/>
+      <c r="S185" s="40"/>
+      <c r="T185" s="40"/>
+      <c r="U185" s="41"/>
     </row>
     <row r="186" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A186" s="30"/>
@@ -15123,20 +15123,20 @@
       <c r="E186" s="31"/>
       <c r="F186" s="31"/>
       <c r="G186" s="31"/>
-      <c r="H186" s="51"/>
-      <c r="I186" s="59"/>
-      <c r="J186" s="59"/>
-      <c r="K186" s="59"/>
-      <c r="L186" s="59"/>
-      <c r="M186" s="59"/>
-      <c r="N186" s="59"/>
-      <c r="O186" s="59"/>
-      <c r="P186" s="59"/>
-      <c r="Q186" s="59"/>
-      <c r="R186" s="59"/>
-      <c r="S186" s="59"/>
-      <c r="T186" s="59"/>
-      <c r="U186" s="52"/>
+      <c r="H186" s="39"/>
+      <c r="I186" s="40"/>
+      <c r="J186" s="40"/>
+      <c r="K186" s="40"/>
+      <c r="L186" s="40"/>
+      <c r="M186" s="40"/>
+      <c r="N186" s="40"/>
+      <c r="O186" s="40"/>
+      <c r="P186" s="40"/>
+      <c r="Q186" s="40"/>
+      <c r="R186" s="40"/>
+      <c r="S186" s="40"/>
+      <c r="T186" s="40"/>
+      <c r="U186" s="41"/>
     </row>
     <row r="187" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" s="30"/>
@@ -15152,20 +15152,20 @@
       <c r="E187" s="31"/>
       <c r="F187" s="31"/>
       <c r="G187" s="31"/>
-      <c r="H187" s="51"/>
-      <c r="I187" s="59"/>
-      <c r="J187" s="59"/>
-      <c r="K187" s="59"/>
-      <c r="L187" s="59"/>
-      <c r="M187" s="59"/>
-      <c r="N187" s="59"/>
-      <c r="O187" s="59"/>
-      <c r="P187" s="59"/>
-      <c r="Q187" s="59"/>
-      <c r="R187" s="59"/>
-      <c r="S187" s="59"/>
-      <c r="T187" s="59"/>
-      <c r="U187" s="52"/>
+      <c r="H187" s="39"/>
+      <c r="I187" s="40"/>
+      <c r="J187" s="40"/>
+      <c r="K187" s="40"/>
+      <c r="L187" s="40"/>
+      <c r="M187" s="40"/>
+      <c r="N187" s="40"/>
+      <c r="O187" s="40"/>
+      <c r="P187" s="40"/>
+      <c r="Q187" s="40"/>
+      <c r="R187" s="40"/>
+      <c r="S187" s="40"/>
+      <c r="T187" s="40"/>
+      <c r="U187" s="41"/>
     </row>
     <row r="188" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" s="30"/>
@@ -15181,20 +15181,20 @@
       <c r="E188" s="31"/>
       <c r="F188" s="31"/>
       <c r="G188" s="31"/>
-      <c r="H188" s="51"/>
-      <c r="I188" s="59"/>
-      <c r="J188" s="59"/>
-      <c r="K188" s="59"/>
-      <c r="L188" s="59"/>
-      <c r="M188" s="59"/>
-      <c r="N188" s="59"/>
-      <c r="O188" s="59"/>
-      <c r="P188" s="59"/>
-      <c r="Q188" s="59"/>
-      <c r="R188" s="59"/>
-      <c r="S188" s="59"/>
-      <c r="T188" s="59"/>
-      <c r="U188" s="52"/>
+      <c r="H188" s="39"/>
+      <c r="I188" s="40"/>
+      <c r="J188" s="40"/>
+      <c r="K188" s="40"/>
+      <c r="L188" s="40"/>
+      <c r="M188" s="40"/>
+      <c r="N188" s="40"/>
+      <c r="O188" s="40"/>
+      <c r="P188" s="40"/>
+      <c r="Q188" s="40"/>
+      <c r="R188" s="40"/>
+      <c r="S188" s="40"/>
+      <c r="T188" s="40"/>
+      <c r="U188" s="41"/>
     </row>
     <row r="189" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A189" s="30"/>
@@ -15210,20 +15210,20 @@
       <c r="E189" s="31"/>
       <c r="F189" s="31"/>
       <c r="G189" s="31"/>
-      <c r="H189" s="51"/>
-      <c r="I189" s="59"/>
-      <c r="J189" s="59"/>
-      <c r="K189" s="59"/>
-      <c r="L189" s="59"/>
-      <c r="M189" s="59"/>
-      <c r="N189" s="59"/>
-      <c r="O189" s="59"/>
-      <c r="P189" s="59"/>
-      <c r="Q189" s="59"/>
-      <c r="R189" s="59"/>
-      <c r="S189" s="59"/>
-      <c r="T189" s="59"/>
-      <c r="U189" s="52"/>
+      <c r="H189" s="39"/>
+      <c r="I189" s="40"/>
+      <c r="J189" s="40"/>
+      <c r="K189" s="40"/>
+      <c r="L189" s="40"/>
+      <c r="M189" s="40"/>
+      <c r="N189" s="40"/>
+      <c r="O189" s="40"/>
+      <c r="P189" s="40"/>
+      <c r="Q189" s="40"/>
+      <c r="R189" s="40"/>
+      <c r="S189" s="40"/>
+      <c r="T189" s="40"/>
+      <c r="U189" s="41"/>
     </row>
     <row r="190" spans="1:35" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A190" s="30"/>
@@ -15239,20 +15239,20 @@
       <c r="E190" s="31"/>
       <c r="F190" s="31"/>
       <c r="G190" s="31"/>
-      <c r="H190" s="51"/>
-      <c r="I190" s="59"/>
-      <c r="J190" s="59"/>
-      <c r="K190" s="59"/>
-      <c r="L190" s="59"/>
-      <c r="M190" s="59"/>
-      <c r="N190" s="59"/>
-      <c r="O190" s="59"/>
-      <c r="P190" s="59"/>
-      <c r="Q190" s="59"/>
-      <c r="R190" s="59"/>
-      <c r="S190" s="59"/>
-      <c r="T190" s="59"/>
-      <c r="U190" s="52"/>
+      <c r="H190" s="39"/>
+      <c r="I190" s="40"/>
+      <c r="J190" s="40"/>
+      <c r="K190" s="40"/>
+      <c r="L190" s="40"/>
+      <c r="M190" s="40"/>
+      <c r="N190" s="40"/>
+      <c r="O190" s="40"/>
+      <c r="P190" s="40"/>
+      <c r="Q190" s="40"/>
+      <c r="R190" s="40"/>
+      <c r="S190" s="40"/>
+      <c r="T190" s="40"/>
+      <c r="U190" s="41"/>
     </row>
     <row r="191" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A191" s="30"/>
@@ -15268,20 +15268,20 @@
       <c r="E191" s="31"/>
       <c r="F191" s="31"/>
       <c r="G191" s="31"/>
-      <c r="H191" s="51"/>
-      <c r="I191" s="59"/>
-      <c r="J191" s="59"/>
-      <c r="K191" s="59"/>
-      <c r="L191" s="59"/>
-      <c r="M191" s="59"/>
-      <c r="N191" s="59"/>
-      <c r="O191" s="59"/>
-      <c r="P191" s="59"/>
-      <c r="Q191" s="59"/>
-      <c r="R191" s="59"/>
-      <c r="S191" s="59"/>
-      <c r="T191" s="59"/>
-      <c r="U191" s="52"/>
+      <c r="H191" s="39"/>
+      <c r="I191" s="40"/>
+      <c r="J191" s="40"/>
+      <c r="K191" s="40"/>
+      <c r="L191" s="40"/>
+      <c r="M191" s="40"/>
+      <c r="N191" s="40"/>
+      <c r="O191" s="40"/>
+      <c r="P191" s="40"/>
+      <c r="Q191" s="40"/>
+      <c r="R191" s="40"/>
+      <c r="S191" s="40"/>
+      <c r="T191" s="40"/>
+      <c r="U191" s="41"/>
     </row>
     <row r="192" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" s="30"/>
@@ -15297,20 +15297,20 @@
       <c r="E192" s="31"/>
       <c r="F192" s="31"/>
       <c r="G192" s="31"/>
-      <c r="H192" s="51"/>
-      <c r="I192" s="59"/>
-      <c r="J192" s="59"/>
-      <c r="K192" s="59"/>
-      <c r="L192" s="59"/>
-      <c r="M192" s="59"/>
-      <c r="N192" s="59"/>
-      <c r="O192" s="59"/>
-      <c r="P192" s="59"/>
-      <c r="Q192" s="59"/>
-      <c r="R192" s="59"/>
-      <c r="S192" s="59"/>
-      <c r="T192" s="59"/>
-      <c r="U192" s="52"/>
+      <c r="H192" s="39"/>
+      <c r="I192" s="40"/>
+      <c r="J192" s="40"/>
+      <c r="K192" s="40"/>
+      <c r="L192" s="40"/>
+      <c r="M192" s="40"/>
+      <c r="N192" s="40"/>
+      <c r="O192" s="40"/>
+      <c r="P192" s="40"/>
+      <c r="Q192" s="40"/>
+      <c r="R192" s="40"/>
+      <c r="S192" s="40"/>
+      <c r="T192" s="40"/>
+      <c r="U192" s="41"/>
     </row>
     <row r="193" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="30"/>
@@ -15326,22 +15326,22 @@
       <c r="E193" s="31"/>
       <c r="F193" s="31"/>
       <c r="G193" s="31"/>
-      <c r="H193" s="51" t="s">
+      <c r="H193" s="39" t="s">
         <v>770</v>
       </c>
-      <c r="I193" s="59"/>
-      <c r="J193" s="59"/>
-      <c r="K193" s="59"/>
-      <c r="L193" s="59"/>
-      <c r="M193" s="59"/>
-      <c r="N193" s="59"/>
-      <c r="O193" s="59"/>
-      <c r="P193" s="59"/>
-      <c r="Q193" s="59"/>
-      <c r="R193" s="59"/>
-      <c r="S193" s="59"/>
-      <c r="T193" s="59"/>
-      <c r="U193" s="52"/>
+      <c r="I193" s="40"/>
+      <c r="J193" s="40"/>
+      <c r="K193" s="40"/>
+      <c r="L193" s="40"/>
+      <c r="M193" s="40"/>
+      <c r="N193" s="40"/>
+      <c r="O193" s="40"/>
+      <c r="P193" s="40"/>
+      <c r="Q193" s="40"/>
+      <c r="R193" s="40"/>
+      <c r="S193" s="40"/>
+      <c r="T193" s="40"/>
+      <c r="U193" s="41"/>
     </row>
     <row r="194" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" s="30"/>
@@ -15357,20 +15357,20 @@
       <c r="E194" s="31"/>
       <c r="F194" s="31"/>
       <c r="G194" s="31"/>
-      <c r="H194" s="51"/>
-      <c r="I194" s="59"/>
-      <c r="J194" s="59"/>
-      <c r="K194" s="59"/>
-      <c r="L194" s="59"/>
-      <c r="M194" s="59"/>
-      <c r="N194" s="59"/>
-      <c r="O194" s="59"/>
-      <c r="P194" s="59"/>
-      <c r="Q194" s="59"/>
-      <c r="R194" s="59"/>
-      <c r="S194" s="59"/>
-      <c r="T194" s="59"/>
-      <c r="U194" s="52"/>
+      <c r="H194" s="39"/>
+      <c r="I194" s="40"/>
+      <c r="J194" s="40"/>
+      <c r="K194" s="40"/>
+      <c r="L194" s="40"/>
+      <c r="M194" s="40"/>
+      <c r="N194" s="40"/>
+      <c r="O194" s="40"/>
+      <c r="P194" s="40"/>
+      <c r="Q194" s="40"/>
+      <c r="R194" s="40"/>
+      <c r="S194" s="40"/>
+      <c r="T194" s="40"/>
+      <c r="U194" s="41"/>
     </row>
     <row r="195" spans="1:21" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A195" s="30"/>
@@ -15384,20 +15384,20 @@
       <c r="E195" s="31"/>
       <c r="F195" s="31"/>
       <c r="G195" s="31"/>
-      <c r="H195" s="51"/>
-      <c r="I195" s="59"/>
-      <c r="J195" s="59"/>
-      <c r="K195" s="59"/>
-      <c r="L195" s="59"/>
-      <c r="M195" s="59"/>
-      <c r="N195" s="59"/>
-      <c r="O195" s="59"/>
-      <c r="P195" s="59"/>
-      <c r="Q195" s="59"/>
-      <c r="R195" s="59"/>
-      <c r="S195" s="59"/>
-      <c r="T195" s="59"/>
-      <c r="U195" s="52"/>
+      <c r="H195" s="39"/>
+      <c r="I195" s="40"/>
+      <c r="J195" s="40"/>
+      <c r="K195" s="40"/>
+      <c r="L195" s="40"/>
+      <c r="M195" s="40"/>
+      <c r="N195" s="40"/>
+      <c r="O195" s="40"/>
+      <c r="P195" s="40"/>
+      <c r="Q195" s="40"/>
+      <c r="R195" s="40"/>
+      <c r="S195" s="40"/>
+      <c r="T195" s="40"/>
+      <c r="U195" s="41"/>
     </row>
     <row r="196" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" s="30"/>
@@ -15411,20 +15411,20 @@
       <c r="E196" s="31"/>
       <c r="F196" s="31"/>
       <c r="G196" s="31"/>
-      <c r="H196" s="51"/>
-      <c r="I196" s="59"/>
-      <c r="J196" s="59"/>
-      <c r="K196" s="59"/>
-      <c r="L196" s="59"/>
-      <c r="M196" s="59"/>
-      <c r="N196" s="59"/>
-      <c r="O196" s="59"/>
-      <c r="P196" s="59"/>
-      <c r="Q196" s="59"/>
-      <c r="R196" s="59"/>
-      <c r="S196" s="59"/>
-      <c r="T196" s="59"/>
-      <c r="U196" s="52"/>
+      <c r="H196" s="39"/>
+      <c r="I196" s="40"/>
+      <c r="J196" s="40"/>
+      <c r="K196" s="40"/>
+      <c r="L196" s="40"/>
+      <c r="M196" s="40"/>
+      <c r="N196" s="40"/>
+      <c r="O196" s="40"/>
+      <c r="P196" s="40"/>
+      <c r="Q196" s="40"/>
+      <c r="R196" s="40"/>
+      <c r="S196" s="40"/>
+      <c r="T196" s="40"/>
+      <c r="U196" s="41"/>
     </row>
     <row r="197" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" s="30"/>
@@ -15438,68 +15438,25 @@
       <c r="E197" s="31"/>
       <c r="F197" s="31"/>
       <c r="G197" s="31"/>
-      <c r="H197" s="51"/>
-      <c r="I197" s="59"/>
-      <c r="J197" s="59"/>
-      <c r="K197" s="59"/>
-      <c r="L197" s="59"/>
-      <c r="M197" s="59"/>
-      <c r="N197" s="59"/>
-      <c r="O197" s="59"/>
-      <c r="P197" s="59"/>
-      <c r="Q197" s="59"/>
-      <c r="R197" s="59"/>
-      <c r="S197" s="59"/>
-      <c r="T197" s="59"/>
-      <c r="U197" s="52"/>
+      <c r="H197" s="39"/>
+      <c r="I197" s="40"/>
+      <c r="J197" s="40"/>
+      <c r="K197" s="40"/>
+      <c r="L197" s="40"/>
+      <c r="M197" s="40"/>
+      <c r="N197" s="40"/>
+      <c r="O197" s="40"/>
+      <c r="P197" s="40"/>
+      <c r="Q197" s="40"/>
+      <c r="R197" s="40"/>
+      <c r="S197" s="40"/>
+      <c r="T197" s="40"/>
+      <c r="U197" s="41"/>
     </row>
   </sheetData>
   <sheetProtection password="C644" sheet="1" formatColumns="0" autoFilter="0"/>
   <autoFilter ref="A7:U7"/>
   <mergeCells count="59">
-    <mergeCell ref="H195:U195"/>
-    <mergeCell ref="H196:U196"/>
-    <mergeCell ref="H197:U197"/>
-    <mergeCell ref="H190:U190"/>
-    <mergeCell ref="H191:U191"/>
-    <mergeCell ref="H192:U192"/>
-    <mergeCell ref="H193:U193"/>
-    <mergeCell ref="H194:U194"/>
-    <mergeCell ref="H185:U185"/>
-    <mergeCell ref="H186:U186"/>
-    <mergeCell ref="H187:U187"/>
-    <mergeCell ref="H188:U188"/>
-    <mergeCell ref="H189:U189"/>
-    <mergeCell ref="H180:U180"/>
-    <mergeCell ref="H181:U181"/>
-    <mergeCell ref="H182:U182"/>
-    <mergeCell ref="H183:U183"/>
-    <mergeCell ref="H184:U184"/>
-    <mergeCell ref="C148:I148"/>
-    <mergeCell ref="C149:I149"/>
-    <mergeCell ref="C153:I153"/>
-    <mergeCell ref="C169:I169"/>
-    <mergeCell ref="A179:U179"/>
-    <mergeCell ref="C45:I45"/>
-    <mergeCell ref="C66:I66"/>
-    <mergeCell ref="C67:I67"/>
-    <mergeCell ref="C97:I97"/>
-    <mergeCell ref="C128:I128"/>
-    <mergeCell ref="C11:I11"/>
-    <mergeCell ref="C12:I12"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="C14:I14"/>
-    <mergeCell ref="C37:I37"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="U6:U7"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="O6:O7"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="R6:R7"/>
     <mergeCell ref="A2:U2"/>
     <mergeCell ref="A3:U3"/>
     <mergeCell ref="A4:U4"/>
@@ -15516,6 +15473,49 @@
     <mergeCell ref="H5:H7"/>
     <mergeCell ref="I5:I7"/>
     <mergeCell ref="J6:K6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="R6:R7"/>
+    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="C12:I12"/>
+    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="C37:I37"/>
+    <mergeCell ref="C45:I45"/>
+    <mergeCell ref="C66:I66"/>
+    <mergeCell ref="C67:I67"/>
+    <mergeCell ref="C97:I97"/>
+    <mergeCell ref="C128:I128"/>
+    <mergeCell ref="C148:I148"/>
+    <mergeCell ref="C149:I149"/>
+    <mergeCell ref="C153:I153"/>
+    <mergeCell ref="C169:I169"/>
+    <mergeCell ref="A179:U179"/>
+    <mergeCell ref="H180:U180"/>
+    <mergeCell ref="H181:U181"/>
+    <mergeCell ref="H182:U182"/>
+    <mergeCell ref="H183:U183"/>
+    <mergeCell ref="H184:U184"/>
+    <mergeCell ref="H185:U185"/>
+    <mergeCell ref="H186:U186"/>
+    <mergeCell ref="H187:U187"/>
+    <mergeCell ref="H188:U188"/>
+    <mergeCell ref="H189:U189"/>
+    <mergeCell ref="H195:U195"/>
+    <mergeCell ref="H196:U196"/>
+    <mergeCell ref="H197:U197"/>
+    <mergeCell ref="H190:U190"/>
+    <mergeCell ref="H191:U191"/>
+    <mergeCell ref="H192:U192"/>
+    <mergeCell ref="H193:U193"/>
+    <mergeCell ref="H194:U194"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15605,79 +15605,79 @@
       </c>
     </row>
     <row r="2" spans="1:35" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
-      <c r="O2" s="39"/>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
-      <c r="T2" s="39"/>
-      <c r="U2" s="39"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="50"/>
+      <c r="P2" s="50"/>
+      <c r="Q2" s="50"/>
+      <c r="R2" s="50"/>
+      <c r="S2" s="50"/>
+      <c r="T2" s="50"/>
+      <c r="U2" s="50"/>
     </row>
     <row r="3" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40"/>
-      <c r="S3" s="40"/>
-      <c r="T3" s="40"/>
-      <c r="U3" s="40"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="51"/>
+      <c r="O3" s="51"/>
+      <c r="P3" s="51"/>
+      <c r="Q3" s="51"/>
+      <c r="R3" s="51"/>
+      <c r="S3" s="51"/>
+      <c r="T3" s="51"/>
+      <c r="U3" s="51"/>
     </row>
     <row r="4" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="41"/>
-      <c r="K4" s="41"/>
-      <c r="L4" s="41"/>
-      <c r="M4" s="41"/>
-      <c r="N4" s="41"/>
-      <c r="O4" s="41"/>
-      <c r="P4" s="41"/>
-      <c r="Q4" s="41"/>
-      <c r="R4" s="41"/>
-      <c r="S4" s="41"/>
-      <c r="T4" s="41"/>
-      <c r="U4" s="41"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="52"/>
+      <c r="M4" s="52"/>
+      <c r="N4" s="52"/>
+      <c r="O4" s="52"/>
+      <c r="P4" s="52"/>
+      <c r="Q4" s="52"/>
+      <c r="R4" s="52"/>
+      <c r="S4" s="52"/>
+      <c r="T4" s="52"/>
+      <c r="U4" s="52"/>
     </row>
     <row r="5" spans="1:35" ht="40.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="48" t="s">
@@ -15707,115 +15707,115 @@
       <c r="I5" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="J5" s="42" t="s">
+      <c r="J5" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="43"/>
-      <c r="L5" s="43"/>
-      <c r="M5" s="43"/>
-      <c r="N5" s="43"/>
-      <c r="O5" s="44"/>
-      <c r="P5" s="45" t="s">
+      <c r="K5" s="54"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="54"/>
+      <c r="N5" s="54"/>
+      <c r="O5" s="55"/>
+      <c r="P5" s="56" t="s">
         <v>780</v>
       </c>
-      <c r="Q5" s="46"/>
-      <c r="R5" s="47"/>
-      <c r="S5" s="45">
+      <c r="Q5" s="57"/>
+      <c r="R5" s="58"/>
+      <c r="S5" s="56">
         <v>9701212867</v>
       </c>
-      <c r="T5" s="46"/>
-      <c r="U5" s="47"/>
+      <c r="T5" s="57"/>
+      <c r="U5" s="58"/>
     </row>
     <row r="6" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="49"/>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="51" t="s">
+      <c r="A6" s="59"/>
+      <c r="B6" s="59"/>
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="52"/>
+      <c r="K6" s="41"/>
       <c r="L6" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="M6" s="51" t="s">
+      <c r="M6" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="N6" s="52"/>
+      <c r="N6" s="41"/>
       <c r="O6" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="P6" s="51" t="s">
+      <c r="P6" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="Q6" s="52"/>
+      <c r="Q6" s="41"/>
       <c r="R6" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="S6" s="51" t="s">
+      <c r="S6" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="T6" s="52"/>
+      <c r="T6" s="41"/>
       <c r="U6" s="48" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:35" ht="31.35" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="50"/>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="50"/>
-      <c r="I7" s="50"/>
+      <c r="A7" s="49"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
       <c r="J7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L7" s="50"/>
+      <c r="L7" s="49"/>
       <c r="M7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="O7" s="50"/>
+      <c r="O7" s="49"/>
       <c r="P7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="Q7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="R7" s="50"/>
+      <c r="R7" s="49"/>
       <c r="S7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="T7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="U7" s="50"/>
+      <c r="U7" s="49"/>
     </row>
     <row r="8" spans="1:35" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="55"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="47"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -15869,15 +15869,15 @@
       <c r="B9" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="56" t="s">
+      <c r="C9" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="58"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="44"/>
       <c r="M9" s="6">
         <f t="shared" si="0"/>
         <v>21909487.239999998</v>
@@ -15928,15 +15928,15 @@
       <c r="B10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="56" t="s">
+      <c r="C10" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="58"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="44"/>
       <c r="M10" s="6">
         <f t="shared" si="0"/>
         <v>21909487.239999998</v>
@@ -15987,15 +15987,15 @@
       <c r="B11" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="56" t="s">
+      <c r="C11" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="57"/>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="58"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="44"/>
       <c r="M11" s="6">
         <f t="shared" si="0"/>
         <v>21909487.239999998</v>
@@ -16046,15 +16046,15 @@
       <c r="B12" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="56" t="s">
+      <c r="C12" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="57"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="58"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="44"/>
       <c r="M12" s="6">
         <f>SUM(M13,M66,M148,M169)</f>
         <v>21909487.239999998</v>
@@ -16105,15 +16105,15 @@
       <c r="B13" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="56" t="s">
+      <c r="C13" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="58"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="44"/>
       <c r="M13" s="6">
         <f>SUM(M14,M37,M45)</f>
         <v>3561291.31</v>
@@ -16164,15 +16164,15 @@
       <c r="B14" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="56" t="s">
+      <c r="C14" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="58"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="43"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="44"/>
       <c r="M14" s="6">
         <f>SUM(M15,M19,M21,M29)</f>
         <v>2618573.91</v>
@@ -16920,10 +16920,10 @@
       <c r="C25" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="D25" s="60" t="s">
+      <c r="D25" s="62" t="s">
         <v>781</v>
       </c>
-      <c r="E25" s="62" t="s">
+      <c r="E25" s="60" t="s">
         <v>784</v>
       </c>
       <c r="F25" s="18" t="s">
@@ -16976,8 +16976,8 @@
       <c r="C26" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="D26" s="61"/>
-      <c r="E26" s="63"/>
+      <c r="D26" s="63"/>
+      <c r="E26" s="61"/>
       <c r="F26" s="18" t="s">
         <v>79</v>
       </c>
@@ -17404,10 +17404,10 @@
       <c r="C33" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="D33" s="60" t="s">
+      <c r="D33" s="62" t="s">
         <v>781</v>
       </c>
-      <c r="E33" s="62" t="s">
+      <c r="E33" s="60" t="s">
         <v>784</v>
       </c>
       <c r="F33" s="18" t="s">
@@ -17463,8 +17463,8 @@
       <c r="C34" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="D34" s="61"/>
-      <c r="E34" s="63"/>
+      <c r="D34" s="63"/>
+      <c r="E34" s="61"/>
       <c r="F34" s="18" t="s">
         <v>79</v>
       </c>
@@ -17621,15 +17621,15 @@
       <c r="B37" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="C37" s="56" t="s">
+      <c r="C37" s="42" t="s">
         <v>154</v>
       </c>
-      <c r="D37" s="57"/>
-      <c r="E37" s="57"/>
-      <c r="F37" s="57"/>
-      <c r="G37" s="57"/>
-      <c r="H37" s="57"/>
-      <c r="I37" s="58"/>
+      <c r="D37" s="43"/>
+      <c r="E37" s="43"/>
+      <c r="F37" s="43"/>
+      <c r="G37" s="43"/>
+      <c r="H37" s="43"/>
+      <c r="I37" s="44"/>
       <c r="M37" s="6">
         <f>SUM(M38,M41,M43)</f>
         <v>122933.90000000001</v>
@@ -18214,15 +18214,15 @@
       <c r="B45" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="C45" s="56" t="s">
+      <c r="C45" s="42" t="s">
         <v>193</v>
       </c>
-      <c r="D45" s="57"/>
-      <c r="E45" s="57"/>
-      <c r="F45" s="57"/>
-      <c r="G45" s="57"/>
-      <c r="H45" s="57"/>
-      <c r="I45" s="58"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="43"/>
+      <c r="G45" s="43"/>
+      <c r="H45" s="43"/>
+      <c r="I45" s="44"/>
       <c r="M45" s="6">
         <f>SUM(M46,M51,M55,M60,M63)</f>
         <v>819783.5</v>
@@ -19620,15 +19620,15 @@
       <c r="B66" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="C66" s="56" t="s">
+      <c r="C66" s="42" t="s">
         <v>299</v>
       </c>
-      <c r="D66" s="57"/>
-      <c r="E66" s="57"/>
-      <c r="F66" s="57"/>
-      <c r="G66" s="57"/>
-      <c r="H66" s="57"/>
-      <c r="I66" s="58"/>
+      <c r="D66" s="43"/>
+      <c r="E66" s="43"/>
+      <c r="F66" s="43"/>
+      <c r="G66" s="43"/>
+      <c r="H66" s="43"/>
+      <c r="I66" s="44"/>
       <c r="M66" s="6">
         <f>SUM(M67,M97,M128)</f>
         <v>4332566.72</v>
@@ -19679,15 +19679,15 @@
       <c r="B67" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="C67" s="56" t="s">
+      <c r="C67" s="42" t="s">
         <v>302</v>
       </c>
-      <c r="D67" s="57"/>
-      <c r="E67" s="57"/>
-      <c r="F67" s="57"/>
-      <c r="G67" s="57"/>
-      <c r="H67" s="57"/>
-      <c r="I67" s="58"/>
+      <c r="D67" s="43"/>
+      <c r="E67" s="43"/>
+      <c r="F67" s="43"/>
+      <c r="G67" s="43"/>
+      <c r="H67" s="43"/>
+      <c r="I67" s="44"/>
       <c r="M67" s="6">
         <f>SUM(M68,M71,M75,M79,M82,M85,M89,M92)</f>
         <v>2963619.5900000003</v>
@@ -21739,15 +21739,15 @@
       <c r="B97" s="10" t="s">
         <v>419</v>
       </c>
-      <c r="C97" s="56" t="s">
+      <c r="C97" s="42" t="s">
         <v>420</v>
       </c>
-      <c r="D97" s="57"/>
-      <c r="E97" s="57"/>
-      <c r="F97" s="57"/>
-      <c r="G97" s="57"/>
-      <c r="H97" s="57"/>
-      <c r="I97" s="58"/>
+      <c r="D97" s="43"/>
+      <c r="E97" s="43"/>
+      <c r="F97" s="43"/>
+      <c r="G97" s="43"/>
+      <c r="H97" s="43"/>
+      <c r="I97" s="44"/>
       <c r="M97" s="6">
         <f>SUM(M98,M107,M110,M113,M116,M119,M122,M125)</f>
         <v>1187256.6599999997</v>
@@ -23826,15 +23826,15 @@
       <c r="B128" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="C128" s="56" t="s">
+      <c r="C128" s="42" t="s">
         <v>534</v>
       </c>
-      <c r="D128" s="57"/>
-      <c r="E128" s="57"/>
-      <c r="F128" s="57"/>
-      <c r="G128" s="57"/>
-      <c r="H128" s="57"/>
-      <c r="I128" s="58"/>
+      <c r="D128" s="43"/>
+      <c r="E128" s="43"/>
+      <c r="F128" s="43"/>
+      <c r="G128" s="43"/>
+      <c r="H128" s="43"/>
+      <c r="I128" s="44"/>
       <c r="M128" s="6">
         <f>SUM(M129,M132,M135,M138,M143)</f>
         <v>181690.47</v>
@@ -25157,15 +25157,15 @@
       <c r="B148" s="10" t="s">
         <v>616</v>
       </c>
-      <c r="C148" s="56" t="s">
+      <c r="C148" s="42" t="s">
         <v>617</v>
       </c>
-      <c r="D148" s="57"/>
-      <c r="E148" s="57"/>
-      <c r="F148" s="57"/>
-      <c r="G148" s="57"/>
-      <c r="H148" s="57"/>
-      <c r="I148" s="58"/>
+      <c r="D148" s="43"/>
+      <c r="E148" s="43"/>
+      <c r="F148" s="43"/>
+      <c r="G148" s="43"/>
+      <c r="H148" s="43"/>
+      <c r="I148" s="44"/>
       <c r="M148" s="6">
         <f>SUM(M149,M153)</f>
         <v>447303.98</v>
@@ -25216,15 +25216,15 @@
       <c r="B149" s="10" t="s">
         <v>619</v>
       </c>
-      <c r="C149" s="56" t="s">
+      <c r="C149" s="42" t="s">
         <v>620</v>
       </c>
-      <c r="D149" s="57"/>
-      <c r="E149" s="57"/>
-      <c r="F149" s="57"/>
-      <c r="G149" s="57"/>
-      <c r="H149" s="57"/>
-      <c r="I149" s="58"/>
+      <c r="D149" s="43"/>
+      <c r="E149" s="43"/>
+      <c r="F149" s="43"/>
+      <c r="G149" s="43"/>
+      <c r="H149" s="43"/>
+      <c r="I149" s="44"/>
       <c r="M149" s="6">
         <f>SUM(M150)</f>
         <v>241468.92</v>
@@ -25487,15 +25487,15 @@
       <c r="B153" s="10" t="s">
         <v>635</v>
       </c>
-      <c r="C153" s="56" t="s">
+      <c r="C153" s="42" t="s">
         <v>636</v>
       </c>
-      <c r="D153" s="57"/>
-      <c r="E153" s="57"/>
-      <c r="F153" s="57"/>
-      <c r="G153" s="57"/>
-      <c r="H153" s="57"/>
-      <c r="I153" s="58"/>
+      <c r="D153" s="43"/>
+      <c r="E153" s="43"/>
+      <c r="F153" s="43"/>
+      <c r="G153" s="43"/>
+      <c r="H153" s="43"/>
+      <c r="I153" s="44"/>
       <c r="M153" s="6">
         <f>SUM(M154,M157,M160,M163,M166)</f>
         <v>205835.06</v>
@@ -26618,15 +26618,15 @@
       <c r="B169" s="10" t="s">
         <v>683</v>
       </c>
-      <c r="C169" s="56" t="s">
+      <c r="C169" s="42" t="s">
         <v>684</v>
       </c>
-      <c r="D169" s="57"/>
-      <c r="E169" s="57"/>
-      <c r="F169" s="57"/>
-      <c r="G169" s="57"/>
-      <c r="H169" s="57"/>
-      <c r="I169" s="58"/>
+      <c r="D169" s="43"/>
+      <c r="E169" s="43"/>
+      <c r="F169" s="43"/>
+      <c r="G169" s="43"/>
+      <c r="H169" s="43"/>
+      <c r="I169" s="44"/>
       <c r="M169" s="6">
         <f>SUM(M170,M173,M177)</f>
         <v>13568325.229999999</v>
@@ -27304,29 +27304,29 @@
       </c>
     </row>
     <row r="179" spans="1:35" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A179" s="53" t="s">
+      <c r="A179" s="45" t="s">
         <v>728</v>
       </c>
-      <c r="B179" s="54"/>
-      <c r="C179" s="54"/>
-      <c r="D179" s="54"/>
-      <c r="E179" s="54"/>
-      <c r="F179" s="54"/>
-      <c r="G179" s="54"/>
-      <c r="H179" s="54"/>
-      <c r="I179" s="54"/>
-      <c r="J179" s="54"/>
-      <c r="K179" s="54"/>
-      <c r="L179" s="54"/>
-      <c r="M179" s="54"/>
-      <c r="N179" s="54"/>
-      <c r="O179" s="54"/>
-      <c r="P179" s="54"/>
-      <c r="Q179" s="54"/>
-      <c r="R179" s="54"/>
-      <c r="S179" s="54"/>
-      <c r="T179" s="54"/>
-      <c r="U179" s="55"/>
+      <c r="B179" s="46"/>
+      <c r="C179" s="46"/>
+      <c r="D179" s="46"/>
+      <c r="E179" s="46"/>
+      <c r="F179" s="46"/>
+      <c r="G179" s="46"/>
+      <c r="H179" s="46"/>
+      <c r="I179" s="46"/>
+      <c r="J179" s="46"/>
+      <c r="K179" s="46"/>
+      <c r="L179" s="46"/>
+      <c r="M179" s="46"/>
+      <c r="N179" s="46"/>
+      <c r="O179" s="46"/>
+      <c r="P179" s="46"/>
+      <c r="Q179" s="46"/>
+      <c r="R179" s="46"/>
+      <c r="S179" s="46"/>
+      <c r="T179" s="46"/>
+      <c r="U179" s="47"/>
     </row>
     <row r="180" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" s="30"/>
@@ -27342,20 +27342,20 @@
       <c r="E180" s="31"/>
       <c r="F180" s="31"/>
       <c r="G180" s="31"/>
-      <c r="H180" s="51"/>
-      <c r="I180" s="59"/>
-      <c r="J180" s="59"/>
-      <c r="K180" s="59"/>
-      <c r="L180" s="59"/>
-      <c r="M180" s="59"/>
-      <c r="N180" s="59"/>
-      <c r="O180" s="59"/>
-      <c r="P180" s="59"/>
-      <c r="Q180" s="59"/>
-      <c r="R180" s="59"/>
-      <c r="S180" s="59"/>
-      <c r="T180" s="59"/>
-      <c r="U180" s="52"/>
+      <c r="H180" s="39"/>
+      <c r="I180" s="40"/>
+      <c r="J180" s="40"/>
+      <c r="K180" s="40"/>
+      <c r="L180" s="40"/>
+      <c r="M180" s="40"/>
+      <c r="N180" s="40"/>
+      <c r="O180" s="40"/>
+      <c r="P180" s="40"/>
+      <c r="Q180" s="40"/>
+      <c r="R180" s="40"/>
+      <c r="S180" s="40"/>
+      <c r="T180" s="40"/>
+      <c r="U180" s="41"/>
     </row>
     <row r="181" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" s="30"/>
@@ -27371,20 +27371,20 @@
       <c r="E181" s="31"/>
       <c r="F181" s="31"/>
       <c r="G181" s="31"/>
-      <c r="H181" s="51"/>
-      <c r="I181" s="59"/>
-      <c r="J181" s="59"/>
-      <c r="K181" s="59"/>
-      <c r="L181" s="59"/>
-      <c r="M181" s="59"/>
-      <c r="N181" s="59"/>
-      <c r="O181" s="59"/>
-      <c r="P181" s="59"/>
-      <c r="Q181" s="59"/>
-      <c r="R181" s="59"/>
-      <c r="S181" s="59"/>
-      <c r="T181" s="59"/>
-      <c r="U181" s="52"/>
+      <c r="H181" s="39"/>
+      <c r="I181" s="40"/>
+      <c r="J181" s="40"/>
+      <c r="K181" s="40"/>
+      <c r="L181" s="40"/>
+      <c r="M181" s="40"/>
+      <c r="N181" s="40"/>
+      <c r="O181" s="40"/>
+      <c r="P181" s="40"/>
+      <c r="Q181" s="40"/>
+      <c r="R181" s="40"/>
+      <c r="S181" s="40"/>
+      <c r="T181" s="40"/>
+      <c r="U181" s="41"/>
     </row>
     <row r="182" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A182" s="30"/>
@@ -27400,20 +27400,20 @@
       <c r="E182" s="31"/>
       <c r="F182" s="31"/>
       <c r="G182" s="31"/>
-      <c r="H182" s="51"/>
-      <c r="I182" s="59"/>
-      <c r="J182" s="59"/>
-      <c r="K182" s="59"/>
-      <c r="L182" s="59"/>
-      <c r="M182" s="59"/>
-      <c r="N182" s="59"/>
-      <c r="O182" s="59"/>
-      <c r="P182" s="59"/>
-      <c r="Q182" s="59"/>
-      <c r="R182" s="59"/>
-      <c r="S182" s="59"/>
-      <c r="T182" s="59"/>
-      <c r="U182" s="52"/>
+      <c r="H182" s="39"/>
+      <c r="I182" s="40"/>
+      <c r="J182" s="40"/>
+      <c r="K182" s="40"/>
+      <c r="L182" s="40"/>
+      <c r="M182" s="40"/>
+      <c r="N182" s="40"/>
+      <c r="O182" s="40"/>
+      <c r="P182" s="40"/>
+      <c r="Q182" s="40"/>
+      <c r="R182" s="40"/>
+      <c r="S182" s="40"/>
+      <c r="T182" s="40"/>
+      <c r="U182" s="41"/>
     </row>
     <row r="183" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" s="30"/>
@@ -27429,20 +27429,20 @@
       <c r="E183" s="31"/>
       <c r="F183" s="31"/>
       <c r="G183" s="31"/>
-      <c r="H183" s="51"/>
-      <c r="I183" s="59"/>
-      <c r="J183" s="59"/>
-      <c r="K183" s="59"/>
-      <c r="L183" s="59"/>
-      <c r="M183" s="59"/>
-      <c r="N183" s="59"/>
-      <c r="O183" s="59"/>
-      <c r="P183" s="59"/>
-      <c r="Q183" s="59"/>
-      <c r="R183" s="59"/>
-      <c r="S183" s="59"/>
-      <c r="T183" s="59"/>
-      <c r="U183" s="52"/>
+      <c r="H183" s="39"/>
+      <c r="I183" s="40"/>
+      <c r="J183" s="40"/>
+      <c r="K183" s="40"/>
+      <c r="L183" s="40"/>
+      <c r="M183" s="40"/>
+      <c r="N183" s="40"/>
+      <c r="O183" s="40"/>
+      <c r="P183" s="40"/>
+      <c r="Q183" s="40"/>
+      <c r="R183" s="40"/>
+      <c r="S183" s="40"/>
+      <c r="T183" s="40"/>
+      <c r="U183" s="41"/>
     </row>
     <row r="184" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" s="30"/>
@@ -27458,20 +27458,20 @@
       <c r="E184" s="31"/>
       <c r="F184" s="31"/>
       <c r="G184" s="31"/>
-      <c r="H184" s="51"/>
-      <c r="I184" s="59"/>
-      <c r="J184" s="59"/>
-      <c r="K184" s="59"/>
-      <c r="L184" s="59"/>
-      <c r="M184" s="59"/>
-      <c r="N184" s="59"/>
-      <c r="O184" s="59"/>
-      <c r="P184" s="59"/>
-      <c r="Q184" s="59"/>
-      <c r="R184" s="59"/>
-      <c r="S184" s="59"/>
-      <c r="T184" s="59"/>
-      <c r="U184" s="52"/>
+      <c r="H184" s="39"/>
+      <c r="I184" s="40"/>
+      <c r="J184" s="40"/>
+      <c r="K184" s="40"/>
+      <c r="L184" s="40"/>
+      <c r="M184" s="40"/>
+      <c r="N184" s="40"/>
+      <c r="O184" s="40"/>
+      <c r="P184" s="40"/>
+      <c r="Q184" s="40"/>
+      <c r="R184" s="40"/>
+      <c r="S184" s="40"/>
+      <c r="T184" s="40"/>
+      <c r="U184" s="41"/>
     </row>
     <row r="185" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A185" s="30"/>
@@ -27487,20 +27487,20 @@
       <c r="E185" s="31"/>
       <c r="F185" s="31"/>
       <c r="G185" s="31"/>
-      <c r="H185" s="51"/>
-      <c r="I185" s="59"/>
-      <c r="J185" s="59"/>
-      <c r="K185" s="59"/>
-      <c r="L185" s="59"/>
-      <c r="M185" s="59"/>
-      <c r="N185" s="59"/>
-      <c r="O185" s="59"/>
-      <c r="P185" s="59"/>
-      <c r="Q185" s="59"/>
-      <c r="R185" s="59"/>
-      <c r="S185" s="59"/>
-      <c r="T185" s="59"/>
-      <c r="U185" s="52"/>
+      <c r="H185" s="39"/>
+      <c r="I185" s="40"/>
+      <c r="J185" s="40"/>
+      <c r="K185" s="40"/>
+      <c r="L185" s="40"/>
+      <c r="M185" s="40"/>
+      <c r="N185" s="40"/>
+      <c r="O185" s="40"/>
+      <c r="P185" s="40"/>
+      <c r="Q185" s="40"/>
+      <c r="R185" s="40"/>
+      <c r="S185" s="40"/>
+      <c r="T185" s="40"/>
+      <c r="U185" s="41"/>
     </row>
     <row r="186" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A186" s="30"/>
@@ -27516,20 +27516,20 @@
       <c r="E186" s="31"/>
       <c r="F186" s="31"/>
       <c r="G186" s="31"/>
-      <c r="H186" s="51"/>
-      <c r="I186" s="59"/>
-      <c r="J186" s="59"/>
-      <c r="K186" s="59"/>
-      <c r="L186" s="59"/>
-      <c r="M186" s="59"/>
-      <c r="N186" s="59"/>
-      <c r="O186" s="59"/>
-      <c r="P186" s="59"/>
-      <c r="Q186" s="59"/>
-      <c r="R186" s="59"/>
-      <c r="S186" s="59"/>
-      <c r="T186" s="59"/>
-      <c r="U186" s="52"/>
+      <c r="H186" s="39"/>
+      <c r="I186" s="40"/>
+      <c r="J186" s="40"/>
+      <c r="K186" s="40"/>
+      <c r="L186" s="40"/>
+      <c r="M186" s="40"/>
+      <c r="N186" s="40"/>
+      <c r="O186" s="40"/>
+      <c r="P186" s="40"/>
+      <c r="Q186" s="40"/>
+      <c r="R186" s="40"/>
+      <c r="S186" s="40"/>
+      <c r="T186" s="40"/>
+      <c r="U186" s="41"/>
     </row>
     <row r="187" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" s="30"/>
@@ -27545,20 +27545,20 @@
       <c r="E187" s="31"/>
       <c r="F187" s="31"/>
       <c r="G187" s="31"/>
-      <c r="H187" s="51"/>
-      <c r="I187" s="59"/>
-      <c r="J187" s="59"/>
-      <c r="K187" s="59"/>
-      <c r="L187" s="59"/>
-      <c r="M187" s="59"/>
-      <c r="N187" s="59"/>
-      <c r="O187" s="59"/>
-      <c r="P187" s="59"/>
-      <c r="Q187" s="59"/>
-      <c r="R187" s="59"/>
-      <c r="S187" s="59"/>
-      <c r="T187" s="59"/>
-      <c r="U187" s="52"/>
+      <c r="H187" s="39"/>
+      <c r="I187" s="40"/>
+      <c r="J187" s="40"/>
+      <c r="K187" s="40"/>
+      <c r="L187" s="40"/>
+      <c r="M187" s="40"/>
+      <c r="N187" s="40"/>
+      <c r="O187" s="40"/>
+      <c r="P187" s="40"/>
+      <c r="Q187" s="40"/>
+      <c r="R187" s="40"/>
+      <c r="S187" s="40"/>
+      <c r="T187" s="40"/>
+      <c r="U187" s="41"/>
     </row>
     <row r="188" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" s="30"/>
@@ -27574,20 +27574,20 @@
       <c r="E188" s="31"/>
       <c r="F188" s="31"/>
       <c r="G188" s="31"/>
-      <c r="H188" s="51"/>
-      <c r="I188" s="59"/>
-      <c r="J188" s="59"/>
-      <c r="K188" s="59"/>
-      <c r="L188" s="59"/>
-      <c r="M188" s="59"/>
-      <c r="N188" s="59"/>
-      <c r="O188" s="59"/>
-      <c r="P188" s="59"/>
-      <c r="Q188" s="59"/>
-      <c r="R188" s="59"/>
-      <c r="S188" s="59"/>
-      <c r="T188" s="59"/>
-      <c r="U188" s="52"/>
+      <c r="H188" s="39"/>
+      <c r="I188" s="40"/>
+      <c r="J188" s="40"/>
+      <c r="K188" s="40"/>
+      <c r="L188" s="40"/>
+      <c r="M188" s="40"/>
+      <c r="N188" s="40"/>
+      <c r="O188" s="40"/>
+      <c r="P188" s="40"/>
+      <c r="Q188" s="40"/>
+      <c r="R188" s="40"/>
+      <c r="S188" s="40"/>
+      <c r="T188" s="40"/>
+      <c r="U188" s="41"/>
     </row>
     <row r="189" spans="1:35" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A189" s="30"/>
@@ -27603,20 +27603,20 @@
       <c r="E189" s="31"/>
       <c r="F189" s="31"/>
       <c r="G189" s="31"/>
-      <c r="H189" s="51"/>
-      <c r="I189" s="59"/>
-      <c r="J189" s="59"/>
-      <c r="K189" s="59"/>
-      <c r="L189" s="59"/>
-      <c r="M189" s="59"/>
-      <c r="N189" s="59"/>
-      <c r="O189" s="59"/>
-      <c r="P189" s="59"/>
-      <c r="Q189" s="59"/>
-      <c r="R189" s="59"/>
-      <c r="S189" s="59"/>
-      <c r="T189" s="59"/>
-      <c r="U189" s="52"/>
+      <c r="H189" s="39"/>
+      <c r="I189" s="40"/>
+      <c r="J189" s="40"/>
+      <c r="K189" s="40"/>
+      <c r="L189" s="40"/>
+      <c r="M189" s="40"/>
+      <c r="N189" s="40"/>
+      <c r="O189" s="40"/>
+      <c r="P189" s="40"/>
+      <c r="Q189" s="40"/>
+      <c r="R189" s="40"/>
+      <c r="S189" s="40"/>
+      <c r="T189" s="40"/>
+      <c r="U189" s="41"/>
     </row>
     <row r="190" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A190" s="30"/>
@@ -27632,20 +27632,20 @@
       <c r="E190" s="31"/>
       <c r="F190" s="31"/>
       <c r="G190" s="31"/>
-      <c r="H190" s="51"/>
-      <c r="I190" s="59"/>
-      <c r="J190" s="59"/>
-      <c r="K190" s="59"/>
-      <c r="L190" s="59"/>
-      <c r="M190" s="59"/>
-      <c r="N190" s="59"/>
-      <c r="O190" s="59"/>
-      <c r="P190" s="59"/>
-      <c r="Q190" s="59"/>
-      <c r="R190" s="59"/>
-      <c r="S190" s="59"/>
-      <c r="T190" s="59"/>
-      <c r="U190" s="52"/>
+      <c r="H190" s="39"/>
+      <c r="I190" s="40"/>
+      <c r="J190" s="40"/>
+      <c r="K190" s="40"/>
+      <c r="L190" s="40"/>
+      <c r="M190" s="40"/>
+      <c r="N190" s="40"/>
+      <c r="O190" s="40"/>
+      <c r="P190" s="40"/>
+      <c r="Q190" s="40"/>
+      <c r="R190" s="40"/>
+      <c r="S190" s="40"/>
+      <c r="T190" s="40"/>
+      <c r="U190" s="41"/>
     </row>
     <row r="191" spans="1:35" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A191" s="30"/>
@@ -27661,20 +27661,20 @@
       <c r="E191" s="31"/>
       <c r="F191" s="31"/>
       <c r="G191" s="31"/>
-      <c r="H191" s="51"/>
-      <c r="I191" s="59"/>
-      <c r="J191" s="59"/>
-      <c r="K191" s="59"/>
-      <c r="L191" s="59"/>
-      <c r="M191" s="59"/>
-      <c r="N191" s="59"/>
-      <c r="O191" s="59"/>
-      <c r="P191" s="59"/>
-      <c r="Q191" s="59"/>
-      <c r="R191" s="59"/>
-      <c r="S191" s="59"/>
-      <c r="T191" s="59"/>
-      <c r="U191" s="52"/>
+      <c r="H191" s="39"/>
+      <c r="I191" s="40"/>
+      <c r="J191" s="40"/>
+      <c r="K191" s="40"/>
+      <c r="L191" s="40"/>
+      <c r="M191" s="40"/>
+      <c r="N191" s="40"/>
+      <c r="O191" s="40"/>
+      <c r="P191" s="40"/>
+      <c r="Q191" s="40"/>
+      <c r="R191" s="40"/>
+      <c r="S191" s="40"/>
+      <c r="T191" s="40"/>
+      <c r="U191" s="41"/>
     </row>
     <row r="192" spans="1:35" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" s="30"/>
@@ -27690,20 +27690,20 @@
       <c r="E192" s="31"/>
       <c r="F192" s="31"/>
       <c r="G192" s="31"/>
-      <c r="H192" s="51"/>
-      <c r="I192" s="59"/>
-      <c r="J192" s="59"/>
-      <c r="K192" s="59"/>
-      <c r="L192" s="59"/>
-      <c r="M192" s="59"/>
-      <c r="N192" s="59"/>
-      <c r="O192" s="59"/>
-      <c r="P192" s="59"/>
-      <c r="Q192" s="59"/>
-      <c r="R192" s="59"/>
-      <c r="S192" s="59"/>
-      <c r="T192" s="59"/>
-      <c r="U192" s="52"/>
+      <c r="H192" s="39"/>
+      <c r="I192" s="40"/>
+      <c r="J192" s="40"/>
+      <c r="K192" s="40"/>
+      <c r="L192" s="40"/>
+      <c r="M192" s="40"/>
+      <c r="N192" s="40"/>
+      <c r="O192" s="40"/>
+      <c r="P192" s="40"/>
+      <c r="Q192" s="40"/>
+      <c r="R192" s="40"/>
+      <c r="S192" s="40"/>
+      <c r="T192" s="40"/>
+      <c r="U192" s="41"/>
     </row>
     <row r="193" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="30"/>
@@ -27719,22 +27719,22 @@
       <c r="E193" s="31"/>
       <c r="F193" s="31"/>
       <c r="G193" s="31"/>
-      <c r="H193" s="51" t="s">
+      <c r="H193" s="39" t="s">
         <v>770</v>
       </c>
-      <c r="I193" s="59"/>
-      <c r="J193" s="59"/>
-      <c r="K193" s="59"/>
-      <c r="L193" s="59"/>
-      <c r="M193" s="59"/>
-      <c r="N193" s="59"/>
-      <c r="O193" s="59"/>
-      <c r="P193" s="59"/>
-      <c r="Q193" s="59"/>
-      <c r="R193" s="59"/>
-      <c r="S193" s="59"/>
-      <c r="T193" s="59"/>
-      <c r="U193" s="52"/>
+      <c r="I193" s="40"/>
+      <c r="J193" s="40"/>
+      <c r="K193" s="40"/>
+      <c r="L193" s="40"/>
+      <c r="M193" s="40"/>
+      <c r="N193" s="40"/>
+      <c r="O193" s="40"/>
+      <c r="P193" s="40"/>
+      <c r="Q193" s="40"/>
+      <c r="R193" s="40"/>
+      <c r="S193" s="40"/>
+      <c r="T193" s="40"/>
+      <c r="U193" s="41"/>
     </row>
     <row r="194" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" s="30"/>
@@ -27750,20 +27750,20 @@
       <c r="E194" s="31"/>
       <c r="F194" s="31"/>
       <c r="G194" s="31"/>
-      <c r="H194" s="51"/>
-      <c r="I194" s="59"/>
-      <c r="J194" s="59"/>
-      <c r="K194" s="59"/>
-      <c r="L194" s="59"/>
-      <c r="M194" s="59"/>
-      <c r="N194" s="59"/>
-      <c r="O194" s="59"/>
-      <c r="P194" s="59"/>
-      <c r="Q194" s="59"/>
-      <c r="R194" s="59"/>
-      <c r="S194" s="59"/>
-      <c r="T194" s="59"/>
-      <c r="U194" s="52"/>
+      <c r="H194" s="39"/>
+      <c r="I194" s="40"/>
+      <c r="J194" s="40"/>
+      <c r="K194" s="40"/>
+      <c r="L194" s="40"/>
+      <c r="M194" s="40"/>
+      <c r="N194" s="40"/>
+      <c r="O194" s="40"/>
+      <c r="P194" s="40"/>
+      <c r="Q194" s="40"/>
+      <c r="R194" s="40"/>
+      <c r="S194" s="40"/>
+      <c r="T194" s="40"/>
+      <c r="U194" s="41"/>
     </row>
     <row r="195" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" s="30"/>
@@ -27777,20 +27777,20 @@
       <c r="E195" s="31"/>
       <c r="F195" s="31"/>
       <c r="G195" s="31"/>
-      <c r="H195" s="51"/>
-      <c r="I195" s="59"/>
-      <c r="J195" s="59"/>
-      <c r="K195" s="59"/>
-      <c r="L195" s="59"/>
-      <c r="M195" s="59"/>
-      <c r="N195" s="59"/>
-      <c r="O195" s="59"/>
-      <c r="P195" s="59"/>
-      <c r="Q195" s="59"/>
-      <c r="R195" s="59"/>
-      <c r="S195" s="59"/>
-      <c r="T195" s="59"/>
-      <c r="U195" s="52"/>
+      <c r="H195" s="39"/>
+      <c r="I195" s="40"/>
+      <c r="J195" s="40"/>
+      <c r="K195" s="40"/>
+      <c r="L195" s="40"/>
+      <c r="M195" s="40"/>
+      <c r="N195" s="40"/>
+      <c r="O195" s="40"/>
+      <c r="P195" s="40"/>
+      <c r="Q195" s="40"/>
+      <c r="R195" s="40"/>
+      <c r="S195" s="40"/>
+      <c r="T195" s="40"/>
+      <c r="U195" s="41"/>
     </row>
     <row r="196" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" s="30"/>
@@ -27804,20 +27804,20 @@
       <c r="E196" s="31"/>
       <c r="F196" s="31"/>
       <c r="G196" s="31"/>
-      <c r="H196" s="51"/>
-      <c r="I196" s="59"/>
-      <c r="J196" s="59"/>
-      <c r="K196" s="59"/>
-      <c r="L196" s="59"/>
-      <c r="M196" s="59"/>
-      <c r="N196" s="59"/>
-      <c r="O196" s="59"/>
-      <c r="P196" s="59"/>
-      <c r="Q196" s="59"/>
-      <c r="R196" s="59"/>
-      <c r="S196" s="59"/>
-      <c r="T196" s="59"/>
-      <c r="U196" s="52"/>
+      <c r="H196" s="39"/>
+      <c r="I196" s="40"/>
+      <c r="J196" s="40"/>
+      <c r="K196" s="40"/>
+      <c r="L196" s="40"/>
+      <c r="M196" s="40"/>
+      <c r="N196" s="40"/>
+      <c r="O196" s="40"/>
+      <c r="P196" s="40"/>
+      <c r="Q196" s="40"/>
+      <c r="R196" s="40"/>
+      <c r="S196" s="40"/>
+      <c r="T196" s="40"/>
+      <c r="U196" s="41"/>
     </row>
     <row r="197" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" s="30"/>
@@ -27831,23 +27831,70 @@
       <c r="E197" s="31"/>
       <c r="F197" s="31"/>
       <c r="G197" s="31"/>
-      <c r="H197" s="51"/>
-      <c r="I197" s="59"/>
-      <c r="J197" s="59"/>
-      <c r="K197" s="59"/>
-      <c r="L197" s="59"/>
-      <c r="M197" s="59"/>
-      <c r="N197" s="59"/>
-      <c r="O197" s="59"/>
-      <c r="P197" s="59"/>
-      <c r="Q197" s="59"/>
-      <c r="R197" s="59"/>
-      <c r="S197" s="59"/>
-      <c r="T197" s="59"/>
-      <c r="U197" s="52"/>
+      <c r="H197" s="39"/>
+      <c r="I197" s="40"/>
+      <c r="J197" s="40"/>
+      <c r="K197" s="40"/>
+      <c r="L197" s="40"/>
+      <c r="M197" s="40"/>
+      <c r="N197" s="40"/>
+      <c r="O197" s="40"/>
+      <c r="P197" s="40"/>
+      <c r="Q197" s="40"/>
+      <c r="R197" s="40"/>
+      <c r="S197" s="40"/>
+      <c r="T197" s="40"/>
+      <c r="U197" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="63">
+    <mergeCell ref="H195:U195"/>
+    <mergeCell ref="H196:U196"/>
+    <mergeCell ref="H197:U197"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="H189:U189"/>
+    <mergeCell ref="H190:U190"/>
+    <mergeCell ref="H191:U191"/>
+    <mergeCell ref="H192:U192"/>
+    <mergeCell ref="H193:U193"/>
+    <mergeCell ref="H194:U194"/>
+    <mergeCell ref="H183:U183"/>
+    <mergeCell ref="H184:U184"/>
+    <mergeCell ref="H185:U185"/>
+    <mergeCell ref="H186:U186"/>
+    <mergeCell ref="H187:U187"/>
+    <mergeCell ref="C128:I128"/>
+    <mergeCell ref="C148:I148"/>
+    <mergeCell ref="H188:U188"/>
+    <mergeCell ref="C153:I153"/>
+    <mergeCell ref="C169:I169"/>
+    <mergeCell ref="A179:U179"/>
+    <mergeCell ref="H180:U180"/>
+    <mergeCell ref="H181:U181"/>
+    <mergeCell ref="H182:U182"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="U6:U7"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="C149:I149"/>
+    <mergeCell ref="C11:I11"/>
+    <mergeCell ref="C12:I12"/>
+    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="C37:I37"/>
+    <mergeCell ref="C45:I45"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="C66:I66"/>
+    <mergeCell ref="C67:I67"/>
+    <mergeCell ref="C97:I97"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="H5:H7"/>
+    <mergeCell ref="I5:I7"/>
+    <mergeCell ref="J5:O5"/>
+    <mergeCell ref="P5:R5"/>
+    <mergeCell ref="R6:R7"/>
     <mergeCell ref="A2:U2"/>
     <mergeCell ref="A3:U3"/>
     <mergeCell ref="A4:U4"/>
@@ -27864,53 +27911,6 @@
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="O6:O7"/>
     <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="H5:H7"/>
-    <mergeCell ref="I5:I7"/>
-    <mergeCell ref="J5:O5"/>
-    <mergeCell ref="P5:R5"/>
-    <mergeCell ref="R6:R7"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="U6:U7"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="C149:I149"/>
-    <mergeCell ref="C11:I11"/>
-    <mergeCell ref="C12:I12"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="C14:I14"/>
-    <mergeCell ref="C37:I37"/>
-    <mergeCell ref="C45:I45"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="C66:I66"/>
-    <mergeCell ref="C67:I67"/>
-    <mergeCell ref="C97:I97"/>
-    <mergeCell ref="C128:I128"/>
-    <mergeCell ref="C148:I148"/>
-    <mergeCell ref="H188:U188"/>
-    <mergeCell ref="C153:I153"/>
-    <mergeCell ref="C169:I169"/>
-    <mergeCell ref="A179:U179"/>
-    <mergeCell ref="H180:U180"/>
-    <mergeCell ref="H181:U181"/>
-    <mergeCell ref="H182:U182"/>
-    <mergeCell ref="H195:U195"/>
-    <mergeCell ref="H196:U196"/>
-    <mergeCell ref="H197:U197"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="H189:U189"/>
-    <mergeCell ref="H190:U190"/>
-    <mergeCell ref="H191:U191"/>
-    <mergeCell ref="H192:U192"/>
-    <mergeCell ref="H193:U193"/>
-    <mergeCell ref="H194:U194"/>
-    <mergeCell ref="H183:U183"/>
-    <mergeCell ref="H184:U184"/>
-    <mergeCell ref="H185:U185"/>
-    <mergeCell ref="H186:U186"/>
-    <mergeCell ref="H187:U187"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
